--- a/영업/B2B_영업리스트.xlsx
+++ b/영업/B2B_영업리스트.xlsx
@@ -13,7 +13,7 @@
     <sheet name="영업멘트" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'영업리스트'!$A$1:$T$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'영업리스트'!$A$1:$T$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T104"/>
+  <dimension ref="A1:T122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2092,57 +2092,57 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>(주)더플러스 (요가몰 YOGAMALL)</t>
+          <t>신시어리</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>스포츠·헬스·재활용품 유통사/OEM브랜드</t>
+          <t>소규모 판촉물·패키징 중개벤더</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>https://yogamall.co.kr</t>
+          <t>https://sincerely.one</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>031-947-0808</t>
+          <t>070-7169-1306</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>tobe@theplus.biz</t>
+          <t>ask@sincerely.one</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>https://yogamall.co.kr</t>
+          <t>https://sincerely.one/faq</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>경기 파주시</t>
+          <t>서울 성동구</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>요가·필라테스 매트, 소도구, 리포머, 재활운동 용품, 프랭클린메소드 교육 (요가원·스튜디오 납품)</t>
+          <t>브랜드 굿즈(볼캡·의류·문구·리빙), 기업 판촉·선물용 굿즈</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>약함(요가·필라테스 전문 유통몰, 자체 공장 정보 없음)</t>
+          <t>불명 — 사이트에 자체 공장·중국 지사 언급 없음</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>요가원·필라테스 스튜디오 대상 전문 유통몰로 매트·소도구·재활용품 PB 개발 시 외부 중국 OEM 파트너가 필요함.</t>
+          <t>성수 기반 소규모 브랜드 굿즈 스튜디오로 기업 마케팅팀 대상 소량 커스텀 굿즈를 기획·중개하는 전형적 타깃.</t>
         </is>
       </c>
       <c r="M20" s="9" t="inlineStr">
         <is>
-          <t>https://yogamall.co.kr</t>
+          <t>https://sincerely.one/about</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr"/>
@@ -2164,57 +2164,57 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>(주)브라이즈 (에이더 AIDER)</t>
+          <t>엠유플랜박스</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>스포츠·헬스·재활용품 유통사/OEM브랜드</t>
+          <t>소규모 판촉물·패키징 중개벤더</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>https://aidershop.com</t>
+          <t>https://muplanbox.com</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>1566-3175</t>
+          <t>02-6409-6813</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>aider@bryze.kr</t>
+          <t>muplanbox@naver.com</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>https://m.aidershop.com/article/qa/6/</t>
+          <t>https://muplanbox.com/shopinfo/company.html</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>서울 금천구</t>
+          <t>서울 성동구 성수동</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>무릎·손목·팔꿈치·발목 보호대, 스포츠 테이핑 등 관절 보호대 전문 브랜드 (물리치료사 개발)</t>
+          <t>포장박스·칼라박스·싸바리박스·골판지박스 소량 제작, 브랜드 패키지</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>불명(브랜드 기획·개발 중심, 자체 공장 여부 미공개)</t>
+          <t>불명 — 자체 공장·중국 소싱 언급 없음</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>보호대 전문 온라인 브랜드로 물리치료사 기획 제품을 외주 생산하는 구조로 보여 보호대 OEM 제조 파트너와의 협업 적합성이 매우 높음.</t>
+          <t>성수동 소규모 패키지 제작 브랜드로 소량 브랜드 박스 수요를 받아 외주 생산하는 구조라 중국 패키지 소싱 협업 여지가 큼.</t>
         </is>
       </c>
       <c r="M21" s="9" t="inlineStr">
         <is>
-          <t>https://aidershop.com</t>
+          <t>https://muplanbox.com/shopinfo/company.html</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr"/>
@@ -2236,57 +2236,57 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>(주)앳플리 (ATFLEE)</t>
+          <t>연패키지</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>스포츠·헬스·재활용품 유통사/OEM브랜드</t>
+          <t>소규모 판촉물·패키징 중개벤더</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>https://atflee.com</t>
+          <t>https://www.yeonpack.com</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>02-3445-7877</t>
+          <t>02-6956-1918</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>sales@atflee.com</t>
+          <t>y_pack30@naver.com</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>https://atflee.com/shopinfo/guide.html</t>
+          <t>https://www.yeonpack.com/box</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>서울 강남구</t>
+          <t>서울 중구 을지로</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>요가매트·필라테스매트·스마트 체성분 체중계·홈트레이닝 용품 (자체 브랜드 앳플리, 무신사·삼성 SmartThings 입점)</t>
+          <t>화장품 단상자·디저트박스·선물박스·친환경 패키지 주문제작</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>약함(디자인·앱 중심 온라인 브랜드, 자체 공장 정보 없음)</t>
+          <t>불명 — 자체 공장·중국 소싱 언급 없음</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>자체 공장 없이 브랜드·앱 중심으로 요가매트 등 홈트 용품을 운영하는 전형적인 OEM 브랜드로 중국 소싱 파트너 수요가 큼.</t>
+          <t>을지로 인쇄골목 소재 개인사업자 규모의 패키지 중개 벤더로 브랜드 박스 소량 주문을 외주 생산하는 타깃.</t>
         </is>
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>https://atflee.com/shopinfo/guide.html</t>
+          <t>https://www.yeonpack.com/</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr"/>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>(주)우성레포츠 (아리프 ALEAF)</t>
+          <t>(주)더플러스 (요가몰 YOGAMALL)</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2318,47 +2318,47 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>https://aleafsports.com</t>
+          <t>https://yogamall.co.kr</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>031-527-2338</t>
+          <t>031-947-0808</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>aleaf@wsleports.com</t>
+          <t>tobe@theplus.biz</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>https://aleafsports.com/faq</t>
+          <t>https://yogamall.co.kr</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>경기 남양주시 오남읍</t>
+          <t>경기 파주시</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>요가매트·폼롤러·짐볼·허리보호대·웨이트/홈트 운동기구·키즈스포츠 용품 (자체 브랜드 아리프)</t>
+          <t>요가·필라테스 매트, 소도구, 리포머, 재활운동 용품, 프랭클린메소드 교육 (요가원·스튜디오 납품)</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>불명(온라인 브랜드 운영, 자체 공장 정보 미공개)</t>
+          <t>약함(요가·필라테스 전문 유통몰, 자체 공장 정보 없음)</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>요가·필라테스·홈트 소도구를 자체 브랜드로 온라인 판매하며 허리보호대 등 보호대 라인까지 취급해 중국 OEM 소싱 파트너가 필요할 가능성이 높음.</t>
+          <t>요가원·필라테스 스튜디오 대상 전문 유통몰로 매트·소도구·재활용품 PB 개발 시 외부 중국 OEM 파트너가 필요함.</t>
         </is>
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>https://aleafsports.com/Privacy</t>
+          <t>https://yogamall.co.kr</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr"/>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>(주)코리아스포츠 (아이워너 IWANNA)</t>
+          <t>(주)브라이즈 (에이더 AIDER)</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -2390,47 +2390,47 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>https://korspo.com</t>
+          <t>https://aidershop.com</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>031-573-3313</t>
+          <t>1566-3175</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>k-korspo@naver.com</t>
+          <t>aider@bryze.kr</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>https://www.korea-sports.co.kr/contact</t>
+          <t>https://m.aidershop.com/article/qa/6/</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>경기 남양주시 오남읍</t>
+          <t>서울 금천구</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>폼롤러(EVA/EPP)·마사지볼·마사지스틱·무릎보호대·운동밴드·헬스소도구 (자체 브랜드 아이워너, 프로-스펙스 라이선스)</t>
+          <t>무릎·손목·팔꿈치·발목 보호대, 스포츠 테이핑 등 관절 보호대 전문 브랜드 (물리치료사 개발)</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>불명(자체 브랜드 제조·유통사이나 국내/중국 공장 보유 여부 사이트 확인 불가)</t>
+          <t>불명(브랜드 기획·개발 중심, 자체 공장 여부 미공개)</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>폼롤러·마사지볼·보호대 등 수십 종의 자체 브랜드 품목을 운영하는 종합 헬스소도구 유통사로 품목 확장·원가 절감을 위한 중국 OEM 파트너 수요가 큼.</t>
+          <t>보호대 전문 온라인 브랜드로 물리치료사 기획 제품을 외주 생산하는 구조로 보여 보호대 OEM 제조 파트너와의 협업 적합성이 매우 높음.</t>
         </is>
       </c>
       <c r="M24" s="9" t="inlineStr">
         <is>
-          <t>https://korspo.com/shopinfo/company.html</t>
+          <t>https://aidershop.com</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr"/>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>SJ코리아</t>
+          <t>(주)앳플리 (ATFLEE)</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -2462,35 +2462,47 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>http://www.sjkorea.co.kr</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr"/>
-      <c r="G25" s="5" t="inlineStr"/>
+          <t>https://atflee.com</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>02-3445-7877</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>sales@atflee.com</t>
+        </is>
+      </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>http://www.sjkorea.co.kr</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr"/>
+          <t>https://atflee.com/shopinfo/guide.html</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>서울 강남구</t>
+        </is>
+      </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>정형외과용 소모품(물리치료/통증치료, 캐스트/스프린트, 브레이스·보호대)</t>
+          <t>요가매트·필라테스매트·스마트 체성분 체중계·홈트레이닝 용품 (자체 브랜드 앳플리, 무신사·삼성 SmartThings 입점)</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>불명(정형외과 소모품 유통, 제조 정보 미확인)</t>
+          <t>약함(디자인·앱 중심 온라인 브랜드, 자체 공장 정보 없음)</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>정형외과·물리치료실 대상 브레이스·보호대 소모품 전문 유통사로 의료용 보호대 OEM 공급 파트너 수요가 직접적임.</t>
+          <t>자체 공장 없이 브랜드·앱 중심으로 요가매트 등 홈트 용품을 운영하는 전형적인 OEM 브랜드로 중국 소싱 파트너 수요가 큼.</t>
         </is>
       </c>
       <c r="M25" s="9" t="inlineStr">
         <is>
-          <t>http://www.sjkorea.co.kr/shop/goods/goods_list.php?category=009003006</t>
+          <t>https://atflee.com/shopinfo/guide.html</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr"/>
@@ -2512,49 +2524,57 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>매일매일디자인</t>
+          <t>(주)우성레포츠 (아리프 ALEAF)</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>캐릭터·IP·팬굿즈 기획사</t>
+          <t>스포츠·헬스·재활용품 유통사/OEM브랜드</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>https://www.elmogoon.com/</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr"/>
+          <t>https://aleafsports.com</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>031-527-2338</t>
+        </is>
+      </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>elshop@naver.com</t>
+          <t>aleaf@wsleports.com</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>https://www.elmogoon.com/ (홈페이지 문의)</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr"/>
+          <t>https://aleafsports.com/faq</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>경기 남양주시 오남읍</t>
+        </is>
+      </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>IP 캐릭터 굿즈 기획·제작, 굿즈·패키지 OEM, 브랜딩</t>
+          <t>요가매트·폼롤러·짐볼·허리보호대·웨이트/홈트 운동기구·키즈스포츠 용품 (자체 브랜드 아리프)</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>불명(디자인 스튜디오, 생산 거점 언급 없음)</t>
+          <t>불명(온라인 브랜드 운영, 자체 공장 정보 미공개)</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>IP 캐릭터 굿즈와 패키지 OEM을 기획하는 소규모 디자인 스튜디오로 제조는 전량 외주라 중국 소싱 파트너 필요성이 크다.</t>
+          <t>요가·필라테스·홈트 소도구를 자체 브랜드로 온라인 판매하며 허리보호대 등 보호대 라인까지 취급해 중국 OEM 소싱 파트너가 필요할 가능성이 높음.</t>
         </is>
       </c>
       <c r="M26" s="9" t="inlineStr">
         <is>
-          <t>https://www.elmogoon.com/ ; https://www.facebook.com/elmogoon0980/</t>
+          <t>https://aleafsports.com/Privacy</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr"/>
@@ -2576,53 +2596,57 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>엑스디컨스트럭트(XDT)</t>
+          <t>(주)코리아스포츠 (아이워너 IWANNA)</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>캐릭터·IP·팬굿즈 기획사</t>
+          <t>스포츠·헬스·재활용품 유통사/OEM브랜드</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>https://xdeconstruct.com/</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr"/>
+          <t>https://korspo.com</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>031-573-3313</t>
+        </is>
+      </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>xd@xdeconstruct.com</t>
+          <t>k-korspo@naver.com</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>https://xdeconstruct.com/ (온라인 제작 문의)</t>
+          <t>https://www.korea-sports.co.kr/contact</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>서울 중구</t>
+          <t>경기 남양주시 오남읍</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>아이돌·브랜드 굿즈 OEM/ODM(금속 키링, 주얼리, 헤어 액세서리, 패키지), 소량·대량 제작</t>
+          <t>폼롤러(EVA/EPP)·마사지볼·마사지스틱·무릎보호대·운동밴드·헬스소도구 (자체 브랜드 아이워너, 프로-스펙스 라이선스)</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>불명(기획·샘플·생산·검수·납품 일괄 진행 표기, 자체 공장·중국 거점 언급 없음)</t>
+          <t>불명(자체 브랜드 제조·유통사이나 국내/중국 공장 보유 여부 사이트 확인 불가)</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>아이돌 MD용 금속 키링·주얼리 등 중국 생산 의존도가 높은 품목을 OEM/ODM으로 기획하는 소규모 업체라 안정적인 중국 소싱 파트너가 유용하다.</t>
+          <t>폼롤러·마사지볼·보호대 등 수십 종의 자체 브랜드 품목을 운영하는 종합 헬스소도구 유통사로 품목 확장·원가 절감을 위한 중국 OEM 파트너 수요가 큼.</t>
         </is>
       </c>
       <c r="M27" s="9" t="inlineStr">
         <is>
-          <t>https://m.xdeconstruct.com/product/list_thumb.html?cate_no=42 ; https://xdeconstruct.com/</t>
+          <t>https://korspo.com/shopinfo/company.html</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr"/>
@@ -2644,49 +2668,45 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>클로스업(ClawsUp)</t>
+          <t>SJ코리아</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>캐릭터·IP·팬굿즈 기획사</t>
+          <t>스포츠·헬스·재활용품 유통사/OEM브랜드</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>https://clawsup.com/</t>
+          <t>http://www.sjkorea.co.kr</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>https://clawsup.com/ (홈페이지 제작 문의)</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>경기 부천시 소사구</t>
-        </is>
-      </c>
+          <t>http://www.sjkorea.co.kr</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr"/>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>캐릭터 토이 디자인, ABS/PVC 사출 피규어 양산, 소프트비닐·폴리레진 아트토이, 실리콘·러버 캐릭터 굿즈</t>
+          <t>정형외과용 소모품(물리치료/통증치료, 캐스트/스프린트, 브레이스·보호대)</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>불명(소량~1천개 이상 대량 생산 가능 표기, 금형·양산 거점 미공개)</t>
+          <t>불명(정형외과 소모품 유통, 제조 정보 미확인)</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>기업·프로스포츠·웹툰·지자체 캐릭터의 사출 피규어를 디자인해 양산하는 토이 디자인 업체로 금형·사출 양산은 중국 공장 의존도가 높아 소싱 파트너 수요가 크다.</t>
+          <t>정형외과·물리치료실 대상 브레이스·보호대 소모품 전문 유통사로 의료용 보호대 OEM 공급 파트너 수요가 직접적임.</t>
         </is>
       </c>
       <c r="M28" s="9" t="inlineStr">
         <is>
-          <t>https://clawsup.com/ ; https://www.emis.com/php/company-profile/KR/Clawsup_Inc_en_23408343.html</t>
+          <t>http://www.sjkorea.co.kr/shop/goods/goods_list.php?category=009003006</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr"/>
@@ -2708,49 +2728,57 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>허쉬위쉬(HUSHWISH)</t>
+          <t>메디브랜드(병원마켓) / (주)이을커뮤니케이션아임</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>캐릭터·IP·팬굿즈 기획사</t>
+          <t>제약·의료·치과 판촉물 벤더</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>https://www.hushwish.com/</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr"/>
+          <t>https://www.medibrand.co.kr/</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>1666-6973 / 070-4150-1731</t>
+        </is>
+      </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>hello@hushwish.com</t>
+          <t>medibrand@naver.com</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>https://www.hushwish.com/contact_form/ (프로젝트 의뢰·제작 문의, 회사 계정 이메일만 접수)</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr"/>
+          <t>https://www.medibrand.co.kr/service/cooperation.php</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>서울 서초구</t>
+        </is>
+      </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>캐릭터 개발·라이선싱, 기업 캐릭터 굿즈 기획, 이모티콘·애니메이션 콘텐츠</t>
+          <t>병·의원/치과 개원패키지, 판촉물, 명함, 쇼핑백, 캘린더, 의료진 포스터</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>불명(디자인·라이선싱 스튜디오로 생산 거점 언급 없음)</t>
+          <t>불명 (자체 중국공장·지사 언급 없음, 병원 디자인·인쇄 위주)</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>자체 라이선싱 캐릭터와 기업 캐릭터 굿즈를 기획하지만 제조 기능이 없는 디자인 스튜디오라 상품화 단계에서 중국 소싱 파트너가 필요하다.</t>
+          <t>900개 이상 병·의원 런칭 실적의 병원·치과 전문 디자인마켓으로 판촉물·개원패키지를 취급해 중국 생산 굿즈 공급 협업 여지가 큼.</t>
         </is>
       </c>
       <c r="M29" s="9" t="inlineStr">
         <is>
-          <t>https://www.hushwish.com/contact_form/ ; https://www.hushwish.com/post_character/hushwish_licensing/</t>
+          <t>https://www.medibrand.co.kr/service/cooperation.php</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr"/>
@@ -2772,53 +2800,53 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>굿픽 스튜디오(GOODPIC STUDIO)</t>
+          <t>하이어기프트</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>캐릭터·IP·팬굿즈 기획사 · 판촉물·굿즈 제작대행사</t>
+          <t>제약·의료·치과 판촉물 벤더</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>https://goodpicstudio.com/</t>
+          <t>https://cases.higher-gift.com/</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>070-8244-9005</t>
+          <t>1533-4855</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>contact@goodpic.co.kr</t>
+          <t>highergift@naver.com</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>https://goodpicstudio.com/contact/</t>
+          <t>https://cases.higher-gift.com/contact/</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>굿즈 OEM/ODM 제작 전반(캐릭터·브랜드 굿즈) / 굿즈 OEM/ODM 기획·제작</t>
+          <t>기업·관공서·학교·병원·단체 판촉물·기념품 (제품 선정~인쇄·포장·납품)</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>불명(OEM&amp;ODM 전문 표기만 있고 생산 거점 언급 없음)</t>
+          <t>불명 (자체 공장·중국지사 언급 없음)</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>OEM/ODM 굿즈 기획을 표방하는 소규모 스튜디오로 생산은 외부 공장에 의존하는 구조라 중국 소싱 파트너 제안에 열려 있을 가능성이 높다. / 소규모 OEM/ODM 굿즈 스튜디오로 자체 제조설비 언급이 없어 중국 생산 파트너 의존도가 높을 것으로 보인다.</t>
+          <t>병원 판촉물 납품사례를 별도 사이트로 운영하는 소규모 중개 벤더로 자체 공장이 없어 중국 생산 파트너 수요가 있을 것으로 판단됨.</t>
         </is>
       </c>
       <c r="M30" s="9" t="inlineStr">
         <is>
-          <t>https://goodpicstudio.com/ ; https://goodpicstudio.com/contact/</t>
+          <t>https://cases.higher-gift.com/contact/</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr"/>
@@ -2840,57 +2868,49 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>다이버(DiiVER)</t>
+          <t>매일매일디자인</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>캐릭터·IP·팬굿즈 기획사 · 판촉물·굿즈 제작대행사</t>
+          <t>캐릭터·IP·팬굿즈 기획사</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>https://diiver.kr/</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>02-466-0507</t>
-        </is>
-      </c>
+          <t>https://www.elmogoon.com/</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr"/>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>ask@diiver.kr</t>
+          <t>elshop@naver.com</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>https://diiver.kr/ (채팅 상담으로 견적 문의), https://diiver.kr/partner (파트너 입점)</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>서울 서대문구</t>
-        </is>
-      </c>
+          <t>https://www.elmogoon.com/ (홈페이지 문의)</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>브랜드·캐릭터 굿즈 기획, 웰컴키트, 에코굿즈, 플레잉카드, 패키지·브랜딩 / 브랜드 굿즈 제작, 웰컴키트, 굿즈 스토어 운영대행</t>
+          <t>IP 캐릭터 굿즈 기획·제작, 굿즈·패키지 OEM, 브랜딩</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>약함(경기 고양 '다이버 팩토리' 국내 생산 거점 보유, 중국 거점 언급 없음)</t>
+          <t>불명(디자인 스튜디오, 생산 거점 언급 없음)</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>국내 팩토리로 소량 제작은 자체 처리하지만 대량 IP 굿즈나 공산품 품목은 중국 소싱이 필요할 수 있어 보조 파트너로 접근 가능하다. / 브랜딩·디자인 중심의 굿즈 에이전시로 제조는 외주 구조라 중국 생산 파트너 확보 수요가 크다.</t>
+          <t>IP 캐릭터 굿즈와 패키지 OEM을 기획하는 소규모 디자인 스튜디오로 제조는 전량 외주라 중국 소싱 파트너 필요성이 크다.</t>
         </is>
       </c>
       <c r="M31" s="9" t="inlineStr">
         <is>
-          <t>https://diiver.kr/ ; https://www.diiver.kr/service</t>
+          <t>https://www.elmogoon.com/ ; https://www.facebook.com/elmogoon0980/</t>
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr"/>
@@ -2912,57 +2932,53 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>만상사</t>
+          <t>엑스디컨스트럭트(XDT)</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>캐릭터·IP·팬굿즈 기획사 · 판촉물·굿즈 제작대행사</t>
+          <t>캐릭터·IP·팬굿즈 기획사</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>https://mansangsa.com/</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>1566-9437</t>
-        </is>
-      </c>
+          <t>https://xdeconstruct.com/</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>biz@mansangsa.com</t>
+          <t>xd@xdeconstruct.com</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>https://mansangsa.com/ (홈페이지 상담 신청 폼)</t>
+          <t>https://xdeconstruct.com/ (온라인 제작 문의)</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>서울 금천구</t>
+          <t>서울 중구</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>게임·애니·웹툰·엔터 IP 굿즈, 인형/피규어 개발, OEM/ODM 상품, 단체복·키트, 해외 행사 MD / IP 굿즈, 기업 판촉물, 단체복, 웰컴키트, 인형·피규어 OEM/ODM</t>
+          <t>아이돌·브랜드 굿즈 OEM/ODM(금속 키링, 주얼리, 헤어 액세서리, 패키지), 소량·대량 제작</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>불명(전담 MD가 기획~검수·납품 일괄 진행, 자체 공장·중국 거점 언급 없음)</t>
+          <t>불명(기획·샘플·생산·검수·납품 일괄 진행 표기, 자체 공장·중국 거점 언급 없음)</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>넥슨·크래프톤 등 IP 보유사 대상 인형·피규어·굿즈를 기획해 외주 생산하는 B2B 기획사로 자체 공장이 없어 중국 소싱 파트너가 필요할 가능성이 높다. / 국내 인쇄 설비 기반의 중견 굿즈 플랫폼이나 인형·피규어 등 해외 제작 품목은 외부 소싱망을 활용하므로 부분 협업 여지가 있다.</t>
+          <t>아이돌 MD용 금속 키링·주얼리 등 중국 생산 의존도가 높은 품목을 OEM/ODM으로 기획하는 소규모 업체라 안정적인 중국 소싱 파트너가 유용하다.</t>
         </is>
       </c>
       <c r="M32" s="9" t="inlineStr">
         <is>
-          <t>https://mansangsa.com/about ; https://mansangsa.com/dolls-figures</t>
+          <t>https://m.xdeconstruct.com/product/list_thumb.html?cate_no=42 ; https://xdeconstruct.com/</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr"/>
@@ -2984,57 +3000,49 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>먼데이팩토리</t>
+          <t>클로스업(ClawsUp)</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>캐릭터·IP·팬굿즈 기획사 · 판촉물·굿즈 제작대행사</t>
+          <t>캐릭터·IP·팬굿즈 기획사</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>https://mondayfactory.co.kr/</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>031-546-0340</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>goodday@mondaypicnic.co.kr</t>
-        </is>
-      </c>
+          <t>https://clawsup.com/</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>https://mondayfactory.co.kr/ (온라인 견적 문의)</t>
+          <t>https://clawsup.com/ (홈페이지 제작 문의)</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구</t>
+          <t>경기 부천시 소사구</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>응원봉, 아크릴 스탠드·키링, 파우치, 에코백, 코스터, 웰컴키트, 캐릭터 굿즈·판촉물 / 퍼스널브랜딩 굿즈, 웰컴키트, 판촉물, 기념품(에코백, 문구, 생활소품)</t>
+          <t>캐릭터 토이 디자인, ABS/PVC 사출 피규어 양산, 소프트비닐·폴리레진 아트토이, 실리콘·러버 캐릭터 굿즈</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>불명(캐릭터사업·굿즈제작 원스톱 플랫폼 표기, 생산 거점 언급 없음)</t>
+          <t>불명(소량~1천개 이상 대량 생산 가능 표기, 금형·양산 거점 미공개)</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>응원봉·아크릴·잡화 등 중국 생산 비중이 큰 품목을 원스톱 기획하는 중소 업체로 자체 공장 언급이 없어 중국 소싱 파트너 제안 적합도가 높다. / 해외 소싱을 직접 한다고 하나 자체 현지 조직이 없어 안정적인 중국 생산·검수 파트너가 필요할 가능성이 높다.</t>
+          <t>기업·프로스포츠·웹툰·지자체 캐릭터의 사출 피규어를 디자인해 양산하는 토이 디자인 업체로 금형·사출 양산은 중국 공장 의존도가 높아 소싱 파트너 수요가 크다.</t>
         </is>
       </c>
       <c r="M33" s="9" t="inlineStr">
         <is>
-          <t>https://m.mondayfactory.co.kr/shopinfo/company.html ; https://mondayfactory.co.kr/category/%EC%9D%91%EC%9B%90%EB%B4%89/586/</t>
+          <t>https://clawsup.com/ ; https://www.emis.com/php/company-profile/KR/Clawsup_Inc_en_23408343.html</t>
         </is>
       </c>
       <c r="N33" s="7" t="inlineStr"/>
@@ -3056,49 +3064,49 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>오즈의 제작소(콘콘)</t>
+          <t>허쉬위쉬(HUSHWISH)</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>캐릭터·IP·팬굿즈 기획사 · 판촉물·굿즈 제작대행사</t>
+          <t>캐릭터·IP·팬굿즈 기획사</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>https://ozjejakso.com/</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>02-6735-3300</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr"/>
+          <t>https://www.hushwish.com/</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>hello@hushwish.com</t>
+        </is>
+      </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>https://ozjejakso.com/ (1:1 전담 매니저 상담 신청), 카카오톡 채널 https://pf.kakao.com/_XFfQs</t>
+          <t>https://www.hushwish.com/contact_form/ (프로젝트 의뢰·제작 문의, 회사 계정 이메일만 접수)</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>IP·캐릭터 굿즈, 피규어 굿즈, 페어 인기 굿즈, 기업 굿즈 전반(추천 알고리즘 기반 B2B 굿즈 제작 플랫폼) / 기업·IP 굿즈 추천/디자인/제작/배송 올인원, 대량 굿즈 제작</t>
+          <t>캐릭터 개발·라이선싱, 기업 캐릭터 굿즈 기획, 이모티콘·애니메이션 콘텐츠</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>불명(제작 플랫폼으로 협력 제작처 연결 방식, 자체 공장·중국 거점 언급 없음)</t>
+          <t>불명(디자인·라이선싱 스튜디오로 생산 거점 언급 없음)</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>2021년 설립된 B2B 굿즈 제작 매칭 플랫폼으로 자체 생산 설비 없이 다양한 품목을 외주로 처리하므로 중국 생산 파트너 풀 확보가 사업에 직접 도움이 된다. / 전담 PM이 다양한 굿즈를 기획·제작대행하는 구조라 자체 제조 없이 외부 생산 파트너 확보가 핵심이다.</t>
+          <t>자체 라이선싱 캐릭터와 기업 캐릭터 굿즈를 기획하지만 제조 기능이 없는 디자인 스튜디오라 상품화 단계에서 중국 소싱 파트너가 필요하다.</t>
         </is>
       </c>
       <c r="M34" s="9" t="inlineStr">
         <is>
-          <t>https://ozjejakso.com/ ; https://www.nextunicorn.kr/company/38d1c9668ce44aa7</t>
+          <t>https://www.hushwish.com/contact_form/ ; https://www.hushwish.com/post_character/hushwish_licensing/</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr"/>
@@ -3120,45 +3128,53 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>비더굿즈</t>
+          <t>굿픽 스튜디오(GOODPIC STUDIO)</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>판촉물·굿즈 제작대행사</t>
+          <t>캐릭터·IP·팬굿즈 기획사 · 판촉물·굿즈 제작대행사</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>https://bethegoods.shop/</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="5" t="inlineStr"/>
+          <t>https://goodpicstudio.com/</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>070-8244-9005</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>contact@goodpic.co.kr</t>
+        </is>
+      </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>https://bethegoods.shop/ (제작 문의), 인스타그램 @bethegoods.shop</t>
+          <t>https://goodpicstudio.com/contact/</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>기업 웰컴키트, 신입사원 키트, 행사 굿즈, 친환경 굿즈 소량 제작</t>
+          <t>굿즈 OEM/ODM 제작 전반(캐릭터·브랜드 굿즈) / 굿즈 OEM/ODM 기획·제작</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>불명(자체 공장·중국 지사 언급 확인 안 됨)</t>
+          <t>불명(OEM&amp;ODM 전문 표기만 있고 생산 거점 언급 없음)</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>소량·빠른 납기 위주의 B2B 웰컴키트 대행사로 자체 제조가 없어 구성품 소싱 파트너가 필요할 수 있으나 연락처는 사이트 직접 확인 필요.</t>
+          <t>OEM/ODM 굿즈 기획을 표방하는 소규모 스튜디오로 생산은 외부 공장에 의존하는 구조라 중국 소싱 파트너 제안에 열려 있을 가능성이 높다. / 소규모 OEM/ODM 굿즈 스튜디오로 자체 제조설비 언급이 없어 중국 생산 파트너 의존도가 높을 것으로 보인다.</t>
         </is>
       </c>
       <c r="M35" s="9" t="inlineStr">
         <is>
-          <t>https://bethegoods.shop/welcome-kit</t>
+          <t>https://goodpicstudio.com/ ; https://goodpicstudio.com/contact/</t>
         </is>
       </c>
       <c r="N35" s="7" t="inlineStr"/>
@@ -3180,57 +3196,57 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>썸띵((주)썸띵코퍼레이션)</t>
+          <t>다이버(DiiVER)</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>판촉물·굿즈 제작대행사</t>
+          <t>캐릭터·IP·팬굿즈 기획사 · 판촉물·굿즈 제작대행사</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>https://www.sumthing.co.kr/</t>
+          <t>https://diiver.kr/</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>02-3012-1206</t>
+          <t>02-466-0507</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>partners@sumthing.co.kr</t>
+          <t>ask@diiver.kr</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>https://www.sumthing.co.kr/ (제작문의)</t>
+          <t>https://diiver.kr/ (채팅 상담으로 견적 문의), https://diiver.kr/partner (파트너 입점)</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>서울 송파구</t>
+          <t>서울 서대문구</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>브랜드 굿즈·키트 기획/디자인/제조/포장/배송 원스톱, 웰컴키트</t>
+          <t>브랜드·캐릭터 굿즈 기획, 웰컴키트, 에코굿즈, 플레잉카드, 패키지·브랜딩 / 브랜드 굿즈 제작, 웰컴키트, 굿즈 스토어 운영대행</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>약함(폭넓은 소싱 네트워크와 자체 풀필먼트만 언급, 자체 중국 공장·지사 언급 없음)</t>
+          <t>약함(경기 고양 '다이버 팩토리' 국내 생산 거점 보유, 중국 거점 언급 없음)</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>디자인·기획 중심 굿즈 스타트업으로 제조는 외부 소싱에 의존하므로 난이도 높은 커스텀 아이템의 중국 생산 파트너가 유용하다.</t>
+          <t>국내 팩토리로 소량 제작은 자체 처리하지만 대량 IP 굿즈나 공산품 품목은 중국 소싱이 필요할 수 있어 보조 파트너로 접근 가능하다. / 브랜딩·디자인 중심의 굿즈 에이전시로 제조는 외주 구조라 중국 생산 파트너 확보 수요가 크다.</t>
         </is>
       </c>
       <c r="M36" s="9" t="inlineStr">
         <is>
-          <t>https://www.sumthing.co.kr/About</t>
+          <t>https://diiver.kr/ ; https://www.diiver.kr/service</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr"/>
@@ -3252,57 +3268,57 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>아카이브((주)재승그룹)</t>
+          <t>만상사</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>판촉물·굿즈 제작대행사</t>
+          <t>캐릭터·IP·팬굿즈 기획사 · 판촉물·굿즈 제작대행사</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>https://www.thearc.kr/</t>
+          <t>https://mansangsa.com/</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>031-922-0090</t>
+          <t>1566-9437</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>archivekit@naver.com</t>
+          <t>biz@mansangsa.com</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>https://www.thearc.kr/ (키트 제작 문의)</t>
+          <t>https://mansangsa.com/ (홈페이지 상담 신청 폼)</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>고양 일산동구</t>
+          <t>서울 금천구</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>기업 웰컴키트, 워크숍 키트, 텀블러·다이어리·에코백 등 브랜드 굿즈 패키지</t>
+          <t>게임·애니·웹툰·엔터 IP 굿즈, 인형/피규어 개발, OEM/ODM 상품, 단체복·키트, 해외 행사 MD / IP 굿즈, 기업 판촉물, 단체복, 웰컴키트, 인형·피규어 OEM/ODM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>불명(자체 공장·중국 지사 언급 확인 안 됨)</t>
+          <t>불명(전담 MD가 기획~검수·납품 일괄 진행, 자체 공장·중국 거점 언급 없음)</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>웰컴키트 구성품을 조합·제작하는 대행사로 원가 경쟁력 있는 구성품 소싱을 위한 중국 파트너가 유용하다.</t>
+          <t>넥슨·크래프톤 등 IP 보유사 대상 인형·피규어·굿즈를 기획해 외주 생산하는 B2B 기획사로 자체 공장이 없어 중국 소싱 파트너가 필요할 가능성이 높다. / 국내 인쇄 설비 기반의 중견 굿즈 플랫폼이나 인형·피규어 등 해외 제작 품목은 외부 소싱망을 활용하므로 부분 협업 여지가 있다.</t>
         </is>
       </c>
       <c r="M37" s="9" t="inlineStr">
         <is>
-          <t>https://www.thearc.kr/kitpackage</t>
+          <t>https://mansangsa.com/about ; https://mansangsa.com/dolls-figures</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr"/>
@@ -3324,57 +3340,57 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>에이원기프트(주식회사 에이원기프트)</t>
+          <t>먼데이팩토리</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>판촉물·굿즈 제작대행사</t>
+          <t>캐릭터·IP·팬굿즈 기획사 · 판촉물·굿즈 제작대행사</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>https://aonegift.co.kr/</t>
+          <t>https://mondayfactory.co.kr/</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>1661-1069</t>
+          <t>031-546-0340</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>aone@aonegift.co.kr</t>
+          <t>goodday@mondaypicnic.co.kr</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>https://aonegift.co.kr/ (온라인 견적문의)</t>
+          <t>https://mondayfactory.co.kr/ (온라인 견적 문의)</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>양산 물금읍</t>
+          <t>경기 성남시 분당구</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>기업·관공서 행사 판촉물, 기념품, 사은품 제작</t>
+          <t>응원봉, 아크릴 스탠드·키링, 파우치, 에코백, 코스터, 웰컴키트, 캐릭터 굿즈·판촉물 / 퍼스널브랜딩 굿즈, 웰컴키트, 판촉물, 기념품(에코백, 문구, 생활소품)</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>불명(자체 공장·중국 지사 언급 확인 안 됨)</t>
+          <t>불명(캐릭터사업·굿즈제작 원스톱 플랫폼 표기, 생산 거점 언급 없음)</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>영남권 판촉물 제작대행사로 자체 생산망 언급이 없어 저가·대량 아이템의 중국 소싱 파트너가 필요할 수 있다.</t>
+          <t>응원봉·아크릴·잡화 등 중국 생산 비중이 큰 품목을 원스톱 기획하는 중소 업체로 자체 공장 언급이 없어 중국 소싱 파트너 제안 적합도가 높다. / 해외 소싱을 직접 한다고 하나 자체 현지 조직이 없어 안정적인 중국 생산·검수 파트너가 필요할 가능성이 높다.</t>
         </is>
       </c>
       <c r="M38" s="9" t="inlineStr">
         <is>
-          <t>https://aonegift.co.kr/</t>
+          <t>https://m.mondayfactory.co.kr/shopinfo/company.html ; https://mondayfactory.co.kr/category/%EC%9D%91%EC%9B%90%EB%B4%89/586/</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr"/>
@@ -3396,57 +3412,49 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>주아기프트(주식회사 제이컴스)</t>
+          <t>오즈의 제작소(콘콘)</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>판촉물·굿즈 제작대행사</t>
+          <t>캐릭터·IP·팬굿즈 기획사 · 판촉물·굿즈 제작대행사</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>https://juagift.com/</t>
+          <t>https://ozjejakso.com/</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>1544-6233</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>juagift@juagift.com</t>
-        </is>
-      </c>
+          <t>02-6735-3300</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>https://juagift.com/ (온라인 견적/대량주문 문의)</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>군포시</t>
-        </is>
-      </c>
+          <t>https://ozjejakso.com/ (1:1 전담 매니저 상담 신청), 카카오톡 채널 https://pf.kakao.com/_XFfQs</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>판촉물·기념품·답례품·홍보용품 주문제작(인쇄·각인), 이벤트 사은품</t>
+          <t>IP·캐릭터 굿즈, 피규어 굿즈, 페어 인기 굿즈, 기업 굿즈 전반(추천 알고리즘 기반 B2B 굿즈 제작 플랫폼) / 기업·IP 굿즈 추천/디자인/제작/배송 올인원, 대량 굿즈 제작</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>불명(본사·출고센터만 공개, 중국 공장·지사 언급 없음)</t>
+          <t>불명(제작 플랫폼으로 협력 제작처 연결 방식, 자체 공장·중국 거점 언급 없음)</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>최저가 보장형 판촉물 제작대행사로 국내 출고센터만 운영해 원가 절감을 위한 중국 소싱 파트너 수요가 있을 수 있다.</t>
+          <t>2021년 설립된 B2B 굿즈 제작 매칭 플랫폼으로 자체 생산 설비 없이 다양한 품목을 외주로 처리하므로 중국 생산 파트너 풀 확보가 사업에 직접 도움이 된다. / 전담 PM이 다양한 굿즈를 기획·제작대행하는 구조라 자체 제조 없이 외부 생산 파트너 확보가 핵심이다.</t>
         </is>
       </c>
       <c r="M39" s="9" t="inlineStr">
         <is>
-          <t>https://juagift.com/</t>
+          <t>https://ozjejakso.com/ ; https://www.nextunicorn.kr/company/38d1c9668ce44aa7</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr"/>
@@ -3468,42 +3476,30 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>개성상인((주)개성상인)</t>
+          <t>비더굿즈</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>판촉물·굿즈 제작대행사 · 관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
+          <t>판촉물·굿즈 제작대행사</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>https://www.intermarket.co.kr/</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>1544-8713</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>info@intermarket.co.kr</t>
-        </is>
-      </c>
+          <t>https://bethegoods.shop/</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>https://intermarket.co.kr/src/order.php (주문/견적문의)</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>성남 분당구</t>
-        </is>
-      </c>
+          <t>https://bethegoods.shop/ (제작 문의), 인스타그램 @bethegoods.shop</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>기업·대학·공공기관 기념품, 판촉물, 웰컴키트, 브랜드 굿즈 세트 / 기념품·판촉물·굿즈·홍보물품 제작 (TECH/전자기기, 필기도구, 건강관리용품, 우산 등)</t>
+          <t>기업 웰컴키트, 신입사원 키트, 행사 굿즈, 친환경 굿즈 소량 제작</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -3513,12 +3509,12 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>판교 소재 판촉물·웰컴키트 제작대행사로 자체 제조망 언급이 없어 중국 소싱 파트너 활용 여지가 크다. / 판교 소재 판촉물 플랫폼으로 입점업체(공급사) 모집 구조를 갖추고 있어 직접 소싱보다는 공급사를 통해 조달할 가능성이 있으나 전자기기·굿즈 카테고리 확대 시 중국 소싱 파트너가 유용할 수 있음.</t>
+          <t>소량·빠른 납기 위주의 B2B 웰컴키트 대행사로 자체 제조가 없어 구성품 소싱 파트너가 필요할 수 있으나 연락처는 사이트 직접 확인 필요.</t>
         </is>
       </c>
       <c r="M40" s="9" t="inlineStr">
         <is>
-          <t>https://www.intermarket.co.kr/src/guide_usage.php</t>
+          <t>https://bethegoods.shop/welcome-kit</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr"/>
@@ -3540,53 +3536,57 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>고려기프트</t>
+          <t>썸띵((주)썸띵코퍼레이션)</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>판촉물·굿즈 제작대행사 · 관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
+          <t>판촉물·굿즈 제작대행사</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>https://adpanchok.co.kr/</t>
+          <t>https://www.sumthing.co.kr/</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>1577-2288</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr"/>
+          <t>02-3012-1206</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>partners@sumthing.co.kr</t>
+        </is>
+      </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>https://adpanchok.co.kr/ (온라인 견적상담), 협력사 입점 https://adpanchok.co.kr/partner/</t>
+          <t>https://www.sumthing.co.kr/ (제작문의)</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>서울 도봉구</t>
+          <t>서울 송파구</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>판촉물·홍보물품·기념품·답례품 단체주문(로고 인쇄·각인) / 판촉물·기념품 단체주문 (자동차용품 판촉물, 은행/금융권 판촉물, 공공기관 우선구매 대상기업)</t>
+          <t>브랜드 굿즈·키트 기획/디자인/제조/포장/배송 원스톱, 웰컴키트</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>불명(협력사 입점 방식으로 상품 공급, 자체 공장·중국 지사 언급 없음)</t>
+          <t>약함(폭넓은 소싱 네트워크와 자체 풀필먼트만 언급, 자체 중국 공장·지사 언급 없음)</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>협력사(공급사) 입점형 판촉물 전문몰이라 직접 소싱보다는 공급사 확보 관점에서 중국 소싱 파트너와 협업할 여지가 있다. / 공공기관 우선구매 대상기업이자 자사 사옥을 보유한 대형 판촉물 전문몰로 자동차용품·금융권 판촉물 등 다양한 카테고리를 대량 취급해 중국 소싱 파트너의 가치가 큼.</t>
+          <t>디자인·기획 중심 굿즈 스타트업으로 제조는 외부 소싱에 의존하므로 난이도 높은 커스텀 아이템의 중국 생산 파트너가 유용하다.</t>
         </is>
       </c>
       <c r="M41" s="9" t="inlineStr">
         <is>
-          <t>https://adpanchok.co.kr/partner/</t>
+          <t>https://www.sumthing.co.kr/About</t>
         </is>
       </c>
       <c r="N41" s="7" t="inlineStr"/>
@@ -3608,57 +3608,57 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>세종기프트(구 기프트인포)</t>
+          <t>아카이브((주)재승그룹)</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>판촉물·굿즈 제작대행사 · 관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
+          <t>판촉물·굿즈 제작대행사</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>https://giftinfo.co.kr/</t>
+          <t>https://www.thearc.kr/</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>02-500-5900</t>
+          <t>031-922-0090</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>help@gifti.co.kr</t>
+          <t>archivekit@naver.com</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>https://giftinfo.co.kr/ (온라인 견적/주문)</t>
+          <t>https://www.thearc.kr/ (키트 제작 문의)</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>서울 중구</t>
+          <t>고양 일산동구</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>판촉물·기념품·답례품·굿즈 전반(생활용품, 문구, 우산, 텀블러 등 로고 인쇄 제작) / 판촉물·기념품·답례품·굿즈 인쇄제작 (텀블러, 에코백, 문구, 건강식품 판촉물 등)</t>
+          <t>기업 웰컴키트, 워크숍 키트, 텀블러·다이어리·에코백 등 브랜드 굿즈 패키지</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>불명(사이트에 중국 공장·지사 언급 확인 안 됨, 최저가 보장형 종합 판촉물 쇼핑몰)</t>
+          <t>불명(자체 공장·중국 지사 언급 확인 안 됨)</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>대량 카탈로그형 판촉물 쇼핑몰로 자체 생산시설 언급이 없어 신규 아이템·OEM 기획 시 외부 중국 소싱 파트너가 필요할 가능성이 높다. / 대기업·공공기관 우선구매대상 기업으로 최저가 보장제를 내세우는 대형 판촉물 종합몰이라 원가 경쟁력 확보를 위한 중국 소싱 파트너 수요가 클 것으로 판단됨.</t>
+          <t>웰컴키트 구성품을 조합·제작하는 대행사로 원가 경쟁력 있는 구성품 소싱을 위한 중국 파트너가 유용하다.</t>
         </is>
       </c>
       <c r="M42" s="9" t="inlineStr">
         <is>
-          <t>https://giftinfo.co.kr/</t>
+          <t>https://www.thearc.kr/kitpackage</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr"/>
@@ -3680,42 +3680,42 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>시너지기프트</t>
+          <t>에이원기프트(주식회사 에이원기프트)</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>판촉물·굿즈 제작대행사 · 관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
+          <t>판촉물·굿즈 제작대행사</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>https://www.synergygift.co.kr/</t>
+          <t>https://aonegift.co.kr/</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>02-713-8555</t>
+          <t>1661-1069</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>master@synergygift.co.kr</t>
+          <t>aone@aonegift.co.kr</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>https://synergygift.co.kr/src/guide.php (주문가이드/견적문의)</t>
+          <t>https://aonegift.co.kr/ (온라인 견적문의)</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>고양 덕양구</t>
+          <t>양산 물금읍</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>기업·대학·연구소·공공기관 행사판촉물, 웰컴키트, 사은품, 굿즈 / 기업·대학·연구소·공공기관 행사판촉물, 홍보물품, 사은품, 웰컴키트, 굿즈 (텀블러, 손거울, 냅킨, 메모잇 등 주문제작형)</t>
+          <t>기업·관공서 행사 판촉물, 기념품, 사은품 제작</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>기관·기업 대상 판촉물 제작대행 위주로 자체 제조 언급이 없어 외부 소싱 파트너 활용 여지가 크다. / 보험사 사은품 검색에서 노출되는 공공기관·기업 행사판촉물 전문업체로 웰컴키트·굿즈 등 주문제작형 품목이 많아 중국 OEM 소싱 파트너 수요가 있을 것으로 판단됨.</t>
+          <t>영남권 판촉물 제작대행사로 자체 생산망 언급이 없어 저가·대량 아이템의 중국 소싱 파트너가 필요할 수 있다.</t>
         </is>
       </c>
       <c r="M43" s="9" t="inlineStr">
         <is>
-          <t>https://www.synergygift.co.kr/</t>
+          <t>https://aonegift.co.kr/</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr"/>
@@ -3752,57 +3752,57 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>판촉나라</t>
+          <t>주아기프트(주식회사 제이컴스)</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>판촉물·굿즈 제작대행사 · 관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
+          <t>판촉물·굿즈 제작대행사</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>https://87nara.kr/</t>
+          <t>https://juagift.com/</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>1533-8700</t>
+          <t>1544-6233</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>biz87@naver.com</t>
+          <t>juagift@juagift.com</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>카카오톡 ID 87narakr(야간문의), https://87nara.kr/ (온라인 견적)</t>
+          <t>https://juagift.com/ (온라인 견적/대량주문 문의)</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>대구 수성구</t>
+          <t>군포시</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>학교·관공서·기업 판촉물, 행사 기념품, 답례품, 단체선물 / 판촉물·기념품·답례품·사은품·홍보물 (공공기관기념품 카테고리 운영, 학원홍보물, 떡메모지, 세면백 등)</t>
+          <t>판촉물·기념품·답례품·홍보용품 주문제작(인쇄·각인), 이벤트 사은품</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>불명(자체 공장·중국 지사 언급 확인 안 됨)</t>
+          <t>불명(본사·출고센터만 공개, 중국 공장·지사 언급 없음)</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>소규모 판촉물 전문 쇼핑몰로 자체 제조 기반이 없어 신규 상품 소싱을 외부 파트너에 의존할 가능성이 높다. / 학교·관공서·기업 행사 판촉물을 전문으로 하는 대구권 온라인몰로 공공기관기념품 전용 카테고리를 운영하나 자체 해외 생산망 언급이 없어 외부 중국 소싱 파트너가 필요할 가능성이 높음.</t>
+          <t>최저가 보장형 판촉물 제작대행사로 국내 출고센터만 운영해 원가 절감을 위한 중국 소싱 파트너 수요가 있을 수 있다.</t>
         </is>
       </c>
       <c r="M44" s="9" t="inlineStr">
         <is>
-          <t>https://87nara.kr/</t>
+          <t>https://juagift.com/</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr"/>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>판촉넷(대한판촉 주식회사)</t>
+          <t>개성상인((주)개성상인)</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -3834,47 +3834,47 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>https://panchock.net/</t>
+          <t>https://www.intermarket.co.kr/</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>050-7790-0631</t>
+          <t>1544-8713</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>16008387@korea87.kr</t>
+          <t>info@intermarket.co.kr</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>https://panchock.net/ (온라인 견적문의)</t>
+          <t>https://intermarket.co.kr/src/order.php (주문/견적문의)</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>대구 수성구</t>
+          <t>성남 분당구</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>개업판촉물, 관공서·학교·기업 기념품, 홍보물 도매 / 프랜차이즈·은행(국민은행 등 금융권) 판촉물, 라이터·볼펜 등 판촉물 제작</t>
+          <t>기업·대학·공공기관 기념품, 판촉물, 웰컴키트, 브랜드 굿즈 세트 / 기념품·판촉물·굿즈·홍보물품 제작 (TECH/전자기기, 필기도구, 건강관리용품, 우산 등)</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>불명(회사소개에 자체 공장·중국 지사 언급 없음)</t>
+          <t>불명(자체 공장·중국 지사 언급 확인 안 됨)</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>지역 기반 판촉물 유통·제작대행사로 자체 제조망이 없어 차별화 아이템 확보를 위한 중국 소싱 파트너 수요가 있을 수 있다. / 은행별·프랜차이즈 판촉물 카테고리를 별도 운영하는 판촉물 전문몰로 금융권·가맹점 대량 판촉물 수요에 대응할 중국 소싱 파트너가 필요할 수 있으나 연락처는 사이트 접근 차단으로 미확인.</t>
+          <t>판교 소재 판촉물·웰컴키트 제작대행사로 자체 제조망 언급이 없어 중국 소싱 파트너 활용 여지가 크다. / 판교 소재 판촉물 플랫폼으로 입점업체(공급사) 모집 구조를 갖추고 있어 직접 소싱보다는 공급사를 통해 조달할 가능성이 있으나 전자기기·굿즈 카테고리 확대 시 중국 소싱 파트너가 유용할 수 있음.</t>
         </is>
       </c>
       <c r="M45" s="9" t="inlineStr">
         <is>
-          <t>https://panchock.net/</t>
+          <t>https://www.intermarket.co.kr/src/guide_usage.php</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr"/>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>판촉이지((주)펀앤허브)</t>
+          <t>고려기프트</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -3906,47 +3906,43 @@
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>https://easy1.co.kr/</t>
+          <t>https://adpanchok.co.kr/</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>02-412-0044</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>master@eggift.co.kr</t>
-        </is>
-      </c>
+          <t>1577-2288</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>https://easy1.co.kr/ (온라인 견적문의)</t>
+          <t>https://adpanchok.co.kr/ (온라인 견적상담), 협력사 입점 https://adpanchok.co.kr/partner/</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>서울 금천구(통신판매업신고 기준)</t>
+          <t>서울 도봉구</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>기업·대학·연구소·공공기관 행사판촉물, 홍보물품, 사은품(전자기기·생활용품 등) / 기업·대학·연구소·공공기관 행사판촉물, 홍보물품, 사은품 (공공기관 판촉물 모음전, 상패/트로피, 다이어리, 행사가방 등)</t>
+          <t>판촉물·홍보물품·기념품·답례품 단체주문(로고 인쇄·각인) / 판촉물·기념품 단체주문 (자동차용품 판촉물, 은행/금융권 판촉물, 공공기관 우선구매 대상기업)</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>불명(자체 공장·중국 지사 언급 확인 안 됨)</t>
+          <t>불명(협력사 입점 방식으로 상품 공급, 자체 공장·중국 지사 언급 없음)</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>브랜드 상품 유통 중심의 판촉물 제작대행사로 자체 제조가 없어 OEM 아이템 개발 시 외부 소싱 파트너가 필요하다. / 공공기관 판촉물 모음전을 별도 운영하며 대학·연구소·공공기관 행사 판촉물을 전문으로 하는 업체로 자체 해외 생산 언급이 없어 중국 소싱 파트너 수요가 있을 것으로 판단됨.</t>
+          <t>협력사(공급사) 입점형 판촉물 전문몰이라 직접 소싱보다는 공급사 확보 관점에서 중국 소싱 파트너와 협업할 여지가 있다. / 공공기관 우선구매 대상기업이자 자사 사옥을 보유한 대형 판촉물 전문몰로 자동차용품·금융권 판촉물 등 다양한 카테고리를 대량 취급해 중국 소싱 파트너의 가치가 큼.</t>
         </is>
       </c>
       <c r="M46" s="9" t="inlineStr">
         <is>
-          <t>https://easy1.co.kr/src/privacy.php</t>
+          <t>https://adpanchok.co.kr/partner/</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr"/>
@@ -3961,56 +3957,64 @@
       <c r="A47" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>상</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>마음상자</t>
+          <t>세종기프트(구 기프트인포)</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>OEM 온라인브랜드·패키징</t>
+          <t>판촉물·굿즈 제작대행사 · 관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>https://www.maumsangja.com</t>
+          <t>https://giftinfo.co.kr/</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>02-463-8212</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr"/>
+          <t>02-500-5900</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>help@gifti.co.kr</t>
+        </is>
+      </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>https://www.maumsangja.com/</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr"/>
+          <t>https://giftinfo.co.kr/ (온라인 견적/주문)</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>서울 중구</t>
+        </is>
+      </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>선물박스·단상자·싸바리박스, 쇼핑백, 맞춤 스티커 제작(1:1 패키지 컨설팅)</t>
+          <t>판촉물·기념품·답례품·굿즈 전반(생활용품, 문구, 우산, 텀블러 등 로고 인쇄 제작) / 판촉물·기념품·답례품·굿즈 인쇄제작 (텀블러, 에코백, 문구, 건강식품 판촉물 등)</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>약함(국내 생산시설 보유 표방, 중국 소싱망 언급 없음)</t>
+          <t>불명(사이트에 중국 공장·지사 언급 확인 안 됨, 최저가 보장형 종합 판촉물 쇼핑몰)</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>국내 생산시설로 박스를 만들지만 쇼핑백·파우치 등 외주 품목은 중국 소싱 파트너와 협업 여지가 있다.</t>
+          <t>대량 카탈로그형 판촉물 쇼핑몰로 자체 생산시설 언급이 없어 신규 아이템·OEM 기획 시 외부 중국 소싱 파트너가 필요할 가능성이 높다. / 대기업·공공기관 우선구매대상 기업으로 최저가 보장제를 내세우는 대형 판촉물 종합몰이라 원가 경쟁력 확보를 위한 중국 소싱 파트너 수요가 클 것으로 판단됨.</t>
         </is>
       </c>
       <c r="M47" s="9" t="inlineStr">
         <is>
-          <t>https://www.maumsangja.com/</t>
+          <t>https://giftinfo.co.kr/</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr"/>
@@ -4025,64 +4029,64 @@
       <c r="A48" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>상</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>박스네(BOXNE)</t>
+          <t>시너지기프트</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>OEM 온라인브랜드·패키징</t>
+          <t>판촉물·굿즈 제작대행사 · 관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>https://www.boxne.co.kr</t>
+          <t>https://www.synergygift.co.kr/</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>02-2277-0023</t>
+          <t>02-713-8555</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>syprint02@boxne.co.kr</t>
+          <t>master@synergygift.co.kr</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>https://www.boxne.co.kr/</t>
+          <t>https://synergygift.co.kr/src/guide.php (주문가이드/견적문의)</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>서울 중구</t>
+          <t>고양 덕양구</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>싸바리박스, 컬러 포장박스, 쇼핑백, 패키지 주문제작(김포 자체공장)</t>
+          <t>기업·대학·연구소·공공기관 행사판촉물, 웰컴키트, 사은품, 굿즈 / 기업·대학·연구소·공공기관 행사판촉물, 홍보물품, 사은품, 웰컴키트, 굿즈 (텀블러, 손거울, 냅킨, 메모잇 등 주문제작형)</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>약함(국내 김포 자체공장 보유, 중국 소싱망 언급 없음)</t>
+          <t>불명(자체 공장·중국 지사 언급 확인 안 됨)</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>국내 자체공장으로 박스는 직접 생산하지만 쇼핑백·부자재 원가 절감용 중국 소싱 수요가 있을 수 있다.</t>
+          <t>기관·기업 대상 판촉물 제작대행 위주로 자체 제조 언급이 없어 외부 소싱 파트너 활용 여지가 크다. / 보험사 사은품 검색에서 노출되는 공공기관·기업 행사판촉물 전문업체로 웰컴키트·굿즈 등 주문제작형 품목이 많아 중국 OEM 소싱 파트너 수요가 있을 것으로 판단됨.</t>
         </is>
       </c>
       <c r="M48" s="9" t="inlineStr">
         <is>
-          <t>https://www.boxne.co.kr/</t>
+          <t>https://www.synergygift.co.kr/</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr"/>
@@ -4097,64 +4101,64 @@
       <c r="A49" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>상</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>박스명가(BOXMGA)</t>
+          <t>판촉나라</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>OEM 온라인브랜드·패키징</t>
+          <t>판촉물·굿즈 제작대행사 · 관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>https://www.boxmga.com</t>
+          <t>https://87nara.kr/</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>02-2266-1113</t>
+          <t>1533-8700</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>syprint02@daum.net</t>
+          <t>biz87@naver.com</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>https://www.boxmga.com/sub06/sub01.php</t>
+          <t>카카오톡 ID 87narakr(야간문의), https://87nara.kr/ (온라인 견적)</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>서울 중구</t>
+          <t>대구 수성구</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>FSC인증 패키지, 화장품 단상자, 싸바리박스, 쇼핑백 제작</t>
+          <t>학교·관공서·기업 판촉물, 행사 기념품, 답례품, 단체선물 / 판촉물·기념품·답례품·사은품·홍보물 (공공기관기념품 카테고리 운영, 학원홍보물, 떡메모지, 세면백 등)</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>약함(충무로 기반 국내 인쇄·제작, 중국 소싱망 언급 없음)</t>
+          <t>불명(자체 공장·중국 지사 언급 확인 안 됨)</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>40년 국내 제작 노하우가 있으나 쇼핑백·특수 소재 패키지 원가 절감 시 중국 생산 파트너 수요가 있을 수 있다(박스네와 동일 그룹 추정).</t>
+          <t>소규모 판촉물 전문 쇼핑몰로 자체 제조 기반이 없어 신규 상품 소싱을 외부 파트너에 의존할 가능성이 높다. / 학교·관공서·기업 행사 판촉물을 전문으로 하는 대구권 온라인몰로 공공기관기념품 전용 카테고리를 운영하나 자체 해외 생산망 언급이 없어 외부 중국 소싱 파트너가 필요할 가능성이 높음.</t>
         </is>
       </c>
       <c r="M49" s="9" t="inlineStr">
         <is>
-          <t>https://www.boxmga.com/sub06/sub01.php</t>
+          <t>https://87nara.kr/</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr"/>
@@ -4169,64 +4173,64 @@
       <c r="A50" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>상</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>아르르((주)블랭크코퍼레이션/동원디어푸드)</t>
+          <t>판촉넷(대한판촉 주식회사)</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>OEM 온라인브랜드·패키징</t>
+          <t>판촉물·굿즈 제작대행사 · 관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>https://arrr.kr</t>
+          <t>https://panchock.net/</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>1877-3228</t>
+          <t>050-7790-0631</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>arrr@blankcorp.kr</t>
+          <t>16008387@korea87.kr</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>https://arrr.kr/cs/ / 카카오톡 @아르르</t>
+          <t>https://panchock.net/ (온라인 견적문의)</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>서울 서초구</t>
+          <t>대구 수성구</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>반려동물 용품·간식·장난감(미디어커머스 기반 자체 브랜드)</t>
+          <t>개업판촉물, 관공서·학교·기업 기념품, 홍보물 도매 / 프랜차이즈·은행(국민은행 등 금융권) 판촉물, 라이터·볼펜 등 판촉물 제작</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>불명(자체 공장 없는 미디어커머스형 브랜드, 모회사 소싱망 미확인)</t>
+          <t>불명(회사소개에 자체 공장·중국 지사 언급 없음)</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>외주 생산 기반 반려용품 브랜드지만 대기업(동원) 계열로 편입돼 기존 소싱망을 활용할 가능성이 있다.</t>
+          <t>지역 기반 판촉물 유통·제작대행사로 자체 제조망이 없어 차별화 아이템 확보를 위한 중국 소싱 파트너 수요가 있을 수 있다. / 은행별·프랜차이즈 판촉물 카테고리를 별도 운영하는 판촉물 전문몰로 금융권·가맹점 대량 판촉물 수요에 대응할 중국 소싱 파트너가 필요할 수 있으나 연락처는 사이트 접근 차단으로 미확인.</t>
         </is>
       </c>
       <c r="M50" s="9" t="inlineStr">
         <is>
-          <t>https://arrr.kr/cs/</t>
+          <t>https://panchock.net/</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr"/>
@@ -4241,60 +4245,64 @@
       <c r="A51" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>상</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>늘봄기프트 (늘봄컴퍼니)</t>
+          <t>판촉이지((주)펀앤허브)</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
+          <t>판촉물·굿즈 제작대행사 · 관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>https://alwaysbomgift.com/</t>
+          <t>https://easy1.co.kr/</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>1544-6233</t>
+          <t>02-412-0044</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>alwaysbom2018@naver.com</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr"/>
+          <t>master@eggift.co.kr</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>https://easy1.co.kr/ (온라인 견적문의)</t>
+        </is>
+      </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>성남 분당구</t>
+          <t>서울 금천구(통신판매업신고 기준)</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>기업·공공기관·관공서·대학교·학원·협회 기념품 판촉물 도매 (문구, 에코백, 생활용품 등)</t>
+          <t>기업·대학·연구소·공공기관 행사판촉물, 홍보물품, 사은품(전자기기·생활용품 등) / 기업·대학·연구소·공공기관 행사판촉물, 홍보물품, 사은품 (공공기관 판촉물 모음전, 상패/트로피, 다이어리, 행사가방 등)</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>불명(검색결과에 중국 공장/지사 언급 없음)</t>
+          <t>불명(자체 공장·중국 지사 언급 확인 안 됨)</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>관공서·대학교·학원 대상 판촉물 도매몰을 표방하는 소규모 업체로 자체 생산망이 없어 가격 경쟁력 확보를 위한 중국 소싱 파트너 활용 가능성이 있음.</t>
+          <t>브랜드 상품 유통 중심의 판촉물 제작대행사로 자체 제조가 없어 OEM 아이템 개발 시 외부 소싱 파트너가 필요하다. / 공공기관 판촉물 모음전을 별도 운영하며 대학·연구소·공공기관 행사 판촉물을 전문으로 하는 업체로 자체 해외 생산 언급이 없어 중국 소싱 파트너 수요가 있을 것으로 판단됨.</t>
         </is>
       </c>
       <c r="M51" s="9" t="inlineStr">
         <is>
-          <t>https://alwaysbomgift.com/</t>
+          <t>https://easy1.co.kr/src/privacy.php</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr"/>
@@ -4316,49 +4324,49 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>망고기프트 (원더풀라이프)</t>
+          <t>마음상자</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
+          <t>OEM 온라인브랜드·패키징</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>https://mangogift.co.kr/</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr"/>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>wdplife337@gmail.com</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>서울 구로구</t>
-        </is>
-      </c>
+          <t>https://www.maumsangja.com</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>02-463-8212</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>https://www.maumsangja.com/</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>판촉물·답례품·사은품·기념품 (핫팩, 손난로, 고급 수건 등 맞춤 제작)</t>
+          <t>선물박스·단상자·싸바리박스, 쇼핑백, 맞춤 스티커 제작(1:1 패키지 컨설팅)</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>불명(검색결과에 중국 공장/지사 언급 없음)</t>
+          <t>약함(국내 생산시설 보유 표방, 중국 소싱망 언급 없음)</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>보험사 사은품용 핫팩·수건 등 맞춤 제작 소규모 판촉몰로 자체 생산망이 없어 저가 대량 품목의 중국 소싱 파트너가 필요할 수 있음(대표전화는 검색결과가 타사와 중복 표기되어 미기재).</t>
+          <t>국내 생산시설로 박스를 만들지만 쇼핑백·파우치 등 외주 품목은 중국 소싱 파트너와 협업 여지가 있다.</t>
         </is>
       </c>
       <c r="M52" s="9" t="inlineStr">
         <is>
-          <t>https://mangogift.co.kr/</t>
+          <t>https://www.maumsangja.com/</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr"/>
@@ -4380,53 +4388,57 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>아로기프트</t>
+          <t>박스네(BOXNE)</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
+          <t>OEM 온라인브랜드·패키징</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>https://arogift.com/</t>
+          <t>https://www.boxne.co.kr</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>02-501-0774</t>
+          <t>02-2277-0023</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>arogift@naver.com</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr"/>
+          <t>syprint02@boxne.co.kr</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>https://www.boxne.co.kr/</t>
+        </is>
+      </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>서울 강남구</t>
+          <t>서울 중구</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>판촉물·기념품·사은품·홍보물품·답례품 (학교 졸업/입학 기념품, 담요, 구급함, 쇼핑백, 메모보드 등)</t>
+          <t>싸바리박스, 컬러 포장박스, 쇼핑백, 패키지 주문제작(김포 자체공장)</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>불명(검색결과에 중국 공장/지사 언급 없음)</t>
+          <t>약함(국내 김포 자체공장 보유, 중국 소싱망 언급 없음)</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>학교 기념품 검색에 노출되는 강남권 소규모 판촉몰로 자체 생산 언급이 없어 담요·구급함 등 범용 품목의 중국 소싱 파트너 활용 여지가 있음.</t>
+          <t>국내 자체공장으로 박스는 직접 생산하지만 쇼핑백·부자재 원가 절감용 중국 소싱 수요가 있을 수 있다.</t>
         </is>
       </c>
       <c r="M53" s="9" t="inlineStr">
         <is>
-          <t>https://arogift.com/</t>
+          <t>https://www.boxne.co.kr/</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr"/>
@@ -4448,45 +4460,57 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>예스폼기프트</t>
+          <t>박스명가(BOXMGA)</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
+          <t>OEM 온라인브랜드·패키징</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>https://www.yesformgift.com/</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr"/>
-      <c r="G54" s="5" t="inlineStr"/>
+          <t>https://www.boxmga.com</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>02-2266-1113</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>syprint02@daum.net</t>
+        </is>
+      </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>https://find.yesformgift.com/sp/ (행사별 기념품 검색/주문제작)</t>
-        </is>
-      </c>
-      <c r="I54" s="5" t="inlineStr"/>
+          <t>https://www.boxmga.com/sub06/sub01.php</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>서울 중구</t>
+        </is>
+      </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>졸업·입학선물 기념품, 단체선물 주문제작 (국내 최저가 표방)</t>
+          <t>FSC인증 패키지, 화장품 단상자, 싸바리박스, 쇼핑백 제작</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>불명(사이트 접근 차단으로 확인 불가)</t>
+          <t>약함(충무로 기반 국내 인쇄·제작, 중국 소싱망 언급 없음)</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>서식 플랫폼 예스폼 계열의 기념품 주문제작몰로 졸업·입학 등 학교 행사 기념품을 최저가로 취급해 중국 소싱 파트너 수요가 있을 수 있으나 연락처는 미확인.</t>
+          <t>40년 국내 제작 노하우가 있으나 쇼핑백·특수 소재 패키지 원가 절감 시 중국 생산 파트너 수요가 있을 수 있다(박스네와 동일 그룹 추정).</t>
         </is>
       </c>
       <c r="M54" s="9" t="inlineStr">
         <is>
-          <t>https://find.yesformgift.com/sp/event_%C1%B9%BE%F7%7C%C0%D4%C7%D0%BC%B1%B9%B0/</t>
+          <t>https://www.boxmga.com/sub06/sub01.php</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr"/>
@@ -4508,45 +4532,57 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>위시판촉 (wishcar)</t>
+          <t>아르르((주)블랭크코퍼레이션/동원디어푸드)</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
+          <t>OEM 온라인브랜드·패키징</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>https://wishcar.co.kr/</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr"/>
-      <c r="G55" s="5" t="inlineStr"/>
+          <t>https://arrr.kr</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>1877-3228</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>arrr@blankcorp.kr</t>
+        </is>
+      </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>https://wishcar.co.kr/shop/list.php?ca_id=081008 (프랜차이즈 판촉물 카테고리)</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr"/>
+          <t>https://arrr.kr/cs/ / 카카오톡 @아르르</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>서울 서초구</t>
+        </is>
+      </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>공공기관·지자체·협회·기업 행사 판촉물·기념품, 프랜차이즈 본사납품·가맹점 홍보 굿즈</t>
+          <t>반려동물 용품·간식·장난감(미디어커머스 기반 자체 브랜드)</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>불명(사이트 접근 차단으로 확인 불가)</t>
+          <t>불명(자체 공장 없는 미디어커머스형 브랜드, 모회사 소싱망 미확인)</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>언론(브랜드경제신문)에서 공공기관·지자체 행사 담당자용 판촉물 플랫폼으로 소개되고 프랜차이즈 본사납품 카테고리를 갖춰 중국 소싱 파트너 수요가 있을 수 있으나 연락처는 미확인.</t>
+          <t>외주 생산 기반 반려용품 브랜드지만 대기업(동원) 계열로 편입돼 기존 소싱망을 활용할 가능성이 있다.</t>
         </is>
       </c>
       <c r="M55" s="9" t="inlineStr">
         <is>
-          <t>https://www.benews.co.kr/news/475927</t>
+          <t>https://arrr.kr/cs/</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr"/>
@@ -4568,7 +4604,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>제이기프트</t>
+          <t>늘봄기프트 (늘봄컴퍼니)</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -4578,24 +4614,28 @@
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>https://jgift.kr/</t>
+          <t>https://alwaysbomgift.com/</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>070-8777-9371</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr"/>
+          <t>1544-6233</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>alwaysbom2018@naver.com</t>
+        </is>
+      </c>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>수원 권선구</t>
+          <t>성남 분당구</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>홍보판촉물 (USB, 보조배터리, 볼펜, 우산, 백팩·파우치, 경광봉·안전용품, 트로피, 비즈니스 선물세트)</t>
+          <t>기업·공공기관·관공서·대학교·학원·협회 기념품 판촉물 도매 (문구, 에코백, 생활용품 등)</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
@@ -4605,12 +4645,12 @@
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>USB·보조배터리 등 전자 판촉물과 가방류를 주력으로 하는 수원 소재 소규모 판촉몰로 중국 생산 의존도가 높은 품목 구성이라 소싱 파트너 활용 가능성이 있음(공개 이메일이 개인 계정 형태라 미기재).</t>
+          <t>관공서·대학교·학원 대상 판촉물 도매몰을 표방하는 소규모 업체로 자체 생산망이 없어 가격 경쟁력 확보를 위한 중국 소싱 파트너 활용 가능성이 있음.</t>
         </is>
       </c>
       <c r="M56" s="9" t="inlineStr">
         <is>
-          <t>https://jgift.kr/shop/view.php?index_no=749880</t>
+          <t>https://alwaysbomgift.com/</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr"/>
@@ -4632,7 +4672,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>판촉물천국</t>
+          <t>망고기프트 (원더풀라이프)</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -4642,35 +4682,39 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>https://giftheaven.co.kr/</t>
+          <t>https://mangogift.co.kr/</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr"/>
-      <c r="G57" s="5" t="inlineStr"/>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>https://panchokmool.co.kr/panchokmool-category/school-promotional-item/ (학교기념품 제작 카테고리)</t>
-        </is>
-      </c>
-      <c r="I57" s="5" t="inlineStr"/>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>wdplife337@gmail.com</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr"/>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>서울 구로구</t>
+        </is>
+      </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>학교 기념품·답례품 (USB, 보조배터리 등), 행사 판촉물</t>
+          <t>판촉물·답례품·사은품·기념품 (핫팩, 손난로, 고급 수건 등 맞춤 제작)</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>불명(사이트 접근 차단으로 확인 불가)</t>
+          <t>불명(검색결과에 중국 공장/지사 언급 없음)</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>학교 기념품 전용 카테고리를 운영하며 USB·보조배터리 등 중국 생산 의존 품목을 학교 단체선물로 제안하는 업체라 중국 소싱 파트너 활용 여지가 있으나 연락처는 미확인.</t>
+          <t>보험사 사은품용 핫팩·수건 등 맞춤 제작 소규모 판촉몰로 자체 생산망이 없어 저가 대량 품목의 중국 소싱 파트너가 필요할 수 있음(대표전화는 검색결과가 타사와 중복 표기되어 미기재).</t>
         </is>
       </c>
       <c r="M57" s="9" t="inlineStr">
         <is>
-          <t>https://giftheaven.co.kr/gift/%ED%95%99%EA%B5%90-%EA%B8%B0%EB%85%90%ED%92%88/</t>
+          <t>https://mangogift.co.kr/</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr"/>
@@ -4692,45 +4736,53 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>(주)아이전시</t>
+          <t>아로기프트</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>광고·BTL·행사대행사</t>
+          <t>관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>https://iex8808.cafe24.com</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr"/>
-      <c r="G58" s="5" t="inlineStr"/>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>https://iex8808.cafe24.com (견적·부스문의 게시판, 네이버톡톡)</t>
-        </is>
-      </c>
-      <c r="I58" s="5" t="inlineStr"/>
+          <t>https://arogift.com/</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>02-501-0774</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>arogift@naver.com</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr"/>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>서울 강남구</t>
+        </is>
+      </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>전시부스, 학회부스, 박람회·이벤트 부스, 포토존, 블럭·패브릭 부스, 가판대·홍보·판촉 집기</t>
+          <t>판촉물·기념품·사은품·홍보물품·답례품 (학교 졸업/입학 기념품, 담요, 구급함, 쇼핑백, 메모보드 등)</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>약함(부스 제작·설치 전문, 중국 거점 언급 없음)</t>
+          <t>불명(검색결과에 중국 공장/지사 언급 없음)</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>전시·학회·기업행사용 부스와 판촉 집기를 제작하는 업체로 포토존·가판대·판촉물 부자재를 대량 조달하기 때문에 중국 소싱 파트너 연계 가능성이 있다.</t>
+          <t>학교 기념품 검색에 노출되는 강남권 소규모 판촉몰로 자체 생산 언급이 없어 담요·구급함 등 범용 품목의 중국 소싱 파트너 활용 여지가 있음.</t>
         </is>
       </c>
       <c r="M58" s="9" t="inlineStr">
         <is>
-          <t>https://iex8808.cafe24.com/ ; https://iex8808.cafe24.com/category/%EA%B0%80%ED%8C%90%EB%8C%80%C2%B7%ED%99%8D%EB%B3%B4%C2%B7%ED%8C%90%EC%B4%89%C2%B7%EB%8B%A4%ED%8A%B8/53/</t>
+          <t>https://arogift.com/</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr"/>
@@ -4752,57 +4804,45 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>(주)콤마엔터테인먼트</t>
+          <t>예스폼기프트</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>광고·BTL·행사대행사</t>
+          <t>관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>https://www.comma-entertainment.com</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>02-6319-6947</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>info@comma-entertainment.com</t>
-        </is>
-      </c>
+          <t>https://www.yesformgift.com/</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr"/>
+      <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>https://www.comma-entertainment.com/contact</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>서울 강남구</t>
-        </is>
-      </c>
+          <t>https://find.yesformgift.com/sp/ (행사별 기념품 검색/주문제작)</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>이벤트·컨벤션 대행, 콘서트, 프로모션, BTL 마케팅, 옥외광고, 해외 마케팅(인바운드·아웃바운드), SNS·인플루언서</t>
+          <t>졸업·입학선물 기념품, 단체선물 주문제작 (국내 최저가 표방)</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>약함(해외 마케팅 대행사이나 중국 공장·지사 언급 없음)</t>
+          <t>불명(사이트 접근 차단으로 확인 불가)</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>국내 기업의 해외 마케팅과 해외 기업의 국내 행사를 대행하는 글로벌 종합광고대행사로 행사·프로모션용 굿즈를 국경 간으로 조달·배송해야 해 중국 소싱·운송 일괄 파트너가 유용하다.</t>
+          <t>서식 플랫폼 예스폼 계열의 기념품 주문제작몰로 졸업·입학 등 학교 행사 기념품을 최저가로 취급해 중국 소싱 파트너 수요가 있을 수 있으나 연락처는 미확인.</t>
         </is>
       </c>
       <c r="M59" s="9" t="inlineStr">
         <is>
-          <t>https://www.comma-entertainment.com/contact ; https://www.comma-entertainment.com/experience</t>
+          <t>https://find.yesformgift.com/sp/event_%C1%B9%BE%F7%7C%C0%D4%C7%D0%BC%B1%B9%B0/</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr"/>
@@ -4824,57 +4864,45 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>(주)크레픽스</t>
+          <t>위시판촉 (wishcar)</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>광고·BTL·행사대행사</t>
+          <t>관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>https://www.creaphics.com</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>070-7604-5959</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>jin@creaphics.com</t>
-        </is>
-      </c>
+          <t>https://wishcar.co.kr/</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr"/>
+      <c r="G60" s="5" t="inlineStr"/>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>https://www.creaphics.com/24</t>
-        </is>
-      </c>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>서울 구로구</t>
-        </is>
-      </c>
+          <t>https://wishcar.co.kr/shop/list.php?ca_id=081008 (프랜차이즈 판촉물 카테고리)</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>BTL 광고, 행사 대행, 프로모션, 광고물 제작</t>
+          <t>공공기관·지자체·협회·기업 행사 판촉물·기념품, 프랜차이즈 본사납품·가맹점 홍보 굿즈</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>약함(소규모 BTL 대행사, 자체 해외 거점 언급 없음)</t>
+          <t>불명(사이트 접근 차단으로 확인 불가)</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>효율성을 내세우는 소형 BTL 광고회사로 자체 제작 인프라가 없어 행사 판촉물·굿즈를 저비용으로 조달해 줄 외부 소싱 파트너가 필요하다.</t>
+          <t>언론(브랜드경제신문)에서 공공기관·지자체 행사 담당자용 판촉물 플랫폼으로 소개되고 프랜차이즈 본사납품 카테고리를 갖춰 중국 소싱 파트너 수요가 있을 수 있으나 연락처는 미확인.</t>
         </is>
       </c>
       <c r="M60" s="9" t="inlineStr">
         <is>
-          <t>https://www.creaphics.com/24</t>
+          <t>https://www.benews.co.kr/news/475927</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr"/>
@@ -4896,49 +4924,49 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>(주)탑스탠다드</t>
+          <t>제이기프트</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>광고·BTL·행사대행사</t>
+          <t>관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>http://www.topstandard.co.kr</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr"/>
+          <t>https://jgift.kr/</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>070-8777-9371</t>
+        </is>
+      </c>
       <c r="G61" s="5" t="inlineStr"/>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>http://www.topstandard.co.kr (홈페이지 문의)</t>
-        </is>
-      </c>
+      <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>경기 광명시</t>
+          <t>수원 권선구</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>행사 진행 대행, 전시부스 제작·설치, 심포지엄·컨퍼런스·세미나, 기업행사, 행사용품 렌탈(탑렌탈)</t>
+          <t>홍보판촉물 (USB, 보조배터리, 볼펜, 우산, 백팩·파우치, 경광봉·안전용품, 트로피, 비즈니스 선물세트)</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>약함(국내 행사·전시 제작 대행, 중국 거점 언급 없음)</t>
+          <t>불명(검색결과에 중국 공장/지사 언급 없음)</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>2014년 설립된 행사 진행·전시부스 제작 종합대행사로 행사용품 렌탈 사업까지 운영해 행사물품을 직접 대량 구매하는 구조이므로 중국 소싱 파트너의 원가 절감 제안이 유효하다.</t>
+          <t>USB·보조배터리 등 전자 판촉물과 가방류를 주력으로 하는 수원 소재 소규모 판촉몰로 중국 생산 의존도가 높은 품목 구성이라 소싱 파트너 활용 가능성이 있음(공개 이메일이 개인 계정 형태라 미기재).</t>
         </is>
       </c>
       <c r="M61" s="9" t="inlineStr">
         <is>
-          <t>http://www.topstandard.co.kr/ ; https://www.jobkorea.co.kr/recruit/co_read/c/topstandard</t>
+          <t>https://jgift.kr/shop/view.php?index_no=749880</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr"/>
@@ -4960,45 +4988,45 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>(주)펀잇컴퍼니(펀플랜)</t>
+          <t>판촉물천국</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>광고·BTL·행사대행사</t>
+          <t>관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>https://www.funplan.co.kr</t>
+          <t>https://giftheaven.co.kr/</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>https://www.funplan.co.kr (홈페이지 문의) ; 인스타그램 @funplan.official</t>
+          <t>https://panchokmool.co.kr/panchokmool-category/school-promotional-item/ (학교기념품 제작 카테고리)</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>행사대행, 팝업스토어, 전시, 프로모션, 오프라인 BTL 행사</t>
+          <t>학교 기념품·답례품 (USB, 보조배터리 등), 행사 판촉물</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>약함(행사대행·팝업 전문, 중국 거점 언급 없음)</t>
+          <t>불명(사이트 접근 차단으로 확인 불가)</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>팝업스토어와 전시·프로모션을 전문으로 하는 행사대행사로 팝업 집기·굿즈·사은품을 매 프로젝트마다 외주 제작해야 하므로 중국 소싱 대행 수요가 크다.</t>
+          <t>학교 기념품 전용 카테고리를 운영하며 USB·보조배터리 등 중국 생산 의존 품목을 학교 단체선물로 제안하는 업체라 중국 소싱 파트너 활용 여지가 있으나 연락처는 미확인.</t>
         </is>
       </c>
       <c r="M62" s="9" t="inlineStr">
         <is>
-          <t>https://www.funplan.co.kr/</t>
+          <t>https://giftheaven.co.kr/gift/%ED%95%99%EA%B5%90-%EA%B8%B0%EB%85%90%ED%92%88/</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr"/>
@@ -5020,7 +5048,7 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>성심코퍼레이션</t>
+          <t>(주)아이전시</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -5030,35 +5058,35 @@
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>https://www.sscomkor.com</t>
+          <t>https://iex8808.cafe24.com</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr"/>
       <c r="G63" s="5" t="inlineStr"/>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>카카오톡 채널 @성심코퍼레이션 ; https://www.sscomkor.com/aboutus</t>
+          <t>https://iex8808.cafe24.com (견적·부스문의 게시판, 네이버톡톡)</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>전시회 기획·운영, 소규모·호텔 행사, 기업행사, 독립부스, 팝업스토어 대행, 홍보월·포토존·족자봉 제작</t>
+          <t>전시부스, 학회부스, 박람회·이벤트 부스, 포토존, 블럭·패브릭 부스, 가판대·홍보·판촉 집기</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>약함(전시·행사 대행 전문, 중국 거점 언급 없음)</t>
+          <t>약함(부스 제작·설치 전문, 중국 거점 언급 없음)</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>전시회·팝업스토어·기업행사를 기획부터 설치·운영까지 일괄 대행하면서 홍보월·포토존 등 연출물을 자체 제작하므로 행사 소품·기념품의 중국 소싱 파트너가 필요하다.</t>
+          <t>전시·학회·기업행사용 부스와 판촉 집기를 제작하는 업체로 포토존·가판대·판촉물 부자재를 대량 조달하기 때문에 중국 소싱 파트너 연계 가능성이 있다.</t>
         </is>
       </c>
       <c r="M63" s="9" t="inlineStr">
         <is>
-          <t>https://www.sscomkor.com/aboutus ; https://www.sscomkor.com/shop/?idx=27</t>
+          <t>https://iex8808.cafe24.com/ ; https://iex8808.cafe24.com/category/%EA%B0%80%ED%8C%90%EB%8C%80%C2%B7%ED%99%8D%EB%B3%B4%C2%B7%ED%8C%90%EC%B4%89%C2%B7%EB%8B%A4%ED%8A%B8/53/</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr"/>
@@ -5080,7 +5108,7 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>아이스큐브(광고대행사 아이스큐브)</t>
+          <t>(주)콤마엔터테인먼트</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -5090,35 +5118,47 @@
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>https://www.icecubecom.co.kr</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr"/>
-      <c r="G64" s="5" t="inlineStr"/>
+          <t>https://www.comma-entertainment.com</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>02-6319-6947</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>info@comma-entertainment.com</t>
+        </is>
+      </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>https://www.icecubecom.co.kr (홈페이지 문의)</t>
-        </is>
-      </c>
-      <c r="I64" s="5" t="inlineStr"/>
+          <t>https://www.comma-entertainment.com/contact</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>서울 강남구</t>
+        </is>
+      </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>BTL, 신제품 런칭쇼, 팝업스토어, 팬미팅, 콘서트, 기업교육·기업문화 콘텐츠, 영상제작</t>
+          <t>이벤트·컨벤션 대행, 콘서트, 프로모션, BTL 마케팅, 옥외광고, 해외 마케팅(인바운드·아웃바운드), SNS·인플루언서</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>약함(마케팅 전문 대행사, 중국 거점 언급 없음)</t>
+          <t>약함(해외 마케팅 대행사이나 중국 공장·지사 언급 없음)</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>신제품 런칭쇼·팝업스토어·팬미팅 등 굿즈 소비가 많은 행사를 전문으로 하는 마케팅 대행사로, 자체 제조 기반이 없어 굿즈 생산 소싱 파트너의 효용이 크다.</t>
+          <t>국내 기업의 해외 마케팅과 해외 기업의 국내 행사를 대행하는 글로벌 종합광고대행사로 행사·프로모션용 굿즈를 국경 간으로 조달·배송해야 해 중국 소싱·운송 일괄 파트너가 유용하다.</t>
         </is>
       </c>
       <c r="M64" s="9" t="inlineStr">
         <is>
-          <t>https://www.icecubecom.co.kr/BUSINESS</t>
+          <t>https://www.comma-entertainment.com/contact ; https://www.comma-entertainment.com/experience</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr"/>
@@ -5140,7 +5180,7 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>애드넷</t>
+          <t>(주)크레픽스</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -5150,47 +5190,47 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>https://ad119.com</t>
+          <t>https://www.creaphics.com</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>02-831-4871</t>
+          <t>070-7604-5959</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>ad8282@hanmail.net</t>
+          <t>jin@creaphics.com</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>https://ad119.com</t>
+          <t>https://www.creaphics.com/24</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>서울 금천구</t>
+          <t>서울 구로구</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>친환경 전시부스 제작, 행사·컨퍼런스 디스플레이, 포토존, 배너거치대, 진열대, 인쇄·홍보물</t>
+          <t>BTL 광고, 행사 대행, 프로모션, 광고물 제작</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>약함(전시부스·디스플레이 제작 전문, 중국 거점 언급 없음)</t>
+          <t>약함(소규모 BTL 대행사, 자체 해외 거점 언급 없음)</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>전시부스와 배너거치대·진열대 등 행사 디스플레이 용품을 판매·제작하는 업체로 표준 행사물품을 중국에서 저가 소싱해 마진을 개선할 수요가 있다.</t>
+          <t>효율성을 내세우는 소형 BTL 광고회사로 자체 제작 인프라가 없어 행사 판촉물·굿즈를 저비용으로 조달해 줄 외부 소싱 파트너가 필요하다.</t>
         </is>
       </c>
       <c r="M65" s="9" t="inlineStr">
         <is>
-          <t>https://ad119.com/ ; https://ad119.com/55/?idx=115</t>
+          <t>https://www.creaphics.com/24</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr"/>
@@ -5212,7 +5252,7 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>이상기획</t>
+          <t>(주)탑스탠다드</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -5222,35 +5262,39 @@
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>https://www.mothid.com</t>
+          <t>http://www.topstandard.co.kr</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr"/>
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>https://www.mothid.com/promotion (홈페이지 문의)</t>
-        </is>
-      </c>
-      <c r="I66" s="5" t="inlineStr"/>
+          <t>http://www.topstandard.co.kr (홈페이지 문의)</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>경기 광명시</t>
+        </is>
+      </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>기업행사, 공모전, 제품설명회, 쇼케이스, 프로모션·BTL 대행, 컨벤션, 전시회·박람회, 팝업스토어</t>
+          <t>행사 진행 대행, 전시부스 제작·설치, 심포지엄·컨퍼런스·세미나, 기업행사, 행사용품 렌탈(탑렌탈)</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>약함(행사·프로모션 대행 전문, 중국 거점 언급 없음)</t>
+          <t>약함(국내 행사·전시 제작 대행, 중국 거점 언급 없음)</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>제품설명회·쇼케이스·팝업스토어 등 다양한 기업행사를 대행하는 기획사로 행사별 맞춤 굿즈·판촉물을 외주로 조달해야 해 샘플부터 검수·운송까지 맡길 파트너가 필요하다.</t>
+          <t>2014년 설립된 행사 진행·전시부스 제작 종합대행사로 행사용품 렌탈 사업까지 운영해 행사물품을 직접 대량 구매하는 구조이므로 중국 소싱 파트너의 원가 절감 제안이 유효하다.</t>
         </is>
       </c>
       <c r="M66" s="9" t="inlineStr">
         <is>
-          <t>https://www.mothid.com/promotion</t>
+          <t>http://www.topstandard.co.kr/ ; https://www.jobkorea.co.kr/recruit/co_read/c/topstandard</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr"/>
@@ -5272,7 +5316,7 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>플레이스컴(PLACECOM)</t>
+          <t>(주)펀잇컴퍼니(펀플랜)</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -5282,35 +5326,35 @@
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>https://www.placecom.co.kr</t>
+          <t>https://www.funplan.co.kr</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr"/>
       <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>https://www.placecom.co.kr/%ED%9A%8C%EC%82%AC%EC%86%8C%EA%B0%9C (홈페이지 문의)</t>
+          <t>https://www.funplan.co.kr (홈페이지 문의) ; 인스타그램 @funplan.official</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>팝업스토어 기획·제작·운영, 팝업스토어 장소 대관(광화문·청계광장 등), BTL 프로모션</t>
+          <t>행사대행, 팝업스토어, 전시, 프로모션, 오프라인 BTL 행사</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>약함(팝업스토어 제작·운영 전문, 중국 거점 언급 없음)</t>
+          <t>약함(행사대행·팝업 전문, 중국 거점 언급 없음)</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>팝업스토어 장소 대관과 제작·운영을 함께 하는 BTL 전문사로 팝업마다 집기·굿즈·사은품을 새로 제작해야 하므로 중국 소싱·생산 대행 파트너 수요가 지속적이다.</t>
+          <t>팝업스토어와 전시·프로모션을 전문으로 하는 행사대행사로 팝업 집기·굿즈·사은품을 매 프로젝트마다 외주 제작해야 하므로 중국 소싱 대행 수요가 크다.</t>
         </is>
       </c>
       <c r="M67" s="9" t="inlineStr">
         <is>
-          <t>https://www.placecom.co.kr/%ED%9A%8C%EC%82%AC%EC%86%8C%EA%B0%9C</t>
+          <t>https://www.funplan.co.kr/</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr"/>
@@ -5332,45 +5376,45 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>순풍</t>
+          <t>성심코퍼레이션</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>무역·소싱대행·수입도매</t>
+          <t>광고·BTL·행사대행사</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>https://soonfung.com</t>
+          <t>https://www.sscomkor.com</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr"/>
       <c r="G68" s="5" t="inlineStr"/>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>https://soonfung.com/</t>
+          <t>카카오톡 채널 @성심코퍼레이션 ; https://www.sscomkor.com/aboutus</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>중국구매대행, OEM·ODM, 배송대행(배대지), 병행수입, 도매</t>
+          <t>전시회 기획·운영, 소규모·호텔 행사, 기업행사, 독립부스, 팝업스토어 대행, 홍보월·포토존·족자봉 제작</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>불명(구매대행·배대지 운영 표방, 자체 공장 여부 미확인)</t>
+          <t>약함(전시·행사 대행 전문, 중국 거점 언급 없음)</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>구매대행·배대지 중심 소규모 업체로 OEM 공장 수배는 외부 제조 파트너와 협업할 가능성이 있다.</t>
+          <t>전시회·팝업스토어·기업행사를 기획부터 설치·운영까지 일괄 대행하면서 홍보월·포토존 등 연출물을 자체 제작하므로 행사 소품·기념품의 중국 소싱 파트너가 필요하다.</t>
         </is>
       </c>
       <c r="M68" s="9" t="inlineStr">
         <is>
-          <t>https://soonfung.com/</t>
+          <t>https://www.sscomkor.com/aboutus ; https://www.sscomkor.com/shop/?idx=27</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr"/>
@@ -5392,53 +5436,45 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>차이나바이((주)융일)</t>
+          <t>아이스큐브(광고대행사 아이스큐브)</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>무역·소싱대행·수입도매</t>
+          <t>광고·BTL·행사대행사</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>https://www.chinabuy.co.kr</t>
-        </is>
-      </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>070-8682-6565</t>
-        </is>
-      </c>
+          <t>https://www.icecubecom.co.kr</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr"/>
       <c r="G69" s="5" t="inlineStr"/>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>https://chinabuy.off.co.kr/board/list?bname=notice</t>
-        </is>
-      </c>
-      <c r="I69" s="5" t="inlineStr">
-        <is>
-          <t>서울 강남구</t>
-        </is>
-      </c>
+          <t>https://www.icecubecom.co.kr (홈페이지 문의)</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>중국구매대행(알리바바·1688·타오바오), 배송대행</t>
+          <t>BTL, 신제품 런칭쇼, 팝업스토어, 팬미팅, 콘서트, 기업교육·기업문화 콘텐츠, 영상제작</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>불명(B2C 구매·배송대행 중심, 자체 공장·지사 여부 미확인)</t>
+          <t>약함(마케팅 전문 대행사, 중국 거점 언급 없음)</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>개인 구매대행 위주라 OEM·대량 공장 소싱 의뢰가 들어올 때 외부 파트너와 협업할 여지가 있다.</t>
+          <t>신제품 런칭쇼·팝업스토어·팬미팅 등 굿즈 소비가 많은 행사를 전문으로 하는 마케팅 대행사로, 자체 제조 기반이 없어 굿즈 생산 소싱 파트너의 효용이 크다.</t>
         </is>
       </c>
       <c r="M69" s="9" t="inlineStr">
         <is>
-          <t>https://www.chinabuy.co.kr/</t>
+          <t>https://www.icecubecom.co.kr/BUSINESS</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr"/>
@@ -5460,45 +5496,57 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>(주)대연이엔티 (B2B 스포츠 도매몰)</t>
+          <t>애드넷</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>스포츠·헬스·재활용품 유통사/OEM브랜드</t>
+          <t>광고·BTL·행사대행사</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>https://www.dy-sports.com</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="inlineStr"/>
-      <c r="G70" s="5" t="inlineStr"/>
+          <t>https://ad119.com</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>02-831-4871</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>ad8282@hanmail.net</t>
+        </is>
+      </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>https://www.dy-sports.com</t>
-        </is>
-      </c>
-      <c r="I70" s="5" t="inlineStr"/>
+          <t>https://ad119.com</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>서울 금천구</t>
+        </is>
+      </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>스포츠용품 B2B 도매 (온라인 셀러 대상)</t>
+          <t>친환경 전시부스 제작, 행사·컨퍼런스 디스플레이, 포토존, 배너거치대, 진열대, 인쇄·홍보물</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>불명(B2B 도매몰, 제조 정보 미확인)</t>
+          <t>약함(전시부스·디스플레이 제작 전문, 중국 거점 언급 없음)</t>
         </is>
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>온라인 셀러 대상 스포츠용품 B2B 도매몰로 보호대·헬스소도구 공급 벤더 확보 수요가 있음.</t>
+          <t>전시부스와 배너거치대·진열대 등 행사 디스플레이 용품을 판매·제작하는 업체로 표준 행사물품을 중국에서 저가 소싱해 마진을 개선할 수요가 있다.</t>
         </is>
       </c>
       <c r="M70" s="9" t="inlineStr">
         <is>
-          <t>https://www.dy-sports.com/</t>
+          <t>https://ad119.com/ ; https://ad119.com/55/?idx=115</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr"/>
@@ -5520,57 +5568,45 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>(주)대호스포츠</t>
+          <t>이상기획</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>스포츠·헬스·재활용품 유통사/OEM브랜드</t>
+          <t>광고·BTL·행사대행사</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>https://daehosports.com</t>
-        </is>
-      </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>042-525-6939</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>daehosports@naver.com</t>
-        </is>
-      </c>
+          <t>https://www.mothid.com</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr"/>
+      <c r="G71" s="5" t="inlineStr"/>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>https://daehosports.com</t>
-        </is>
-      </c>
-      <c r="I71" s="5" t="inlineStr">
-        <is>
-          <t>대전광역시</t>
-        </is>
-      </c>
+          <t>https://www.mothid.com/promotion (홈페이지 문의)</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr"/>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>헬스기구·케틀벨·헬스 소도구, 헬스장 납품 전문</t>
+          <t>기업행사, 공모전, 제품설명회, 쇼케이스, 프로모션·BTL 대행, 컨벤션, 전시회·박람회, 팝업스토어</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>불명(헬스기구 납품 전문사, 제조 정보 미확인)</t>
+          <t>약함(행사·프로모션 대행 전문, 중국 거점 언급 없음)</t>
         </is>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>대전 기반 헬스장 납품 전문사로 헬스장 부자재(보호대·밴드·매트) 소싱 파트너가 필요할 수 있음.</t>
+          <t>제품설명회·쇼케이스·팝업스토어 등 다양한 기업행사를 대행하는 기획사로 행사별 맞춤 굿즈·판촉물을 외주로 조달해야 해 샘플부터 검수·운송까지 맡길 파트너가 필요하다.</t>
         </is>
       </c>
       <c r="M71" s="9" t="inlineStr">
         <is>
-          <t>https://daehosports.com/</t>
+          <t>https://www.mothid.com/promotion</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr"/>
@@ -5592,57 +5628,45 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>(주)스포틀러 (SPORTLER)</t>
+          <t>플레이스컴(PLACECOM)</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>스포츠·헬스·재활용품 유통사/OEM브랜드</t>
+          <t>광고·BTL·행사대행사</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>https://sportler.co.kr</t>
-        </is>
-      </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>1670-7933</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>iwhasmp@gmail.com</t>
-        </is>
-      </c>
+          <t>https://www.placecom.co.kr</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr"/>
+      <c r="G72" s="5" t="inlineStr"/>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>https://www.sportler.co.kr/service/index.php</t>
-        </is>
-      </c>
-      <c r="I72" s="5" t="inlineStr">
-        <is>
-          <t>서울 서초구</t>
-        </is>
-      </c>
+          <t>https://www.placecom.co.kr/%ED%9A%8C%EC%82%AC%EC%86%8C%EA%B0%9C (홈페이지 문의)</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr"/>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>홈트 운동기구·요가매트·헬스소도구 (자체 브랜드 직영몰, G마켓·옥션 입점)</t>
+          <t>팝업스토어 기획·제작·운영, 팝업스토어 장소 대관(광화문·청계광장 등), BTL 프로모션</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>불명(온라인 직영 브랜드, 제조처 미공개)</t>
+          <t>약함(팝업스토어 제작·운영 전문, 중국 거점 언급 없음)</t>
         </is>
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>홈트 운동기구를 자체 브랜드로 온라인 유통하는 업체로 보호대·소도구 등 신규 품목 소싱 파트너로 접근 가능함.</t>
+          <t>팝업스토어 장소 대관과 제작·운영을 함께 하는 BTL 전문사로 팝업마다 집기·굿즈·사은품을 새로 제작해야 하므로 중국 소싱·생산 대행 파트너 수요가 지속적이다.</t>
         </is>
       </c>
       <c r="M72" s="9" t="inlineStr">
         <is>
-          <t>https://sportler.co.kr/member/privacy.html</t>
+          <t>https://www.placecom.co.kr/%ED%9A%8C%EC%82%AC%EC%86%8C%EA%B0%9C</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr"/>
@@ -5664,53 +5688,45 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>(주)엠서클 (시셀코리아 SISSEL)</t>
+          <t>순풍</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>스포츠·헬스·재활용품 유통사/OEM브랜드</t>
+          <t>무역·소싱대행·수입도매</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>https://sisselkorea.com</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>1899-3646</t>
-        </is>
-      </c>
+          <t>https://soonfung.com</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr"/>
       <c r="G73" s="5" t="inlineStr"/>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>https://store.kakao.com/sisselkorea (카카오톡 상담)</t>
-        </is>
-      </c>
-      <c r="I73" s="5" t="inlineStr">
-        <is>
-          <t>서울 강남구</t>
-        </is>
-      </c>
+          <t>https://soonfung.com/</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>폼롤러·마사지볼·짐볼·운동밴드·운동방석·정형베개 (스웨덴 시셀 공식 수입, 코스트코 입점)</t>
+          <t>중국구매대행, OEM·ODM, 배송대행(배대지), 병행수입, 도매</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>약함(해외 브랜드 수입 총판, 자체 공장 없음)</t>
+          <t>불명(구매대행·배대지 운영 표방, 자체 공장 여부 미확인)</t>
         </is>
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>시셀 수입 총판이라 핵심 품목은 본사 공급이나 보완 품목(보호대 등) PB 개발 시 중국 OEM 파트너가 필요할 수 있음.</t>
+          <t>구매대행·배대지 중심 소규모 업체로 OEM 공장 수배는 외부 제조 파트너와 협업할 가능성이 있다.</t>
         </is>
       </c>
       <c r="M73" s="9" t="inlineStr">
         <is>
-          <t>https://sisselkorea.com/about.html</t>
+          <t>https://soonfung.com/</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr"/>
@@ -5732,49 +5748,53 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>고핏코리아 (GOFITKOREA)</t>
+          <t>차이나바이((주)융일)</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>스포츠·헬스·재활용품 유통사/OEM브랜드</t>
+          <t>무역·소싱대행·수입도매</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>https://gofitkorea.com</t>
+          <t>https://www.chinabuy.co.kr</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>1833-3745</t>
+          <t>070-8682-6565</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr"/>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>https://gofitkorea.com</t>
-        </is>
-      </c>
-      <c r="I74" s="5" t="inlineStr"/>
+          <t>https://chinabuy.off.co.kr/board/list?bname=notice</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>서울 강남구</t>
+        </is>
+      </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>헬스기구·덤벨·헬스소도구, 헬스장 창업·기업·관공서·아파트 납품 및 피트니스 인테리어</t>
+          <t>중국구매대행(알리바바·1688·타오바오), 배송대행</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>불명(헬스기구 유통·납품 전문, 제조 정보 미확인)</t>
+          <t>불명(B2C 구매·배송대행 중심, 자체 공장·지사 여부 미확인)</t>
         </is>
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>헬스장 창업·관공서 납품 전문 유통사로 소도구·보호대 등 부자재 일괄 소싱 파트너가 필요할 수 있음.</t>
+          <t>개인 구매대행 위주라 OEM·대량 공장 소싱 의뢰가 들어올 때 외부 파트너와 협업할 여지가 있다.</t>
         </is>
       </c>
       <c r="M74" s="9" t="inlineStr">
         <is>
-          <t>https://gofitkorea.com/</t>
+          <t>https://www.chinabuy.co.kr/</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr"/>
@@ -5796,57 +5816,53 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>다산메디칼 (닥터엠알오)</t>
+          <t>기프트앤돌</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>스포츠·헬스·재활용품 유통사/OEM브랜드</t>
+          <t>소규모 판촉물·패키징 중개벤더</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>https://drmro.com</t>
+          <t>https://giftanddoll.co.kr</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>070-7095-9512</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>dasanmd@hanmail.net</t>
-        </is>
-      </c>
+          <t>031-848-2073</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr"/>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>https://drmro.com</t>
+          <t>https://giftanddoll.co.kr/board/%EA%B0%A4%EB%9F%AC%EB%A6%AC/8/</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>경기도 용인시 기흥구</t>
+          <t>경기 양주시</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>병의원용 의료소모품·진료재료·장비 5천여 종 도소매 유통</t>
+          <t>캐릭터 인형·아이돌 인형·봉제 굿즈 주문제작</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
-          <t>약함(의료소모품 유통 전문, 자체 공장 없음)</t>
+          <t>불명 — 중국 공장 관련 언급 확인 안 됨</t>
         </is>
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>병의원 대상 의료소모품 종합 유통사로 보호대·재활 소모품 PB 소싱 시 중국 OEM 파트너가 필요함.</t>
+          <t>기업·엔터사 대상 캐릭터 인형 굿즈 주문제작 소규모 법인으로 봉제 OEM 중국 소싱 협업 가능.</t>
         </is>
       </c>
       <c r="M75" s="9" t="inlineStr">
         <is>
-          <t>https://drmro.com/</t>
+          <t>https://giftanddoll.co.kr/</t>
         </is>
       </c>
       <c r="N75" s="7" t="inlineStr"/>
@@ -5868,7 +5884,7 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>더미통상 (서울종로의료기)</t>
+          <t>(주)대연이엔티 (B2B 스포츠 도매몰)</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -5878,47 +5894,35 @@
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>https://jongromedi.com</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>02-2275-1478</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>habin0929@naver.com</t>
-        </is>
-      </c>
+          <t>https://www.dy-sports.com</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr"/>
+      <c r="G76" s="5" t="inlineStr"/>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>https://jongromedi.com</t>
-        </is>
-      </c>
-      <c r="I76" s="5" t="inlineStr">
-        <is>
-          <t>서울 중구</t>
-        </is>
-      </c>
+          <t>https://www.dy-sports.com</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr"/>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>무릎·손목·허리 보호대, 병원용품, 재활운동 용품, 의료용 산소, 안마기 (관공서·병원 납품 실적)</t>
+          <t>스포츠용품 B2B 도매 (온라인 셀러 대상)</t>
         </is>
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
-          <t>약함(의료기기 유통 전문, 자체 공장 없음)</t>
+          <t>불명(B2B 도매몰, 제조 정보 미확인)</t>
         </is>
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>종로 40년 의료기 유통사로 보호대 카테고리를 다수 취급해 가격 경쟁력 있는 OEM 보호대 공급처를 필요로 할 가능성이 있음.</t>
+          <t>온라인 셀러 대상 스포츠용품 B2B 도매몰로 보호대·헬스소도구 공급 벤더 확보 수요가 있음.</t>
         </is>
       </c>
       <c r="M76" s="9" t="inlineStr">
         <is>
-          <t>https://jongromedi.com</t>
+          <t>https://www.dy-sports.com/</t>
         </is>
       </c>
       <c r="N76" s="7" t="inlineStr"/>
@@ -5940,7 +5944,7 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>동화스포츠</t>
+          <t>(주)대호스포츠</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -5950,39 +5954,47 @@
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>https://www.donghwasports.net</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="inlineStr"/>
-      <c r="G77" s="5" t="inlineStr"/>
+          <t>https://daehosports.com</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>042-525-6939</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>daehosports@naver.com</t>
+        </is>
+      </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>https://www.donghwasports.net / 010 번호만 공개</t>
+          <t>https://daehosports.com</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>부산광역시 강서구</t>
+          <t>대전광역시</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>라텍스밴드·운동밴드·요가매트·짐볼·폼롤러 등 헬스기구·운동용품</t>
+          <t>헬스기구·케틀벨·헬스 소도구, 헬스장 납품 전문</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
-          <t>불명(헬스용품 유통사, 제조 정보 미확인)</t>
+          <t>불명(헬스기구 납품 전문사, 제조 정보 미확인)</t>
         </is>
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>밴드·매트·짐볼·폼롤러 등 중국 OEM 의존도가 높은 헬스 소도구를 폭넓게 취급하는 유통사임.</t>
+          <t>대전 기반 헬스장 납품 전문사로 헬스장 부자재(보호대·밴드·매트) 소싱 파트너가 필요할 수 있음.</t>
         </is>
       </c>
       <c r="M77" s="9" t="inlineStr">
         <is>
-          <t>https://www.donghwasports.net/</t>
+          <t>https://daehosports.com/</t>
         </is>
       </c>
       <c r="N77" s="7" t="inlineStr"/>
@@ -6004,7 +6016,7 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>메디세일 (MEDISALE)</t>
+          <t>(주)스포틀러 (SPORTLER)</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -6014,39 +6026,47 @@
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>https://medisale.co.kr</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr"/>
+          <t>https://sportler.co.kr</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>1670-7933</t>
+        </is>
+      </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>medisale@inot-meditech.com</t>
+          <t>iwhasmp@gmail.com</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>https://medisale.co.kr</t>
-        </is>
-      </c>
-      <c r="I78" s="5" t="inlineStr"/>
+          <t>https://www.sportler.co.kr/service/index.php</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>서울 서초구</t>
+        </is>
+      </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>의료기기·의료소모품 기업 전용 B2B 도매몰</t>
+          <t>홈트 운동기구·요가매트·헬스소도구 (자체 브랜드 직영몰, G마켓·옥션 입점)</t>
         </is>
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
-          <t>약함(B2B 의료소모품 도매, 자체 공장 없음)</t>
+          <t>불명(온라인 직영 브랜드, 제조처 미공개)</t>
         </is>
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>병원·약국 대상 의료소모품 B2B 도매몰로 보호대 등 소모품 라인업 확충 시 OEM 공급처가 필요함.</t>
+          <t>홈트 운동기구를 자체 브랜드로 온라인 유통하는 업체로 보호대·소도구 등 신규 품목 소싱 파트너로 접근 가능함.</t>
         </is>
       </c>
       <c r="M78" s="9" t="inlineStr">
         <is>
-          <t>https://medisale.co.kr/</t>
+          <t>https://sportler.co.kr/member/privacy.html</t>
         </is>
       </c>
       <c r="N78" s="7" t="inlineStr"/>
@@ -6068,7 +6088,7 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>빅사이트 (필라모아 PILAMOA)</t>
+          <t>(주)엠서클 (시셀코리아 SISSEL)</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -6078,18 +6098,18 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>https://pilamoa.com</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr"/>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>jaseatoz@naver.com</t>
-        </is>
-      </c>
+          <t>https://sisselkorea.com</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>1899-3646</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr"/>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>https://pilamoa.com</t>
+          <t>https://store.kakao.com/sisselkorea (카카오톡 상담)</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
@@ -6099,22 +6119,22 @@
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>필라테스 기구(리포머·캐포머)·소도구·미니폼롤러·센터운영 용품 (필라테스 센터 납품 전문몰)</t>
+          <t>폼롤러·마사지볼·짐볼·운동밴드·운동방석·정형베개 (스웨덴 시셀 공식 수입, 코스트코 입점)</t>
         </is>
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
-          <t>약함(필라테스 전문 유통몰, 자체 공장 없음)</t>
+          <t>약함(해외 브랜드 수입 총판, 자체 공장 없음)</t>
         </is>
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>필라테스 센터 대상 토탈 납품몰로 소도구·보호대 PB 확장 시 중국 OEM 소싱 파트너가 필요함 (사이트 게시 연락처가 휴대전화라 대표전화는 미기재).</t>
+          <t>시셀 수입 총판이라 핵심 품목은 본사 공급이나 보완 품목(보호대 등) PB 개발 시 중국 OEM 파트너가 필요할 수 있음.</t>
         </is>
       </c>
       <c r="M79" s="9" t="inlineStr">
         <is>
-          <t>https://pilamoa.com</t>
+          <t>https://sisselkorea.com/about.html</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr"/>
@@ -6136,7 +6156,7 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>스포플 (SPOFL)</t>
+          <t>고핏코리아 (GOFITKOREA)</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -6146,35 +6166,39 @@
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>https://spofl.co.kr</t>
-        </is>
-      </c>
-      <c r="F80" s="5" t="inlineStr"/>
+          <t>https://gofitkorea.com</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>1833-3745</t>
+        </is>
+      </c>
       <c r="G80" s="5" t="inlineStr"/>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_GVrxlK (카카오톡 채널)</t>
+          <t>https://gofitkorea.com</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr"/>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>폼롤러·마사지기·운동밴드·헬스케어 및 스포츠 브랜드 편집 플랫폼</t>
+          <t>헬스기구·덤벨·헬스소도구, 헬스장 창업·기업·관공서·아파트 납품 및 피트니스 인테리어</t>
         </is>
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
-          <t>불명(브랜드 유통 플랫폼, 제조 정보 미확인)</t>
+          <t>불명(헬스기구 유통·납품 전문, 제조 정보 미확인)</t>
         </is>
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>다수 스포츠·헬스케어 브랜드를 유통하는 온라인 플랫폼으로 PB 소도구·보호대 개발 시 외부 OEM 파트너 수요 가능성이 있음.</t>
+          <t>헬스장 창업·관공서 납품 전문 유통사로 소도구·보호대 등 부자재 일괄 소싱 파트너가 필요할 수 있음.</t>
         </is>
       </c>
       <c r="M80" s="9" t="inlineStr">
         <is>
-          <t>https://spofl.co.kr/board/faq/3/</t>
+          <t>https://gofitkorea.com/</t>
         </is>
       </c>
       <c r="N80" s="7" t="inlineStr"/>
@@ -6196,7 +6220,7 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>에스앤에스 (파워플러스몰)</t>
+          <t>다산메디칼 (닥터엠알오)</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -6206,35 +6230,47 @@
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>http://sns3524.godomall.com</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr"/>
-      <c r="G81" s="5" t="inlineStr"/>
+          <t>https://drmro.com</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>070-7095-9512</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>dasanmd@hanmail.net</t>
+        </is>
+      </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>http://sns3524.godomall.com/main/index.php?pcView=y</t>
-        </is>
-      </c>
-      <c r="I81" s="5" t="inlineStr"/>
+          <t>https://drmro.com</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>경기도 용인시 기흥구</t>
+        </is>
+      </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>의료용 관절보호대 제조·유통 (자체 브랜드 파워플러스·스포라이트·웰팜스)</t>
+          <t>병의원용 의료소모품·진료재료·장비 5천여 종 도소매 유통</t>
         </is>
       </c>
       <c r="K81" s="5" t="inlineStr">
         <is>
-          <t>불명(제조·유통 전문사로 소개되나 공장 소재지 미확인)</t>
+          <t>약함(의료소모품 유통 전문, 자체 공장 없음)</t>
         </is>
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>복수의 보호대 브랜드를 운영하는 관절보호대 전문 제조·유통사로 품목 보완용 중국 OEM 협업 여지가 있으나 자체 제조 가능성이 있어 경쟁 관계일 수 있음.</t>
+          <t>병의원 대상 의료소모품 종합 유통사로 보호대·재활 소모품 PB 소싱 시 중국 OEM 파트너가 필요함.</t>
         </is>
       </c>
       <c r="M81" s="9" t="inlineStr">
         <is>
-          <t>http://sns3524.godomall.com/main/index.php?pcView=y</t>
+          <t>https://drmro.com/</t>
         </is>
       </c>
       <c r="N81" s="7" t="inlineStr"/>
@@ -6256,7 +6292,7 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>트라택 (TRATAC)</t>
+          <t>더미통상 (서울종로의료기)</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -6266,35 +6302,47 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>https://tratac.co.kr</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="inlineStr"/>
-      <c r="G82" s="5" t="inlineStr"/>
+          <t>https://jongromedi.com</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>02-2275-1478</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>habin0929@naver.com</t>
+        </is>
+      </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>https://tratac.co.kr</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr"/>
+          <t>https://jongromedi.com</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>서울 중구</t>
+        </is>
+      </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>세라밴드 등 재활·헬스케어 운동용품 (헬스케어 플랫폼)</t>
+          <t>무릎·손목·허리 보호대, 병원용품, 재활운동 용품, 의료용 산소, 안마기 (관공서·병원 납품 실적)</t>
         </is>
       </c>
       <c r="K82" s="5" t="inlineStr">
         <is>
-          <t>불명(헬스케어 유통 플랫폼, 제조 정보 미확인)</t>
+          <t>약함(의료기기 유통 전문, 자체 공장 없음)</t>
         </is>
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>재활·헬스케어 용품 플랫폼으로 물리치료실·재활센터 납품용 보호대·밴드 OEM 공급처가 필요할 수 있음.</t>
+          <t>종로 40년 의료기 유통사로 보호대 카테고리를 다수 취급해 가격 경쟁력 있는 OEM 보호대 공급처를 필요로 할 가능성이 있음.</t>
         </is>
       </c>
       <c r="M82" s="9" t="inlineStr">
         <is>
-          <t>https://tratac.co.kr/shop/prd_list.php?catcode=161100</t>
+          <t>https://jongromedi.com</t>
         </is>
       </c>
       <c r="N82" s="7" t="inlineStr"/>
@@ -6316,7 +6364,7 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>하라스포츠</t>
+          <t>동화스포츠</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -6326,47 +6374,39 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>https://harasports.net</t>
-        </is>
-      </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>063-462-6300</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>hhhh4076@naver.com</t>
-        </is>
-      </c>
+          <t>https://www.donghwasports.net</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr"/>
+      <c r="G83" s="5" t="inlineStr"/>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>https://harasports.net</t>
+          <t>https://www.donghwasports.net / 010 번호만 공개</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>전북특별자치도 군산시</t>
+          <t>부산광역시 강서구</t>
         </is>
       </c>
       <c r="J83" s="5" t="inlineStr">
         <is>
-          <t>원판·아령·바벨봉·케틀벨·메디슨볼·폼롤러·요가매트 등 헬스 소도구 85종</t>
+          <t>라텍스밴드·운동밴드·요가매트·짐볼·폼롤러 등 헬스기구·운동용품</t>
         </is>
       </c>
       <c r="K83" s="5" t="inlineStr">
         <is>
-          <t>불명(헬스 소도구 유통, 제조 정보 미확인)</t>
+          <t>불명(헬스용품 유통사, 제조 정보 미확인)</t>
         </is>
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>헬스 소도구 전 품목을 취급하는 유통사로 보호대·소도구 신규 소싱 파트너로 접근 가능함.</t>
+          <t>밴드·매트·짐볼·폼롤러 등 중국 OEM 의존도가 높은 헬스 소도구를 폭넓게 취급하는 유통사임.</t>
         </is>
       </c>
       <c r="M83" s="9" t="inlineStr">
         <is>
-          <t>https://harasports.net/</t>
+          <t>https://www.donghwasports.net/</t>
         </is>
       </c>
       <c r="N83" s="7" t="inlineStr"/>
@@ -6388,45 +6428,49 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>O-SEAN(런투더퓨처랩스)</t>
+          <t>메디세일 (MEDISALE)</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>캐릭터·IP·팬굿즈 기획사</t>
+          <t>스포츠·헬스·재활용품 유통사/OEM브랜드</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>https://o-sean.io/</t>
+          <t>https://medisale.co.kr</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr"/>
-      <c r="G84" s="5" t="inlineStr"/>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>medisale@inot-meditech.com</t>
+        </is>
+      </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>https://o-sean.io/ (견적 문의·1:1 상담 폼)</t>
+          <t>https://medisale.co.kr</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr"/>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>게임·엔터 IP 피규어 키링, 아크릴 키링·뱃지, 에코백·파우치, 텀블러, 문구, 디지털 굿즈(MOQ 50~100개)</t>
+          <t>의료기기·의료소모품 기업 전용 B2B 도매몰</t>
         </is>
       </c>
       <c r="K84" s="5" t="inlineStr">
         <is>
-          <t>약함(자체 생산 라인 보유 표기, 중국 거점 언급 없음)</t>
+          <t>약함(B2B 의료소모품 도매, 자체 공장 없음)</t>
         </is>
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>게임·엔터 IP용 피규어 키링을 MOQ 100개·4주로 제작하는 스타트업으로 소량 다품종 생산을 위한 중국 소싱 파트너가 보완적으로 필요할 수 있다.</t>
+          <t>병원·약국 대상 의료소모품 B2B 도매몰로 보호대 등 소모품 라인업 확충 시 OEM 공급처가 필요함.</t>
         </is>
       </c>
       <c r="M84" s="9" t="inlineStr">
         <is>
-          <t>https://o-sean.io/about ; https://o-sean.io/category/item/LS-023</t>
+          <t>https://medisale.co.kr/</t>
         </is>
       </c>
       <c r="N84" s="7" t="inlineStr"/>
@@ -6448,57 +6492,53 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>굿즈나라(헤세드하우스)</t>
+          <t>빅사이트 (필라모아 PILAMOA)</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>캐릭터·IP·팬굿즈 기획사</t>
+          <t>스포츠·헬스·재활용품 유통사/OEM브랜드</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>https://goodsnara.com/</t>
-        </is>
-      </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>031-994-7740</t>
-        </is>
-      </c>
+          <t>https://pilamoa.com</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr"/>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>hesedhouse2@naver.com</t>
+          <t>jaseatoz@naver.com</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>https://goodsnara.com/form (굿즈 디자인 폼), 카카오톡 채널(24시간 문의)</t>
+          <t>https://pilamoa.com</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구</t>
+          <t>서울 강남구</t>
         </is>
       </c>
       <c r="J85" s="5" t="inlineStr">
         <is>
-          <t>KPOP 아이돌 팬굿즈(슬로건, 이미지피켓, 반사 포토슬로건), 캔텀블러, 보조배터리, 기념품</t>
+          <t>필라테스 기구(리포머·캐포머)·소도구·미니폼롤러·센터운영 용품 (필라테스 센터 납품 전문몰)</t>
         </is>
       </c>
       <c r="K85" s="5" t="inlineStr">
         <is>
-          <t>불명(홈페이지에 생산 거점·중국 공장 언급 없음)</t>
+          <t>약함(필라테스 전문 유통몰, 자체 공장 없음)</t>
         </is>
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>아이돌 팬덤 대상 응원 굿즈·잡화를 기획 제작하는 소규모 업체로 텀블러·배터리 등 공산품은 외부 소싱이 필요해 중국 파트너 수요가 있을 수 있다.</t>
+          <t>필라테스 센터 대상 토탈 납품몰로 소도구·보호대 PB 확장 시 중국 OEM 소싱 파트너가 필요함 (사이트 게시 연락처가 휴대전화라 대표전화는 미기재).</t>
         </is>
       </c>
       <c r="M85" s="9" t="inlineStr">
         <is>
-          <t>https://goodsnara.com/ ; https://goodsnara.com/form</t>
+          <t>https://pilamoa.com</t>
         </is>
       </c>
       <c r="N85" s="7" t="inlineStr"/>
@@ -6520,57 +6560,45 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>스마일웍스</t>
+          <t>스포플 (SPOFL)</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>캐릭터·IP·팬굿즈 기획사</t>
+          <t>스포츠·헬스·재활용품 유통사/OEM브랜드</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>http://www.smileworks.co.kr/</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>02-2675-8755</t>
-        </is>
-      </c>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t>moon@smileworks.co.kr</t>
-        </is>
-      </c>
+          <t>https://spofl.co.kr</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr"/>
+      <c r="G86" s="5" t="inlineStr"/>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>http://www.smileworks.co.kr/default/online/sub1.php (온라인 문의)</t>
-        </is>
-      </c>
-      <c r="I86" s="5" t="inlineStr">
-        <is>
-          <t>서울 영등포구</t>
-        </is>
-      </c>
+          <t>https://pf.kakao.com/_GVrxlK (카카오톡 채널)</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr"/>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>봉제인형, 사출 피규어, 웹소설·연예인·캐릭터 굿즈, 스트레스볼 등 기타 굿즈</t>
+          <t>폼롤러·마사지기·운동밴드·헬스케어 및 스포츠 브랜드 편집 플랫폼</t>
         </is>
       </c>
       <c r="K86" s="5" t="inlineStr">
         <is>
-          <t>불명(국내·국외 패턴 개발실 운영 표기, 해외 거점 국가·공장 미공개)</t>
+          <t>불명(브랜드 유통 플랫폼, 제조 정보 미확인)</t>
         </is>
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>봉제인형에서 사출 피규어·잡화까지 품목이 넓어 자체 개발실 외 양산 공장 다변화 시 중국 소싱 파트너가 도움이 될 수 있다.</t>
+          <t>다수 스포츠·헬스케어 브랜드를 유통하는 온라인 플랫폼으로 PB 소도구·보호대 개발 시 외부 OEM 파트너 수요 가능성이 있음.</t>
         </is>
       </c>
       <c r="M86" s="9" t="inlineStr">
         <is>
-          <t>http://www.smileworks.co.kr/default/work/sub1.php ; http://www.smileworks.co.kr/default/work/sub2.php</t>
+          <t>https://spofl.co.kr/board/faq/3/</t>
         </is>
       </c>
       <c r="N86" s="7" t="inlineStr"/>
@@ -6592,57 +6620,45 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>시나브로(토이웍스 인형사업부)</t>
+          <t>에스앤에스 (파워플러스몰)</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>캐릭터·IP·팬굿즈 기획사</t>
+          <t>스포츠·헬스·재활용품 유통사/OEM브랜드</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>https://www.toyworks.kr/</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>032-554-9954</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t>toyworks@daum.net</t>
-        </is>
-      </c>
+          <t>http://sns3524.godomall.com</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr"/>
+      <c r="G87" s="5" t="inlineStr"/>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>https://www.toyworks.kr/service/company.php (회사소개·문의)</t>
-        </is>
-      </c>
-      <c r="I87" s="5" t="inlineStr">
-        <is>
-          <t>인천 계양구</t>
-        </is>
-      </c>
+          <t>http://sns3524.godomall.com/main/index.php?pcView=y</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr"/>
       <c r="J87" s="5" t="inlineStr">
         <is>
-          <t>캐릭터 인형 OEM(생산·검수·유통·납품), 판촉물·기념품 유통</t>
+          <t>의료용 관절보호대 제조·유통 (자체 브랜드 파워플러스·스포라이트·웰팜스)</t>
         </is>
       </c>
       <c r="K87" s="5" t="inlineStr">
         <is>
-          <t>불명(회사소개에 '중국OEM' 명시, 자체 공장·지사 여부 미공개)</t>
+          <t>불명(제조·유통 전문사로 소개되나 공장 소재지 미확인)</t>
         </is>
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>중국 OEM을 활용해 인형·판촉물을 공급하는 유통형 업체라 신뢰할 수 있는 현지 소싱 파트너 추가에 관심을 가질 수 있다.</t>
+          <t>복수의 보호대 브랜드를 운영하는 관절보호대 전문 제조·유통사로 품목 보완용 중국 OEM 협업 여지가 있으나 자체 제조 가능성이 있어 경쟁 관계일 수 있음.</t>
         </is>
       </c>
       <c r="M87" s="9" t="inlineStr">
         <is>
-          <t>https://www.toyworks.kr/service/company.php ; https://www.cinavro.kr/service/company.php</t>
+          <t>http://sns3524.godomall.com/main/index.php?pcView=y</t>
         </is>
       </c>
       <c r="N87" s="7" t="inlineStr"/>
@@ -6664,57 +6680,45 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>아이텐션</t>
+          <t>트라택 (TRATAC)</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>캐릭터·IP·팬굿즈 기획사</t>
+          <t>스포츠·헬스·재활용품 유통사/OEM브랜드</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>https://itension.co.kr/</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>070-8015-2628</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>itension@naver.com</t>
-        </is>
-      </c>
+          <t>https://tratac.co.kr</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr"/>
+      <c r="G88" s="5" t="inlineStr"/>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>https://itension.co.kr/ (온라인 주문·문의)</t>
-        </is>
-      </c>
-      <c r="I88" s="5" t="inlineStr">
-        <is>
-          <t>경기 김포시</t>
-        </is>
-      </c>
+          <t>https://tratac.co.kr</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr"/>
       <c r="J88" s="5" t="inlineStr">
         <is>
-          <t>아크릴 키링·스탠드·코롯토, 캐릭터 피규어, 등신대, 디오라마, 패브릭 굿즈</t>
+          <t>세라밴드 등 재활·헬스케어 운동용품 (헬스케어 플랫폼)</t>
         </is>
       </c>
       <c r="K88" s="5" t="inlineStr">
         <is>
-          <t>약함(국내 인쇄·아크릴 자체 제작 위주, 중국 거점 언급 없음)</t>
+          <t>불명(헬스케어 유통 플랫폼, 제조 정보 미확인)</t>
         </is>
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>아크릴 굿즈는 국내 자체 가공하지만 피규어·패브릭 등 품목 확장 시 중국 소싱이 필요할 수 있어 보조 파트너로 접근 가능하다.</t>
+          <t>재활·헬스케어 용품 플랫폼으로 물리치료실·재활센터 납품용 보호대·밴드 OEM 공급처가 필요할 수 있음.</t>
         </is>
       </c>
       <c r="M88" s="9" t="inlineStr">
         <is>
-          <t>https://itension.co.kr/ ; https://www.daangn.com/kr/local-profile/6204/</t>
+          <t>https://tratac.co.kr/shop/prd_list.php?catcode=161100</t>
         </is>
       </c>
       <c r="N88" s="7" t="inlineStr"/>
@@ -6736,49 +6740,57 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>이너부스(INABOOTH)</t>
+          <t>하라스포츠</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>캐릭터·IP·팬굿즈 기획사</t>
+          <t>스포츠·헬스·재활용품 유통사/OEM브랜드</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>https://inabooth.io/</t>
-        </is>
-      </c>
-      <c r="F89" s="5" t="inlineStr"/>
-      <c r="G89" s="5" t="inlineStr"/>
+          <t>https://harasports.net</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>063-462-6300</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>hhhh4076@naver.com</t>
+        </is>
+      </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>https://inabooth.io/ko (플랫폼 내 채팅·협업 제안)</t>
+          <t>https://harasports.net</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>서울 마포구</t>
+          <t>전북특별자치도 군산시</t>
         </is>
       </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
-          <t>캐릭터 IP 라이선싱·콜라보 중개, MD(굿즈) 제작 지원, IP 트렌드 정보</t>
+          <t>원판·아령·바벨봉·케틀벨·메디슨볼·폼롤러·요가매트 등 헬스 소도구 85종</t>
         </is>
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
-          <t>불명(IP 거래 플랫폼으로 자체 생산 거점 언급 없음)</t>
+          <t>불명(헬스 소도구 유통, 제조 정보 미확인)</t>
         </is>
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>캐릭터 IP 라이선싱부터 MD 제작까지 원스톱 지원을 표방하는 플랫폼이라 굿즈 제작 단계에서 연결할 중국 소싱 파트너가 필요할 수 있다.</t>
+          <t>헬스 소도구 전 품목을 취급하는 유통사로 보호대·소도구 신규 소싱 파트너로 접근 가능함.</t>
         </is>
       </c>
       <c r="M89" s="9" t="inlineStr">
         <is>
-          <t>https://inabooth.io/en ; https://news.mt.co.kr/mtview.php?no=2022050311250916932</t>
+          <t>https://harasports.net/</t>
         </is>
       </c>
       <c r="N89" s="7" t="inlineStr"/>
@@ -6800,57 +6812,53 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>케빈스룸</t>
+          <t>(주)비즈마켓</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>캐릭터·IP·팬굿즈 기획사</t>
+          <t>제약·의료·치과 판촉물 벤더</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>https://www.kevinsroom.co.kr/</t>
+          <t>https://www.bizmarket.com/</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>070-4333-2019</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>Kevin@kevinsroom.co.kr</t>
-        </is>
-      </c>
+          <t>1670-1628</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr"/>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>https://www.kevinsroom.co.kr/contactmain (견적문의), 카카오톡 채널 https://pf.kakao.com/_aJxcxgxb</t>
+          <t>https://www.bizmarket.com/promotion</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>경기 광명시</t>
+          <t>서울 용산구</t>
         </is>
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>캐릭터 봉제인형, 인형 키링, 파우치 키링, 핸드워머, 스트레스볼, 풉백 파우치</t>
+          <t>제약·전자·금융사 사은품·판촉물 제작, 제약사 전용(PL/PB) 상품 개발, 캐릭터·로고 활용 굿즈, 기업 판촉몰 구축</t>
         </is>
       </c>
       <c r="K90" s="5" t="inlineStr">
         <is>
-          <t>불명(국내 제작이 어려운 봉제 인형을 합리적 단가로 제작한다고 표기, 해외 공장 소재 미공개)</t>
+          <t>불명 (글로벌 B2B 서비스 언급은 있으나 자체 중국공장·지사 명시 없음)</t>
         </is>
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>봉제 캐릭터 굿즈를 해외 생산 기반으로 공급하는 소규모 업체로 생산처 다변화나 신규 품목 소싱 시 중국 파트너가 유용할 수 있다.</t>
+          <t>제약사 대상 전용 판촉물·PL/PB 굿즈 개발을 사업영역으로 명시한 업체로, 규모는 크지만 제약 판촉 물량이 안정적임.</t>
         </is>
       </c>
       <c r="M90" s="9" t="inlineStr">
         <is>
-          <t>https://www.kevinsroom.co.kr/contactmain ; https://www.kevinsroom.co.kr/plushdoll</t>
+          <t>https://www.bizmarket.com/promotion</t>
         </is>
       </c>
       <c r="N90" s="7" t="inlineStr"/>
@@ -6872,57 +6880,45 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>위오아이엔씨(WEO)</t>
+          <t>가로기프트</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>캐릭터·IP·팬굿즈 기획사 · 판촉물·굿즈 제작대행사</t>
+          <t>제약·의료·치과 판촉물 벤더</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>https://weo.co.kr/</t>
-        </is>
-      </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>02-2088-2427</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>weomail@weo.co.kr</t>
-        </is>
-      </c>
+          <t>https://garogift.com/</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr"/>
+      <c r="G91" s="5" t="inlineStr"/>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>https://weo.co.kr/ (제작 문의 게시판)</t>
-        </is>
-      </c>
-      <c r="I91" s="5" t="inlineStr">
-        <is>
-          <t>서울 영등포구</t>
-        </is>
-      </c>
+          <t>https://garogift.com/</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr"/>
       <c r="J91" s="5" t="inlineStr">
         <is>
-          <t>봉제인형(아이돌 인형, 라이선스 캐릭터 인형), 캐릭터 굿즈, 프로모션 상품 / 봉제인형, 캐릭터·아이돌 IP 굿즈, 프로모션 상품</t>
+          <t>병원 판촉물, 약국 판촉물, 텀블러, 기념품, 업종별(보험·학교·학원·교회) 판촉물</t>
         </is>
       </c>
       <c r="K91" s="5" t="inlineStr">
         <is>
-          <t>불명(인형 샘플실 및 직영공장 보유 표기, 공장 소재지 미공개)</t>
+          <t>불명 (자체 공장·중국지사 언급 없음)</t>
         </is>
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>인형 직영공장을 보유해 봉제는 자체 처리하나 아이돌·IP 굿즈로 품목이 넓어 비봉제 품목의 중국 소싱 파트너가 필요할 수 있다. / 봉제 자체 공장을 보유해 인형류는 자급하지만 그 외 굿즈 카테고리는 외부 소싱이 필요할 수 있다.</t>
+          <t>병원·약국 판촉물 전용 페이지를 운영하는 소규모 판촉물 중개 벤더로 의료 고객 대상 굿즈 소싱 파트너 수요가 예상됨.</t>
         </is>
       </c>
       <c r="M91" s="9" t="inlineStr">
         <is>
-          <t>https://weo.co.kr/ ; https://bizno.net/article/7378700350</t>
+          <t>https://garogift.com/%EB%B3%91%EC%9B%90-%ED%8C%90%EC%B4%89%EB%AC%BC/</t>
         </is>
       </c>
       <c r="N91" s="7" t="inlineStr"/>
@@ -6944,57 +6940,45 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>굿즈24((주)위펀)</t>
+          <t>나래기프트</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>판촉물·굿즈 제작대행사</t>
+          <t>제약·의료·치과 판촉물 벤더</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>https://wefuncorp.com/goods</t>
-        </is>
-      </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>1644-4624</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>sales@snack24h.com</t>
-        </is>
-      </c>
+          <t>https://naregift.kr/</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr"/>
+      <c r="G92" s="5" t="inlineStr"/>
       <c r="H92" s="5" t="inlineStr">
         <is>
-          <t>https://wefuncorp.com/goods (굿즈24 상담 신청)</t>
-        </is>
-      </c>
-      <c r="I92" s="5" t="inlineStr">
-        <is>
-          <t>서울 강남구</t>
-        </is>
-      </c>
+          <t>https://naregift.kr/</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr"/>
       <c r="J92" s="5" t="inlineStr">
         <is>
-          <t>기업 웰컴키트, 오피스 키트, 아이돌·웹툰 IP 굿즈, 브랜드 굿즈</t>
+          <t>병원·관공서·기업·학원 홍보용품 주문제작 (텀블러, 볼펜·형광펜, 키링, 파우치, 선물세트)</t>
         </is>
       </c>
       <c r="K92" s="5" t="inlineStr">
         <is>
-          <t>불명(자체 공장·중국 지사 언급 확인 안 됨)</t>
+          <t>불명 (자체 공장·중국지사 언급 없음)</t>
         </is>
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>기업복지 플랫폼(스낵24)의 굿즈 사업부로 자체 제조가 없어 외부 소싱 파트너가 필요하지만 기존 거래 벤더가 있을 가능성이 있다.</t>
+          <t>병원을 주요 납품처로 명시한 소규모 판촉물 주문제작 쇼핑몰로 자체 생산시설 없이 유통 중심이라 중국 생산 파트너 제안 여지가 있음.</t>
         </is>
       </c>
       <c r="M92" s="9" t="inlineStr">
         <is>
-          <t>https://wefuncorp.com/goods</t>
+          <t>https://naregift.kr/m/sub/prdview.php?prdcode=249476</t>
         </is>
       </c>
       <c r="N92" s="7" t="inlineStr"/>
@@ -7016,53 +7000,45 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>빅스템(BIGSTEM)</t>
+          <t>라임기프트판촉물</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>판촉물·굿즈 제작대행사</t>
+          <t>제약·의료·치과 판촉물 벤더</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>https://bigstem.co.kr/</t>
+          <t>https://limegiftmall.com/</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr"/>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>smooji@daum.net</t>
-        </is>
-      </c>
+      <c r="G93" s="5" t="inlineStr"/>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>카카오톡 채널 https://pf.kakao.com/_xihxixnb, https://bigstem.co.kr/ (제작문의)</t>
-        </is>
-      </c>
-      <c r="I93" s="5" t="inlineStr">
-        <is>
-          <t>서울 강북구</t>
-        </is>
-      </c>
+          <t>https://limegiftmall.com/</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr"/>
       <c r="J93" s="5" t="inlineStr">
         <is>
-          <t>레디백, 폴딩카트, 봉제인형 키링, 리유저블백 등 기업·전시·행사 프로모션 굿즈</t>
+          <t>병원/약국 판촉물 카테고리, 기념품, 사은품</t>
         </is>
       </c>
       <c r="K93" s="5" t="inlineStr">
         <is>
-          <t>약함(중국 주요 제조업체에 직원 파견해 협력관계 구축 언급, 자체 공장·지사는 아님)</t>
+          <t>불명 (자체 공장·중국지사 언급 없음)</t>
         </is>
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>이미 중국 협력 제조사 네트워크를 운영하지만 자체 법인은 없어 신규 카테고리 소싱이나 검수 대행 파트너로는 협업 여지가 있다.</t>
+          <t>병원/약국 판촉물 카테고리를 별도로 운영하는 소규모 판촉물 쇼핑몰로 의료 고객향 굿즈 소싱 협업 여지가 있음.</t>
         </is>
       </c>
       <c r="M93" s="9" t="inlineStr">
         <is>
-          <t>https://bigstem.co.kr/about-us/</t>
+          <t>https://limegiftmall.com/list/list.html?ccode=12292</t>
         </is>
       </c>
       <c r="N93" s="7" t="inlineStr"/>
@@ -7084,57 +7060,45 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>올댓프린팅</t>
+          <t>바나나조이</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>판촉물·굿즈 제작대행사</t>
+          <t>제약·의료·치과 판촉물 벤더</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>https://allthatprinting.co.kr/</t>
-        </is>
-      </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t>031-418-1109</t>
-        </is>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>allthatprinting.m@gmail.com</t>
-        </is>
-      </c>
+          <t>http://bananajoy.kr/</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr"/>
+      <c r="G94" s="5" t="inlineStr"/>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>https://allthatprinting.co.kr/board/문의하기/6/ (문의 게시판)</t>
-        </is>
-      </c>
-      <c r="I94" s="5" t="inlineStr">
-        <is>
-          <t>안산 단원구</t>
-        </is>
-      </c>
+          <t>http://bananajoy.kr/</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr"/>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t>아크릴 키링·스탠드·코롯토·스마트톡, NFC 굿즈, 기업 홍보 굿즈</t>
+          <t>병원/약국 사은품 카테고리, 주문제작 다이어리, 타올·우산세트, 기념품 도매</t>
         </is>
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
-          <t>약함(국내 아크릴 자체 생산 위주, 중국 공장·지사 언급 없음)</t>
+          <t>불명 (자체 공장·중국지사 언급 없음)</t>
         </is>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>아크릴 굿즈는 국내 자체 생산하지만 기업 홍보 굿즈 카테고리 확장 시 아크릴 외 품목의 중국 소싱 파트너가 필요할 수 있다.</t>
+          <t>병원/약국 전용 사은품 카테고리를 운영하는 소규모 판촉물 도매몰로 의료 고객 납품용 굿즈 소싱 파트너 제안이 가능함.</t>
         </is>
       </c>
       <c r="M94" s="9" t="inlineStr">
         <is>
-          <t>https://allthatprinting.co.kr/about.html</t>
+          <t>http://www.bananajoy.kr/list/list.html?ccode=12292</t>
         </is>
       </c>
       <c r="N94" s="7" t="inlineStr"/>
@@ -7149,52 +7113,60 @@
       <c r="A95" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="10" t="inlineStr">
-        <is>
-          <t>하</t>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>기프트위키</t>
+          <t>알짜기프트</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
+          <t>제약·의료·치과 판촉물 벤더</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>https://giftwiki.kr/</t>
+          <t>http://aljjagift.com/</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>1522-8992</t>
+          <t>1661-8712</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr"/>
-      <c r="H95" s="5" t="inlineStr"/>
-      <c r="I95" s="5" t="inlineStr"/>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>http://aljjagift.com/</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>서울 금천구</t>
+        </is>
+      </c>
       <c r="J95" s="5" t="inlineStr">
         <is>
-          <t>기념품·홍보용품 맞춤 제작 판촉물</t>
+          <t>홍보판촉물, 기념품, 답례품, 단체선물 도매</t>
         </is>
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
-          <t>불명(사이트 접근 차단으로 확인 불가)</t>
+          <t>약함 (조아기프트 네트워크 소속 판매점으로 자체 공장·중국지사 언급 없음)</t>
         </is>
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>기념품·홍보용품 맞춤 제작 판촉몰로 검색에 노출되나 취급 규모와 연락처를 확인하지 못해 우선순위는 낮음.</t>
+          <t>제약사 판촉물 검색에 노출되는 소규모 판촉물 도매 벤더로 자체 생산시설 없이 유통 중심이라 소싱 파트너 제안이 가능함.</t>
         </is>
       </c>
       <c r="M95" s="9" t="inlineStr">
         <is>
-          <t>https://giftwiki.kr/</t>
+          <t>http://aljjagift.com/</t>
         </is>
       </c>
       <c r="N95" s="7" t="inlineStr"/>
@@ -7209,64 +7181,60 @@
       <c r="A96" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="10" t="inlineStr">
-        <is>
-          <t>하</t>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>딜리버리팩토리((주)커넥트어센드)</t>
+          <t>조일기프트 / (주)올가코리아</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>무역·소싱대행·수입도매</t>
+          <t>제약·의료·치과 판촉물 벤더</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>https://deliveryfactory.co.kr</t>
-        </is>
-      </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>070-8834-1001</t>
-        </is>
-      </c>
+          <t>https://joilgift.kr/</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr"/>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>mousy008@cscommerce.co.kr</t>
+          <t>gift@olgakorea.com</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>https://deliveryfactory.co.kr/service</t>
+          <t>https://joilgift.kr/</t>
         </is>
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>서울 서초구</t>
+          <t>용인 기흥구</t>
         </is>
       </c>
       <c r="J96" s="5" t="inlineStr">
         <is>
-          <t>중국수입대행, OEM제조, 식약처검사대행, 물류관리</t>
+          <t>온습도계, 주문제작 에코백·뱃지·북마크, 핸드타올, 생활용품 판촉물</t>
         </is>
       </c>
       <c r="K96" s="5" t="inlineStr">
         <is>
-          <t>강함(자체공장/지사)(중국공장 직수입·OEM 제조 서비스를 자체 운영)</t>
+          <t>불명 (자체 공장·중국지사 언급 없음)</t>
         </is>
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>중국공장 직수입·OEM 대행을 자체 서비스로 운영하는 직접 경쟁사로 외부 소싱 파트너 수요가 낮다.</t>
+          <t>온습도계 등 제약 판촉 단골 품목을 취급하는 소규모 판촉물 벤더로 주문제작형 굿즈 소싱 수요가 있음.</t>
         </is>
       </c>
       <c r="M96" s="9" t="inlineStr">
         <is>
-          <t>https://deliveryfactory.co.kr/</t>
+          <t>https://joilgift.kr/m/sub/prdview.php?prdcode=212000</t>
         </is>
       </c>
       <c r="N96" s="7" t="inlineStr"/>
@@ -7281,44 +7249,56 @@
       <c r="A97" s="5" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="10" t="inlineStr">
-        <is>
-          <t>하</t>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>세인(SEIN)</t>
+          <t>판촉물365 (HS/판촉물365)</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>무역·소싱대행·수입도매</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr"/>
+          <t>제약·의료·치과 판촉물 벤더</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>https://dapaleo.com/</t>
+        </is>
+      </c>
       <c r="F97" s="5" t="inlineStr"/>
-      <c r="G97" s="5" t="inlineStr"/>
-      <c r="H97" s="5" t="inlineStr"/>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>heesu18900@gmail.com</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>https://www.dapaleo.com/new/customer/sample.htm</t>
+        </is>
+      </c>
       <c r="I97" s="5" t="inlineStr"/>
       <c r="J97" s="5" t="inlineStr">
         <is>
-          <t>중국 완제품 소싱·구매대행, OEM 제작·생산관리, 검품·국제물류</t>
+          <t>기업·병원·은행·관공서 맞춤 우산, 타올, 볼펜, 텀블러, 머그, 보조배터리, USB, 캘린더</t>
         </is>
       </c>
       <c r="K97" s="5" t="inlineStr">
         <is>
-          <t>강함(자체공장/지사)(중국 현지법인·한국지사 운영, 대표 중국 거주 26년)</t>
+          <t>불명 (자체 공장·중국지사 언급 없음, 여성기업·창업기업 인증 소규모 업체)</t>
         </is>
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>중국 현지법인을 직접 운영하며 소싱·OEM·검품을 일괄 수행하는 직접 경쟁사다.</t>
+          <t>병원을 주요 고객군으로 명시한 여성기업 인증 소규모 판촉물 벤더로 원가 경쟁력 있는 중국 생산 파트너 수요가 예상됨.</t>
         </is>
       </c>
       <c r="M97" s="9" t="inlineStr">
         <is>
-          <t>https://www.japantalk.net/free/?mod=document&amp;uid=5110</t>
+          <t>https://dapaleo.business.site/</t>
         </is>
       </c>
       <c r="N97" s="7" t="inlineStr"/>
@@ -7333,52 +7313,60 @@
       <c r="A98" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="10" t="inlineStr">
-        <is>
-          <t>하</t>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>소싱차이나</t>
+          <t>판촉물파트너(인쇄기프트 스토어)</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>무역·소싱대행·수입도매</t>
+          <t>제약·의료·치과 판촉물 벤더</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>https://sourcingchina.co.kr</t>
-        </is>
-      </c>
-      <c r="F98" s="5" t="inlineStr"/>
+          <t>https://printgift.co.kr/</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>070-4238-6667</t>
+        </is>
+      </c>
       <c r="G98" s="5" t="inlineStr"/>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>https://sourcingchina.co.kr/</t>
-        </is>
-      </c>
-      <c r="I98" s="5" t="inlineStr"/>
+          <t>https://printgift.co.kr/shopinfo/company.html</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>서울 광진구</t>
+        </is>
+      </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
-          <t>중국수입대행, 굿즈제작(OEM), 의류사입, 안전인증 대행</t>
+          <t>판촉물·기념품·답례품 도매 인쇄 제작 (클립형 볼펜, 웹캠커버, 보조배터리 등)</t>
         </is>
       </c>
       <c r="K98" s="5" t="inlineStr">
         <is>
-          <t>불명(중국 수입대행 전문이나 자체 지사 여부 미확인)</t>
+          <t>불명 (자체 공장·중국지사 언급 없음)</t>
         </is>
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>중국 수입대행·굿즈 OEM을 직접 수행하는 동종 경쟁사다.</t>
+          <t>약국 판촉물 검색에 노출되는 소규모 인쇄·판촉물 도매 스토어로 자체 공장 없이 인쇄 가공 중심이라 중국 소싱 협업 여지가 있음.</t>
         </is>
       </c>
       <c r="M98" s="9" t="inlineStr">
         <is>
-          <t>https://sourcingchina.co.kr/go_01/</t>
+          <t>https://printgift.co.kr/shopinfo/company.html</t>
         </is>
       </c>
       <c r="N98" s="7" t="inlineStr"/>
@@ -7393,52 +7381,52 @@
       <c r="A99" s="5" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="10" t="inlineStr">
-        <is>
-          <t>하</t>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>이우허브</t>
+          <t>O-SEAN(런투더퓨처랩스)</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>무역·소싱대행·수입도매</t>
+          <t>캐릭터·IP·팬굿즈 기획사</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>https://www.yiwuhub.net</t>
+          <t>https://o-sean.io/</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr"/>
       <c r="G99" s="5" t="inlineStr"/>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>https://www.yiwuhub.net/34</t>
+          <t>https://o-sean.io/ (견적 문의·1:1 상담 폼)</t>
         </is>
       </c>
       <c r="I99" s="5" t="inlineStr"/>
       <c r="J99" s="5" t="inlineStr">
         <is>
-          <t>중국(이우) 수입대행, OEM</t>
+          <t>게임·엔터 IP 피규어 키링, 아크릴 키링·뱃지, 에코백·파우치, 텀블러, 문구, 디지털 굿즈(MOQ 50~100개)</t>
         </is>
       </c>
       <c r="K99" s="5" t="inlineStr">
         <is>
-          <t>불명(이우 기반 수입대행 표방, 자체 지사 여부 미확인)</t>
+          <t>약함(자체 생산 라인 보유 표기, 중국 거점 언급 없음)</t>
         </is>
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>이우 도매시장 기반 수입대행·OEM을 직접 제공하는 동종 경쟁사다.</t>
+          <t>게임·엔터 IP용 피규어 키링을 MOQ 100개·4주로 제작하는 스타트업으로 소량 다품종 생산을 위한 중국 소싱 파트너가 보완적으로 필요할 수 있다.</t>
         </is>
       </c>
       <c r="M99" s="9" t="inlineStr">
         <is>
-          <t>https://www.yiwuhub.net/34</t>
+          <t>https://o-sean.io/about ; https://o-sean.io/category/item/LS-023</t>
         </is>
       </c>
       <c r="N99" s="7" t="inlineStr"/>
@@ -7453,56 +7441,64 @@
       <c r="A100" s="5" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="10" t="inlineStr">
-        <is>
-          <t>하</t>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>홀세일차이나</t>
+          <t>굿즈나라(헤세드하우스)</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>무역·소싱대행·수입도매</t>
+          <t>캐릭터·IP·팬굿즈 기획사</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>https://wholesalechina.co.kr</t>
+          <t>https://goodsnara.com/</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>070-8248-6654</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="inlineStr"/>
+          <t>031-994-7740</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>hesedhouse2@naver.com</t>
+        </is>
+      </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>https://wholesalechina.co.kr/board/list/code/faq</t>
-        </is>
-      </c>
-      <c r="I100" s="5" t="inlineStr"/>
+          <t>https://goodsnara.com/form (굿즈 디자인 폼), 카카오톡 채널(24시간 문의)</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>경기 고양시 일산서구</t>
+        </is>
+      </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>중국 구매대행, 시장조사, 수입대행, 배송대행(중국 현지 물류센터)</t>
+          <t>KPOP 아이돌 팬굿즈(슬로건, 이미지피켓, 반사 포토슬로건), 캔텀블러, 보조배터리, 기념품</t>
         </is>
       </c>
       <c r="K100" s="5" t="inlineStr">
         <is>
-          <t>강함(자체공장/지사)(중국 현지 물류센터 운영 명시)</t>
+          <t>불명(홈페이지에 생산 거점·중국 공장 언급 없음)</t>
         </is>
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>중국 현지 물류센터와 수입대행을 직접 운영하는 경쟁사로 외부 소싱망이 필요하지 않다.</t>
+          <t>아이돌 팬덤 대상 응원 굿즈·잡화를 기획 제작하는 소규모 업체로 텀블러·배터리 등 공산품은 외부 소싱이 필요해 중국 파트너 수요가 있을 수 있다.</t>
         </is>
       </c>
       <c r="M100" s="9" t="inlineStr">
         <is>
-          <t>https://wholesalechina.co.kr/agency/delivery</t>
+          <t>https://goodsnara.com/ ; https://goodsnara.com/form</t>
         </is>
       </c>
       <c r="N100" s="7" t="inlineStr"/>
@@ -7517,14 +7513,14 @@
       <c r="A101" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="10" t="inlineStr">
-        <is>
-          <t>하</t>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>쿠디솜</t>
+          <t>스마일웍스</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -7534,43 +7530,47 @@
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>https://www.qudisom.com/</t>
+          <t>http://www.smileworks.co.kr/</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>1666-0211</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="inlineStr"/>
+          <t>02-2675-8755</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>moon@smileworks.co.kr</t>
+        </is>
+      </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>https://www.qudisom.com/ (고객 문의 게시판·주문 프로세스 페이지)</t>
+          <t>http://www.smileworks.co.kr/default/online/sub1.php (온라인 문의)</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>인천 남동구</t>
+          <t>서울 영등포구</t>
         </is>
       </c>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t>캐릭터 인형·봉제 아이템, 캐릭터 굿즈, KC인증 대행</t>
+          <t>봉제인형, 사출 피규어, 웹소설·연예인·캐릭터 굿즈, 스트레스볼 등 기타 굿즈</t>
         </is>
       </c>
       <c r="K101" s="5" t="inlineStr">
         <is>
-          <t>강함(자체공장/지사)(항저우·양저우·웨이팡 직영 공장 주소 공개, 중간 유통 없이 직접 생산)</t>
+          <t>불명(국내·국외 패턴 개발실 운영 표기, 해외 거점 국가·공장 미공개)</t>
         </is>
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>중국 직영 공장 3곳 이상을 운영하는 구조라 외부 중국 소싱 파트너 필요성이 낮고 오히려 경쟁사에 가깝다.</t>
+          <t>봉제인형에서 사출 피규어·잡화까지 품목이 넓어 자체 개발실 외 양산 공장 다변화 시 중국 소싱 파트너가 도움이 될 수 있다.</t>
         </is>
       </c>
       <c r="M101" s="9" t="inlineStr">
         <is>
-          <t>https://www.qudisom.com/ ; https://www.qudisom.com/sewingorder</t>
+          <t>http://www.smileworks.co.kr/default/work/sub1.php ; http://www.smileworks.co.kr/default/work/sub2.php</t>
         </is>
       </c>
       <c r="N101" s="7" t="inlineStr"/>
@@ -7585,14 +7585,14 @@
       <c r="A102" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="10" t="inlineStr">
-        <is>
-          <t>하</t>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>팔팔토이(88TOY)</t>
+          <t>시나브로(토이웍스 인형사업부)</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
@@ -7602,47 +7602,47 @@
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>http://www.88toy.co.kr/</t>
+          <t>https://www.toyworks.kr/</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>02-6052-0150</t>
+          <t>032-554-9954</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>pp.88toy@gmail.com</t>
+          <t>toyworks@daum.net</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>http://www.88toy.co.kr/ABOUTOEM (제작문의 게시판 후 이메일 접수)</t>
+          <t>https://www.toyworks.kr/service/company.php (회사소개·문의)</t>
         </is>
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>서울 구로구</t>
+          <t>인천 계양구</t>
         </is>
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>캐릭터 봉제인형 OEM(샘플 1개~10만개), 인형 부자재·라벨</t>
+          <t>캐릭터 인형 OEM(생산·검수·유통·납품), 판촉물·기념품 유통</t>
         </is>
       </c>
       <c r="K102" s="5" t="inlineStr">
         <is>
-          <t>강함(자체공장/지사)(중국 청도 공장과 독점계약해 자사 제품만 생산, 서울 항동 샘플개발실 운영)</t>
+          <t>불명(회사소개에 '중국OEM' 명시, 자체 공장·지사 여부 미공개)</t>
         </is>
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>이미 청도 독점 공장을 확보한 인형 제조사로 인형 외 품목(피규어·잡화) 소싱이 아니면 외부 중국 파트너 수요가 낮다.</t>
+          <t>중국 OEM을 활용해 인형·판촉물을 공급하는 유통형 업체라 신뢰할 수 있는 현지 소싱 파트너 추가에 관심을 가질 수 있다.</t>
         </is>
       </c>
       <c r="M102" s="9" t="inlineStr">
         <is>
-          <t>http://www.88toy.co.kr/ABOUTOEM ; http://www.88toy.co.kr/183</t>
+          <t>https://www.toyworks.kr/service/company.php ; https://www.cinavro.kr/service/company.php</t>
         </is>
       </c>
       <c r="N102" s="7" t="inlineStr"/>
@@ -7657,52 +7657,64 @@
       <c r="A103" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="10" t="inlineStr">
-        <is>
-          <t>하</t>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>고굿즈(GOGOODS)</t>
+          <t>아이텐션</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>판촉물·굿즈 제작대행사</t>
+          <t>캐릭터·IP·팬굿즈 기획사</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>https://gogoods.kr/</t>
-        </is>
-      </c>
-      <c r="F103" s="5" t="inlineStr"/>
-      <c r="G103" s="5" t="inlineStr"/>
+          <t>https://itension.co.kr/</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>070-8015-2628</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>itension@naver.com</t>
+        </is>
+      </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>https://gogoods.kr/manufacturing (제작·소싱 문의)</t>
-        </is>
-      </c>
-      <c r="I103" s="5" t="inlineStr"/>
+          <t>https://itension.co.kr/ (온라인 주문·문의)</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>경기 김포시</t>
+        </is>
+      </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>굿즈·패션잡화 OEM/ODM, 중국 공장 소싱, 구매대행</t>
+          <t>아크릴 키링·스탠드·코롯토, 캐릭터 피규어, 등신대, 디오라마, 패브릭 굿즈</t>
         </is>
       </c>
       <c r="K103" s="5" t="inlineStr">
         <is>
-          <t>강함(자체공장/지사)(이우 지사, 심천/동관 지사 운영 및 현지 검수·A/S 명시)</t>
+          <t>약함(국내 인쇄·아크릴 자체 제작 위주, 중국 거점 언급 없음)</t>
         </is>
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>중국 이우·심천·동관 지사를 직접 운영하는 소싱형 업체라 외부 중국 소싱 파트너가 필요하지 않고 오히려 경쟁사에 가깝다.</t>
+          <t>아크릴 굿즈는 국내 자체 가공하지만 피규어·패브릭 등 품목 확장 시 중국 소싱이 필요할 수 있어 보조 파트너로 접근 가능하다.</t>
         </is>
       </c>
       <c r="M103" s="9" t="inlineStr">
         <is>
-          <t>https://gogoods.kr/manufacturing</t>
+          <t>https://itension.co.kr/ ; https://www.daangn.com/kr/local-profile/6204/</t>
         </is>
       </c>
       <c r="N103" s="7" t="inlineStr"/>
@@ -7717,64 +7729,56 @@
       <c r="A104" s="5" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="10" t="inlineStr">
-        <is>
-          <t>하</t>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>판촉사랑</t>
+          <t>이너부스(INABOOTH)</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>판촉물·굿즈 제작대행사 · 관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
+          <t>캐릭터·IP·팬굿즈 기획사</t>
         </is>
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>https://www.87sarang.com/</t>
-        </is>
-      </c>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>1688-8744</t>
-        </is>
-      </c>
-      <c r="G104" s="5" t="inlineStr">
-        <is>
-          <t>gift@87sarang.com</t>
-        </is>
-      </c>
+          <t>https://inabooth.io/</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr"/>
+      <c r="G104" s="5" t="inlineStr"/>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>https://www.87sarang.com/co/contact2.html (질문과답변/견적문의)</t>
+          <t>https://inabooth.io/ko (플랫폼 내 채팅·협업 제안)</t>
         </is>
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>인천 남동구</t>
+          <t>서울 마포구</t>
         </is>
       </c>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t>기업 판촉물, 답례품, 기념품, 홍보물(자체 인쇄시설 보유) / 기업·금융권·공공기관 판촉물, 답례품, 기념품 (전국 지역별 판촉사랑 분점망 운영)</t>
+          <t>캐릭터 IP 라이선싱·콜라보 중개, MD(굿즈) 제작 지원, IP 트렌드 정보</t>
         </is>
       </c>
       <c r="K104" s="5" t="inlineStr">
         <is>
-          <t>강함(자체공장/지사)(회사소개에 중국지사 보유 및 디자인연구소·자체 인쇄시설 명시)</t>
+          <t>불명(IP 거래 플랫폼으로 자체 생산 거점 언급 없음)</t>
         </is>
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>중국지사와 자체 인쇄시설을 갖춘 판촉물 전문기업이라 외부 중국 소싱 파트너 필요성이 낮다. / 서울·부산·경남·전남·제주 등 전국 지역 분점망을 갖추고 업종별(금융권 포함) 납품사례를 공개하는 규모 있는 업체로 다품종 대량 소싱 파트너 수요가 클 것으로 판단됨.</t>
+          <t>캐릭터 IP 라이선싱부터 MD 제작까지 원스톱 지원을 표방하는 플랫폼이라 굿즈 제작 단계에서 연결할 중국 소싱 파트너가 필요할 수 있다.</t>
         </is>
       </c>
       <c r="M104" s="9" t="inlineStr">
         <is>
-          <t>https://www.87sarang.com/co/company2.html</t>
+          <t>https://inabooth.io/en ; https://news.mt.co.kr/mtview.php?no=2022050311250916932</t>
         </is>
       </c>
       <c r="N104" s="7" t="inlineStr"/>
@@ -7785,13 +7789,1209 @@
       <c r="S104" s="7" t="inlineStr"/>
       <c r="T104" s="7" t="inlineStr"/>
     </row>
+    <row r="105">
+      <c r="A105" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>케빈스룸</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>캐릭터·IP·팬굿즈 기획사</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kevinsroom.co.kr/</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>070-4333-2019</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>Kevin@kevinsroom.co.kr</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kevinsroom.co.kr/contactmain (견적문의), 카카오톡 채널 https://pf.kakao.com/_aJxcxgxb</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>경기 광명시</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t>캐릭터 봉제인형, 인형 키링, 파우치 키링, 핸드워머, 스트레스볼, 풉백 파우치</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t>불명(국내 제작이 어려운 봉제 인형을 합리적 단가로 제작한다고 표기, 해외 공장 소재 미공개)</t>
+        </is>
+      </c>
+      <c r="L105" s="5" t="inlineStr">
+        <is>
+          <t>봉제 캐릭터 굿즈를 해외 생산 기반으로 공급하는 소규모 업체로 생산처 다변화나 신규 품목 소싱 시 중국 파트너가 유용할 수 있다.</t>
+        </is>
+      </c>
+      <c r="M105" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kevinsroom.co.kr/contactmain ; https://www.kevinsroom.co.kr/plushdoll</t>
+        </is>
+      </c>
+      <c r="N105" s="7" t="inlineStr"/>
+      <c r="O105" s="7" t="inlineStr"/>
+      <c r="P105" s="7" t="inlineStr"/>
+      <c r="Q105" s="7" t="inlineStr"/>
+      <c r="R105" s="7" t="inlineStr"/>
+      <c r="S105" s="7" t="inlineStr"/>
+      <c r="T105" s="7" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>위오아이엔씨(WEO)</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>캐릭터·IP·팬굿즈 기획사 · 판촉물·굿즈 제작대행사</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>https://weo.co.kr/</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>02-2088-2427</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>weomail@weo.co.kr</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>https://weo.co.kr/ (제작 문의 게시판)</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>서울 영등포구</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t>봉제인형(아이돌 인형, 라이선스 캐릭터 인형), 캐릭터 굿즈, 프로모션 상품 / 봉제인형, 캐릭터·아이돌 IP 굿즈, 프로모션 상품</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="inlineStr">
+        <is>
+          <t>불명(인형 샘플실 및 직영공장 보유 표기, 공장 소재지 미공개)</t>
+        </is>
+      </c>
+      <c r="L106" s="5" t="inlineStr">
+        <is>
+          <t>인형 직영공장을 보유해 봉제는 자체 처리하나 아이돌·IP 굿즈로 품목이 넓어 비봉제 품목의 중국 소싱 파트너가 필요할 수 있다. / 봉제 자체 공장을 보유해 인형류는 자급하지만 그 외 굿즈 카테고리는 외부 소싱이 필요할 수 있다.</t>
+        </is>
+      </c>
+      <c r="M106" s="9" t="inlineStr">
+        <is>
+          <t>https://weo.co.kr/ ; https://bizno.net/article/7378700350</t>
+        </is>
+      </c>
+      <c r="N106" s="7" t="inlineStr"/>
+      <c r="O106" s="7" t="inlineStr"/>
+      <c r="P106" s="7" t="inlineStr"/>
+      <c r="Q106" s="7" t="inlineStr"/>
+      <c r="R106" s="7" t="inlineStr"/>
+      <c r="S106" s="7" t="inlineStr"/>
+      <c r="T106" s="7" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>굿즈24((주)위펀)</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>판촉물·굿즈 제작대행사</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>https://wefuncorp.com/goods</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>1644-4624</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>sales@snack24h.com</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>https://wefuncorp.com/goods (굿즈24 상담 신청)</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>서울 강남구</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>기업 웰컴키트, 오피스 키트, 아이돌·웹툰 IP 굿즈, 브랜드 굿즈</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t>불명(자체 공장·중국 지사 언급 확인 안 됨)</t>
+        </is>
+      </c>
+      <c r="L107" s="5" t="inlineStr">
+        <is>
+          <t>기업복지 플랫폼(스낵24)의 굿즈 사업부로 자체 제조가 없어 외부 소싱 파트너가 필요하지만 기존 거래 벤더가 있을 가능성이 있다.</t>
+        </is>
+      </c>
+      <c r="M107" s="9" t="inlineStr">
+        <is>
+          <t>https://wefuncorp.com/goods</t>
+        </is>
+      </c>
+      <c r="N107" s="7" t="inlineStr"/>
+      <c r="O107" s="7" t="inlineStr"/>
+      <c r="P107" s="7" t="inlineStr"/>
+      <c r="Q107" s="7" t="inlineStr"/>
+      <c r="R107" s="7" t="inlineStr"/>
+      <c r="S107" s="7" t="inlineStr"/>
+      <c r="T107" s="7" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>빅스템(BIGSTEM)</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>판촉물·굿즈 제작대행사</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>https://bigstem.co.kr/</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr"/>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>smooji@daum.net</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>카카오톡 채널 https://pf.kakao.com/_xihxixnb, https://bigstem.co.kr/ (제작문의)</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>서울 강북구</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>레디백, 폴딩카트, 봉제인형 키링, 리유저블백 등 기업·전시·행사 프로모션 굿즈</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="inlineStr">
+        <is>
+          <t>약함(중국 주요 제조업체에 직원 파견해 협력관계 구축 언급, 자체 공장·지사는 아님)</t>
+        </is>
+      </c>
+      <c r="L108" s="5" t="inlineStr">
+        <is>
+          <t>이미 중국 협력 제조사 네트워크를 운영하지만 자체 법인은 없어 신규 카테고리 소싱이나 검수 대행 파트너로는 협업 여지가 있다.</t>
+        </is>
+      </c>
+      <c r="M108" s="9" t="inlineStr">
+        <is>
+          <t>https://bigstem.co.kr/about-us/</t>
+        </is>
+      </c>
+      <c r="N108" s="7" t="inlineStr"/>
+      <c r="O108" s="7" t="inlineStr"/>
+      <c r="P108" s="7" t="inlineStr"/>
+      <c r="Q108" s="7" t="inlineStr"/>
+      <c r="R108" s="7" t="inlineStr"/>
+      <c r="S108" s="7" t="inlineStr"/>
+      <c r="T108" s="7" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>올댓프린팅</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>판촉물·굿즈 제작대행사</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>https://allthatprinting.co.kr/</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>031-418-1109</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>allthatprinting.m@gmail.com</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>https://allthatprinting.co.kr/board/문의하기/6/ (문의 게시판)</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>안산 단원구</t>
+        </is>
+      </c>
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t>아크릴 키링·스탠드·코롯토·스마트톡, NFC 굿즈, 기업 홍보 굿즈</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="inlineStr">
+        <is>
+          <t>약함(국내 아크릴 자체 생산 위주, 중국 공장·지사 언급 없음)</t>
+        </is>
+      </c>
+      <c r="L109" s="5" t="inlineStr">
+        <is>
+          <t>아크릴 굿즈는 국내 자체 생산하지만 기업 홍보 굿즈 카테고리 확장 시 아크릴 외 품목의 중국 소싱 파트너가 필요할 수 있다.</t>
+        </is>
+      </c>
+      <c r="M109" s="9" t="inlineStr">
+        <is>
+          <t>https://allthatprinting.co.kr/about.html</t>
+        </is>
+      </c>
+      <c r="N109" s="7" t="inlineStr"/>
+      <c r="O109" s="7" t="inlineStr"/>
+      <c r="P109" s="7" t="inlineStr"/>
+      <c r="Q109" s="7" t="inlineStr"/>
+      <c r="R109" s="7" t="inlineStr"/>
+      <c r="S109" s="7" t="inlineStr"/>
+      <c r="T109" s="7" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>기프트위키</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>https://giftwiki.kr/</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>1522-8992</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr"/>
+      <c r="H110" s="5" t="inlineStr"/>
+      <c r="I110" s="5" t="inlineStr"/>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>기념품·홍보용품 맞춤 제작 판촉물</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="inlineStr">
+        <is>
+          <t>불명(사이트 접근 차단으로 확인 불가)</t>
+        </is>
+      </c>
+      <c r="L110" s="5" t="inlineStr">
+        <is>
+          <t>기념품·홍보용품 맞춤 제작 판촉몰로 검색에 노출되나 취급 규모와 연락처를 확인하지 못해 우선순위는 낮음.</t>
+        </is>
+      </c>
+      <c r="M110" s="9" t="inlineStr">
+        <is>
+          <t>https://giftwiki.kr/</t>
+        </is>
+      </c>
+      <c r="N110" s="7" t="inlineStr"/>
+      <c r="O110" s="7" t="inlineStr"/>
+      <c r="P110" s="7" t="inlineStr"/>
+      <c r="Q110" s="7" t="inlineStr"/>
+      <c r="R110" s="7" t="inlineStr"/>
+      <c r="S110" s="7" t="inlineStr"/>
+      <c r="T110" s="7" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>딜리버리팩토리((주)커넥트어센드)</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>무역·소싱대행·수입도매</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>https://deliveryfactory.co.kr</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>070-8834-1001</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>mousy008@cscommerce.co.kr</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>https://deliveryfactory.co.kr/service</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>서울 서초구</t>
+        </is>
+      </c>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>중국수입대행, OEM제조, 식약처검사대행, 물류관리</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="inlineStr">
+        <is>
+          <t>강함(자체공장/지사)(중국공장 직수입·OEM 제조 서비스를 자체 운영)</t>
+        </is>
+      </c>
+      <c r="L111" s="5" t="inlineStr">
+        <is>
+          <t>중국공장 직수입·OEM 대행을 자체 서비스로 운영하는 직접 경쟁사로 외부 소싱 파트너 수요가 낮다.</t>
+        </is>
+      </c>
+      <c r="M111" s="9" t="inlineStr">
+        <is>
+          <t>https://deliveryfactory.co.kr/</t>
+        </is>
+      </c>
+      <c r="N111" s="7" t="inlineStr"/>
+      <c r="O111" s="7" t="inlineStr"/>
+      <c r="P111" s="7" t="inlineStr"/>
+      <c r="Q111" s="7" t="inlineStr"/>
+      <c r="R111" s="7" t="inlineStr"/>
+      <c r="S111" s="7" t="inlineStr"/>
+      <c r="T111" s="7" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="10" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>세인(SEIN)</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>무역·소싱대행·수입도매</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr"/>
+      <c r="F112" s="5" t="inlineStr"/>
+      <c r="G112" s="5" t="inlineStr"/>
+      <c r="H112" s="5" t="inlineStr"/>
+      <c r="I112" s="5" t="inlineStr"/>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>중국 완제품 소싱·구매대행, OEM 제작·생산관리, 검품·국제물류</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="inlineStr">
+        <is>
+          <t>강함(자체공장/지사)(중국 현지법인·한국지사 운영, 대표 중국 거주 26년)</t>
+        </is>
+      </c>
+      <c r="L112" s="5" t="inlineStr">
+        <is>
+          <t>중국 현지법인을 직접 운영하며 소싱·OEM·검품을 일괄 수행하는 직접 경쟁사다.</t>
+        </is>
+      </c>
+      <c r="M112" s="9" t="inlineStr">
+        <is>
+          <t>https://www.japantalk.net/free/?mod=document&amp;uid=5110</t>
+        </is>
+      </c>
+      <c r="N112" s="7" t="inlineStr"/>
+      <c r="O112" s="7" t="inlineStr"/>
+      <c r="P112" s="7" t="inlineStr"/>
+      <c r="Q112" s="7" t="inlineStr"/>
+      <c r="R112" s="7" t="inlineStr"/>
+      <c r="S112" s="7" t="inlineStr"/>
+      <c r="T112" s="7" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>소싱차이나</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>무역·소싱대행·수입도매</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>https://sourcingchina.co.kr</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr"/>
+      <c r="G113" s="5" t="inlineStr"/>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>https://sourcingchina.co.kr/</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr"/>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>중국수입대행, 굿즈제작(OEM), 의류사입, 안전인증 대행</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr">
+        <is>
+          <t>불명(중국 수입대행 전문이나 자체 지사 여부 미확인)</t>
+        </is>
+      </c>
+      <c r="L113" s="5" t="inlineStr">
+        <is>
+          <t>중국 수입대행·굿즈 OEM을 직접 수행하는 동종 경쟁사다.</t>
+        </is>
+      </c>
+      <c r="M113" s="9" t="inlineStr">
+        <is>
+          <t>https://sourcingchina.co.kr/go_01/</t>
+        </is>
+      </c>
+      <c r="N113" s="7" t="inlineStr"/>
+      <c r="O113" s="7" t="inlineStr"/>
+      <c r="P113" s="7" t="inlineStr"/>
+      <c r="Q113" s="7" t="inlineStr"/>
+      <c r="R113" s="7" t="inlineStr"/>
+      <c r="S113" s="7" t="inlineStr"/>
+      <c r="T113" s="7" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="10" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>이우허브</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>무역·소싱대행·수입도매</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>https://www.yiwuhub.net</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr"/>
+      <c r="G114" s="5" t="inlineStr"/>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>https://www.yiwuhub.net/34</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr"/>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>중국(이우) 수입대행, OEM</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t>불명(이우 기반 수입대행 표방, 자체 지사 여부 미확인)</t>
+        </is>
+      </c>
+      <c r="L114" s="5" t="inlineStr">
+        <is>
+          <t>이우 도매시장 기반 수입대행·OEM을 직접 제공하는 동종 경쟁사다.</t>
+        </is>
+      </c>
+      <c r="M114" s="9" t="inlineStr">
+        <is>
+          <t>https://www.yiwuhub.net/34</t>
+        </is>
+      </c>
+      <c r="N114" s="7" t="inlineStr"/>
+      <c r="O114" s="7" t="inlineStr"/>
+      <c r="P114" s="7" t="inlineStr"/>
+      <c r="Q114" s="7" t="inlineStr"/>
+      <c r="R114" s="7" t="inlineStr"/>
+      <c r="S114" s="7" t="inlineStr"/>
+      <c r="T114" s="7" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="10" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>홀세일차이나</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>무역·소싱대행·수입도매</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>https://wholesalechina.co.kr</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>070-8248-6654</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr"/>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>https://wholesalechina.co.kr/board/list/code/faq</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr"/>
+      <c r="J115" s="5" t="inlineStr">
+        <is>
+          <t>중국 구매대행, 시장조사, 수입대행, 배송대행(중국 현지 물류센터)</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="inlineStr">
+        <is>
+          <t>강함(자체공장/지사)(중국 현지 물류센터 운영 명시)</t>
+        </is>
+      </c>
+      <c r="L115" s="5" t="inlineStr">
+        <is>
+          <t>중국 현지 물류센터와 수입대행을 직접 운영하는 경쟁사로 외부 소싱망이 필요하지 않다.</t>
+        </is>
+      </c>
+      <c r="M115" s="9" t="inlineStr">
+        <is>
+          <t>https://wholesalechina.co.kr/agency/delivery</t>
+        </is>
+      </c>
+      <c r="N115" s="7" t="inlineStr"/>
+      <c r="O115" s="7" t="inlineStr"/>
+      <c r="P115" s="7" t="inlineStr"/>
+      <c r="Q115" s="7" t="inlineStr"/>
+      <c r="R115" s="7" t="inlineStr"/>
+      <c r="S115" s="7" t="inlineStr"/>
+      <c r="T115" s="7" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="10" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>드림토이</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>소규모 판촉물·패키징 중개벤더</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>http://www.dreamtoy.co.kr</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>02-896-2020</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr"/>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>http://www.dreamtoy.co.kr/sub03/sub01.php</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>서울 금천구</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t>캐릭터 인형 주문제작, 기업·방송사·이벤트사 OEM 인형 굿즈</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="inlineStr">
+        <is>
+          <t>강함(자체공장/지사) — 한국·중국 자체 공장 운영 명시</t>
+        </is>
+      </c>
+      <c r="L116" s="5" t="inlineStr">
+        <is>
+          <t>가산 인근 인형 OEM 업체이나 이미 중국 자체 공장을 보유해 소싱 대행 수요는 낮음.</t>
+        </is>
+      </c>
+      <c r="M116" s="9" t="inlineStr">
+        <is>
+          <t>https://dreamtoy.co.kr/</t>
+        </is>
+      </c>
+      <c r="N116" s="7" t="inlineStr"/>
+      <c r="O116" s="7" t="inlineStr"/>
+      <c r="P116" s="7" t="inlineStr"/>
+      <c r="Q116" s="7" t="inlineStr"/>
+      <c r="R116" s="7" t="inlineStr"/>
+      <c r="S116" s="7" t="inlineStr"/>
+      <c r="T116" s="7" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="10" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>(주)우정피앤피</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>제약·의료·치과 판촉물 벤더</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>https://www.wjung.com/</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>02-2285-1589</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>kind3000@hanmail.net</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>https://www.wjung.com/contact/guide.html</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>서울 중구</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>홍보물, 굿즈, 카탈로그·브로셔, 박스 패키지, 엽서, 소량 인쇄물</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr">
+        <is>
+          <t>약함 (서울 충무로 자체 인쇄소 보유, 중국 공장·지사 언급 없음)</t>
+        </is>
+      </c>
+      <c r="L117" s="5" t="inlineStr">
+        <is>
+          <t>임플란트·치과 홍보물 검색에 노출되는 인쇄 기반 홍보물·굿즈 제작사로 인쇄 외 굿즈 품목은 외주 소싱이 필요할 것으로 보임.</t>
+        </is>
+      </c>
+      <c r="M117" s="9" t="inlineStr">
+        <is>
+          <t>https://www.wjung.com/contact/guide.html</t>
+        </is>
+      </c>
+      <c r="N117" s="7" t="inlineStr"/>
+      <c r="O117" s="7" t="inlineStr"/>
+      <c r="P117" s="7" t="inlineStr"/>
+      <c r="Q117" s="7" t="inlineStr"/>
+      <c r="R117" s="7" t="inlineStr"/>
+      <c r="S117" s="7" t="inlineStr"/>
+      <c r="T117" s="7" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="10" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>세명사</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>제약·의료·치과 판촉물 벤더</t>
+        </is>
+      </c>
+      <c r="E118" s="9" t="inlineStr">
+        <is>
+          <t>https://www.sm1982.com/</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr"/>
+      <c r="G118" s="5" t="inlineStr"/>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sm1982.com/</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr"/>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>클립펜 주문제작, 다색볼펜·형광펜·메탈펜, 문구세트, 수첩, 기획상품</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>강함(자체공장/지사) 추정 (사이트에 중국 공장 생산 상품 및 국내제작사례 구분 표기)</t>
+        </is>
+      </c>
+      <c r="L118" s="5" t="inlineStr">
+        <is>
+          <t>제약사 판촉 단골인 클립펜 주문제작을 전문으로 하나 이미 중국 공장 생산 라인을 언급하고 있어 신규 소싱 수요는 제한적임.</t>
+        </is>
+      </c>
+      <c r="M118" s="9" t="inlineStr">
+        <is>
+          <t>https://www.sm1982.com/shop/item.php?it_id=00111658455335</t>
+        </is>
+      </c>
+      <c r="N118" s="7" t="inlineStr"/>
+      <c r="O118" s="7" t="inlineStr"/>
+      <c r="P118" s="7" t="inlineStr"/>
+      <c r="Q118" s="7" t="inlineStr"/>
+      <c r="R118" s="7" t="inlineStr"/>
+      <c r="S118" s="7" t="inlineStr"/>
+      <c r="T118" s="7" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>쿠디솜</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>캐릭터·IP·팬굿즈 기획사</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="inlineStr">
+        <is>
+          <t>https://www.qudisom.com/</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>1666-0211</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr"/>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>https://www.qudisom.com/ (고객 문의 게시판·주문 프로세스 페이지)</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>인천 남동구</t>
+        </is>
+      </c>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t>캐릭터 인형·봉제 아이템, 캐릭터 굿즈, KC인증 대행</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="inlineStr">
+        <is>
+          <t>강함(자체공장/지사)(항저우·양저우·웨이팡 직영 공장 주소 공개, 중간 유통 없이 직접 생산)</t>
+        </is>
+      </c>
+      <c r="L119" s="5" t="inlineStr">
+        <is>
+          <t>중국 직영 공장 3곳 이상을 운영하는 구조라 외부 중국 소싱 파트너 필요성이 낮고 오히려 경쟁사에 가깝다.</t>
+        </is>
+      </c>
+      <c r="M119" s="9" t="inlineStr">
+        <is>
+          <t>https://www.qudisom.com/ ; https://www.qudisom.com/sewingorder</t>
+        </is>
+      </c>
+      <c r="N119" s="7" t="inlineStr"/>
+      <c r="O119" s="7" t="inlineStr"/>
+      <c r="P119" s="7" t="inlineStr"/>
+      <c r="Q119" s="7" t="inlineStr"/>
+      <c r="R119" s="7" t="inlineStr"/>
+      <c r="S119" s="7" t="inlineStr"/>
+      <c r="T119" s="7" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="10" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>팔팔토이(88TOY)</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>캐릭터·IP·팬굿즈 기획사 · 소규모 판촉물·패키징 중개벤더</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>http://www.88toy.co.kr/</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>02-6052-0150</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>pp.88toy@gmail.com</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>http://www.88toy.co.kr/ABOUTOEM (제작문의 게시판 후 이메일 접수)</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>서울 구로구</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>캐릭터 봉제인형 OEM(샘플 1개~10만개), 인형 부자재·라벨 / 캐릭터 인형·봉제 굿즈 OEM, 소량 샘플~대량 제작</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>강함(자체공장/지사)(중국 청도 공장과 독점계약해 자사 제품만 생산, 서울 항동 샘플개발실 운영)</t>
+        </is>
+      </c>
+      <c r="L120" s="5" t="inlineStr">
+        <is>
+          <t>이미 청도 독점 공장을 확보한 인형 제조사로 인형 외 품목(피규어·잡화) 소싱이 아니면 외부 중국 파트너 수요가 낮다. / 구로 소재 소규모 인형·캐릭터 굿즈 OEM 창구로 기업 IP 굿즈 발주를 받아 해외 생산을 병행하는 업체.</t>
+        </is>
+      </c>
+      <c r="M120" s="9" t="inlineStr">
+        <is>
+          <t>http://www.88toy.co.kr/ABOUTOEM ; http://www.88toy.co.kr/183</t>
+        </is>
+      </c>
+      <c r="N120" s="7" t="inlineStr"/>
+      <c r="O120" s="7" t="inlineStr"/>
+      <c r="P120" s="7" t="inlineStr"/>
+      <c r="Q120" s="7" t="inlineStr"/>
+      <c r="R120" s="7" t="inlineStr"/>
+      <c r="S120" s="7" t="inlineStr"/>
+      <c r="T120" s="7" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>고굿즈(GOGOODS)</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>판촉물·굿즈 제작대행사</t>
+        </is>
+      </c>
+      <c r="E121" s="9" t="inlineStr">
+        <is>
+          <t>https://gogoods.kr/</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr"/>
+      <c r="G121" s="5" t="inlineStr"/>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>https://gogoods.kr/manufacturing (제작·소싱 문의)</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr"/>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>굿즈·패션잡화 OEM/ODM, 중국 공장 소싱, 구매대행</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="inlineStr">
+        <is>
+          <t>강함(자체공장/지사)(이우 지사, 심천/동관 지사 운영 및 현지 검수·A/S 명시)</t>
+        </is>
+      </c>
+      <c r="L121" s="5" t="inlineStr">
+        <is>
+          <t>중국 이우·심천·동관 지사를 직접 운영하는 소싱형 업체라 외부 중국 소싱 파트너가 필요하지 않고 오히려 경쟁사에 가깝다.</t>
+        </is>
+      </c>
+      <c r="M121" s="9" t="inlineStr">
+        <is>
+          <t>https://gogoods.kr/manufacturing</t>
+        </is>
+      </c>
+      <c r="N121" s="7" t="inlineStr"/>
+      <c r="O121" s="7" t="inlineStr"/>
+      <c r="P121" s="7" t="inlineStr"/>
+      <c r="Q121" s="7" t="inlineStr"/>
+      <c r="R121" s="7" t="inlineStr"/>
+      <c r="S121" s="7" t="inlineStr"/>
+      <c r="T121" s="7" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>판촉사랑</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>판촉물·굿즈 제작대행사 · 관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
+        </is>
+      </c>
+      <c r="E122" s="9" t="inlineStr">
+        <is>
+          <t>https://www.87sarang.com/</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>1688-8744</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>gift@87sarang.com</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>https://www.87sarang.com/co/contact2.html (질문과답변/견적문의)</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>인천 남동구</t>
+        </is>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>기업 판촉물, 답례품, 기념품, 홍보물(자체 인쇄시설 보유) / 기업·금융권·공공기관 판촉물, 답례품, 기념품 (전국 지역별 판촉사랑 분점망 운영)</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="inlineStr">
+        <is>
+          <t>강함(자체공장/지사)(회사소개에 중국지사 보유 및 디자인연구소·자체 인쇄시설 명시)</t>
+        </is>
+      </c>
+      <c r="L122" s="5" t="inlineStr">
+        <is>
+          <t>중국지사와 자체 인쇄시설을 갖춘 판촉물 전문기업이라 외부 중국 소싱 파트너 필요성이 낮다. / 서울·부산·경남·전남·제주 등 전국 지역 분점망을 갖추고 업종별(금융권 포함) 납품사례를 공개하는 규모 있는 업체로 다품종 대량 소싱 파트너 수요가 클 것으로 판단됨.</t>
+        </is>
+      </c>
+      <c r="M122" s="9" t="inlineStr">
+        <is>
+          <t>https://www.87sarang.com/co/company2.html</t>
+        </is>
+      </c>
+      <c r="N122" s="7" t="inlineStr"/>
+      <c r="O122" s="7" t="inlineStr"/>
+      <c r="P122" s="7" t="inlineStr"/>
+      <c r="Q122" s="7" t="inlineStr"/>
+      <c r="R122" s="7" t="inlineStr"/>
+      <c r="S122" s="7" t="inlineStr"/>
+      <c r="T122" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T104"/>
+  <autoFilter ref="A1:T122"/>
   <dataValidations count="2">
-    <dataValidation sqref="Q2:Q104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q122" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"통화,메일발송,관심,견적요청,거절,부재,재연락"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O122" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"전화,이메일,홈페이지문의,카톡채널,방문"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7976,21 +9176,57 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M95" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId179"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M106" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M107" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M108" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M109" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M110" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M111" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M112" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M113" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M114" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M115" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M116" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M117" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M118" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M119" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M120" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M121" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId231"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -8003,7 +9239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8066,27 +9302,27 @@
         </is>
       </c>
       <c r="B3" s="13">
-        <f>COUNTIF(영업리스트!$D$2:$D$403,A3)</f>
+        <f>COUNTIF(영업리스트!$D$2:$D$421,A3)</f>
         <v/>
       </c>
       <c r="C3" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A3,영업리스트!$B$2:$B$403,"상")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A3,영업리스트!$B$2:$B$421,"상")</f>
         <v/>
       </c>
       <c r="D3" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A3,영업리스트!$B$2:$B$403,"중")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A3,영업리스트!$B$2:$B$421,"중")</f>
         <v/>
       </c>
       <c r="E3" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A3,영업리스트!$B$2:$B$403,"하")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A3,영업리스트!$B$2:$B$421,"하")</f>
         <v/>
       </c>
       <c r="F3" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A3,영업리스트!$Q$2:$Q$403,"&lt;&gt;")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A3,영업리스트!$Q$2:$Q$421,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="G3" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A3,영업리스트!$Q$2:$Q$403,"관심")+COUNTIFS(영업리스트!$D$2:$D$403,A3,영업리스트!$Q$2:$Q$403,"견적요청")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A3,영업리스트!$Q$2:$Q$421,"관심")+COUNTIFS(영업리스트!$D$2:$D$421,A3,영업리스트!$Q$2:$Q$421,"견적요청")</f>
         <v/>
       </c>
     </row>
@@ -8097,27 +9333,27 @@
         </is>
       </c>
       <c r="B4" s="13">
-        <f>COUNTIF(영업리스트!$D$2:$D$403,A4)</f>
+        <f>COUNTIF(영업리스트!$D$2:$D$421,A4)</f>
         <v/>
       </c>
       <c r="C4" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A4,영업리스트!$B$2:$B$403,"상")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A4,영업리스트!$B$2:$B$421,"상")</f>
         <v/>
       </c>
       <c r="D4" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A4,영업리스트!$B$2:$B$403,"중")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A4,영업리스트!$B$2:$B$421,"중")</f>
         <v/>
       </c>
       <c r="E4" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A4,영업리스트!$B$2:$B$403,"하")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A4,영업리스트!$B$2:$B$421,"하")</f>
         <v/>
       </c>
       <c r="F4" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A4,영업리스트!$Q$2:$Q$403,"&lt;&gt;")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A4,영업리스트!$Q$2:$Q$421,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="G4" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A4,영업리스트!$Q$2:$Q$403,"관심")+COUNTIFS(영업리스트!$D$2:$D$403,A4,영업리스트!$Q$2:$Q$403,"견적요청")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A4,영업리스트!$Q$2:$Q$421,"관심")+COUNTIFS(영업리스트!$D$2:$D$421,A4,영업리스트!$Q$2:$Q$421,"견적요청")</f>
         <v/>
       </c>
     </row>
@@ -8128,27 +9364,27 @@
         </is>
       </c>
       <c r="B5" s="13">
-        <f>COUNTIF(영업리스트!$D$2:$D$403,A5)</f>
+        <f>COUNTIF(영업리스트!$D$2:$D$421,A5)</f>
         <v/>
       </c>
       <c r="C5" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A5,영업리스트!$B$2:$B$403,"상")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A5,영업리스트!$B$2:$B$421,"상")</f>
         <v/>
       </c>
       <c r="D5" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A5,영업리스트!$B$2:$B$403,"중")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A5,영업리스트!$B$2:$B$421,"중")</f>
         <v/>
       </c>
       <c r="E5" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A5,영업리스트!$B$2:$B$403,"하")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A5,영업리스트!$B$2:$B$421,"하")</f>
         <v/>
       </c>
       <c r="F5" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A5,영업리스트!$Q$2:$Q$403,"&lt;&gt;")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A5,영업리스트!$Q$2:$Q$421,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="G5" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A5,영업리스트!$Q$2:$Q$403,"관심")+COUNTIFS(영업리스트!$D$2:$D$403,A5,영업리스트!$Q$2:$Q$403,"견적요청")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A5,영업리스트!$Q$2:$Q$421,"관심")+COUNTIFS(영업리스트!$D$2:$D$421,A5,영업리스트!$Q$2:$Q$421,"견적요청")</f>
         <v/>
       </c>
     </row>
@@ -8159,340 +9395,433 @@
         </is>
       </c>
       <c r="B6" s="13">
-        <f>COUNTIF(영업리스트!$D$2:$D$403,A6)</f>
+        <f>COUNTIF(영업리스트!$D$2:$D$421,A6)</f>
         <v/>
       </c>
       <c r="C6" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A6,영업리스트!$B$2:$B$403,"상")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A6,영업리스트!$B$2:$B$421,"상")</f>
         <v/>
       </c>
       <c r="D6" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A6,영업리스트!$B$2:$B$403,"중")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A6,영업리스트!$B$2:$B$421,"중")</f>
         <v/>
       </c>
       <c r="E6" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A6,영업리스트!$B$2:$B$403,"하")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A6,영업리스트!$B$2:$B$421,"하")</f>
         <v/>
       </c>
       <c r="F6" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A6,영업리스트!$Q$2:$Q$403,"&lt;&gt;")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A6,영업리스트!$Q$2:$Q$421,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="G6" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A6,영업리스트!$Q$2:$Q$403,"관심")+COUNTIFS(영업리스트!$D$2:$D$403,A6,영업리스트!$Q$2:$Q$403,"견적요청")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A6,영업리스트!$Q$2:$Q$421,"관심")+COUNTIFS(영업리스트!$D$2:$D$421,A6,영업리스트!$Q$2:$Q$421,"견적요청")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>스포츠·헬스·재활용품 유통사/OEM브랜드</t>
+          <t>소규모 판촉물·패키징 중개벤더</t>
         </is>
       </c>
       <c r="B7" s="13">
-        <f>COUNTIF(영업리스트!$D$2:$D$403,A7)</f>
+        <f>COUNTIF(영업리스트!$D$2:$D$421,A7)</f>
         <v/>
       </c>
       <c r="C7" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A7,영업리스트!$B$2:$B$403,"상")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A7,영업리스트!$B$2:$B$421,"상")</f>
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A7,영업리스트!$B$2:$B$403,"중")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A7,영업리스트!$B$2:$B$421,"중")</f>
         <v/>
       </c>
       <c r="E7" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A7,영업리스트!$B$2:$B$403,"하")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A7,영업리스트!$B$2:$B$421,"하")</f>
         <v/>
       </c>
       <c r="F7" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A7,영업리스트!$Q$2:$Q$403,"&lt;&gt;")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A7,영업리스트!$Q$2:$Q$421,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="G7" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A7,영업리스트!$Q$2:$Q$403,"관심")+COUNTIFS(영업리스트!$D$2:$D$403,A7,영업리스트!$Q$2:$Q$403,"견적요청")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A7,영업리스트!$Q$2:$Q$421,"관심")+COUNTIFS(영업리스트!$D$2:$D$421,A7,영업리스트!$Q$2:$Q$421,"견적요청")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>캐릭터·IP·팬굿즈 기획사</t>
+          <t>스포츠·헬스·재활용품 유통사/OEM브랜드</t>
         </is>
       </c>
       <c r="B8" s="13">
-        <f>COUNTIF(영업리스트!$D$2:$D$403,A8)</f>
+        <f>COUNTIF(영업리스트!$D$2:$D$421,A8)</f>
         <v/>
       </c>
       <c r="C8" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A8,영업리스트!$B$2:$B$403,"상")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A8,영업리스트!$B$2:$B$421,"상")</f>
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A8,영업리스트!$B$2:$B$403,"중")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A8,영업리스트!$B$2:$B$421,"중")</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A8,영업리스트!$B$2:$B$403,"하")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A8,영업리스트!$B$2:$B$421,"하")</f>
         <v/>
       </c>
       <c r="F8" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A8,영업리스트!$Q$2:$Q$403,"&lt;&gt;")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A8,영업리스트!$Q$2:$Q$421,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="G8" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A8,영업리스트!$Q$2:$Q$403,"관심")+COUNTIFS(영업리스트!$D$2:$D$403,A8,영업리스트!$Q$2:$Q$403,"견적요청")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A8,영업리스트!$Q$2:$Q$421,"관심")+COUNTIFS(영업리스트!$D$2:$D$421,A8,영업리스트!$Q$2:$Q$421,"견적요청")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>캐릭터·IP·팬굿즈 기획사 · 판촉물·굿즈 제작대행사</t>
+          <t>제약·의료·치과 판촉물 벤더</t>
         </is>
       </c>
       <c r="B9" s="13">
-        <f>COUNTIF(영업리스트!$D$2:$D$403,A9)</f>
+        <f>COUNTIF(영업리스트!$D$2:$D$421,A9)</f>
         <v/>
       </c>
       <c r="C9" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A9,영업리스트!$B$2:$B$403,"상")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A9,영업리스트!$B$2:$B$421,"상")</f>
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A9,영업리스트!$B$2:$B$403,"중")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A9,영업리스트!$B$2:$B$421,"중")</f>
         <v/>
       </c>
       <c r="E9" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A9,영업리스트!$B$2:$B$403,"하")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A9,영업리스트!$B$2:$B$421,"하")</f>
         <v/>
       </c>
       <c r="F9" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A9,영업리스트!$Q$2:$Q$403,"&lt;&gt;")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A9,영업리스트!$Q$2:$Q$421,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="G9" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A9,영업리스트!$Q$2:$Q$403,"관심")+COUNTIFS(영업리스트!$D$2:$D$403,A9,영업리스트!$Q$2:$Q$403,"견적요청")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A9,영업리스트!$Q$2:$Q$421,"관심")+COUNTIFS(영업리스트!$D$2:$D$421,A9,영업리스트!$Q$2:$Q$421,"견적요청")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>판촉물·굿즈 제작대행사</t>
+          <t>캐릭터·IP·팬굿즈 기획사</t>
         </is>
       </c>
       <c r="B10" s="13">
-        <f>COUNTIF(영업리스트!$D$2:$D$403,A10)</f>
+        <f>COUNTIF(영업리스트!$D$2:$D$421,A10)</f>
         <v/>
       </c>
       <c r="C10" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A10,영업리스트!$B$2:$B$403,"상")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A10,영업리스트!$B$2:$B$421,"상")</f>
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A10,영업리스트!$B$2:$B$403,"중")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A10,영업리스트!$B$2:$B$421,"중")</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A10,영업리스트!$B$2:$B$403,"하")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A10,영업리스트!$B$2:$B$421,"하")</f>
         <v/>
       </c>
       <c r="F10" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A10,영업리스트!$Q$2:$Q$403,"&lt;&gt;")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A10,영업리스트!$Q$2:$Q$421,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="G10" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A10,영업리스트!$Q$2:$Q$403,"관심")+COUNTIFS(영업리스트!$D$2:$D$403,A10,영업리스트!$Q$2:$Q$403,"견적요청")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A10,영업리스트!$Q$2:$Q$421,"관심")+COUNTIFS(영업리스트!$D$2:$D$421,A10,영업리스트!$Q$2:$Q$421,"견적요청")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>판촉물·굿즈 제작대행사 · 관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
+          <t>캐릭터·IP·팬굿즈 기획사 · 소규모 판촉물·패키징 중개벤더</t>
         </is>
       </c>
       <c r="B11" s="13">
-        <f>COUNTIF(영업리스트!$D$2:$D$403,A11)</f>
+        <f>COUNTIF(영업리스트!$D$2:$D$421,A11)</f>
         <v/>
       </c>
       <c r="C11" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A11,영업리스트!$B$2:$B$403,"상")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A11,영업리스트!$B$2:$B$421,"상")</f>
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A11,영업리스트!$B$2:$B$403,"중")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A11,영업리스트!$B$2:$B$421,"중")</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A11,영업리스트!$B$2:$B$403,"하")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A11,영업리스트!$B$2:$B$421,"하")</f>
         <v/>
       </c>
       <c r="F11" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A11,영업리스트!$Q$2:$Q$403,"&lt;&gt;")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A11,영업리스트!$Q$2:$Q$421,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="G11" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A11,영업리스트!$Q$2:$Q$403,"관심")+COUNTIFS(영업리스트!$D$2:$D$403,A11,영업리스트!$Q$2:$Q$403,"견적요청")</f>
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A11,영업리스트!$Q$2:$Q$421,"관심")+COUNTIFS(영업리스트!$D$2:$D$421,A11,영업리스트!$Q$2:$Q$421,"견적요청")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
+          <t>캐릭터·IP·팬굿즈 기획사 · 판촉물·굿즈 제작대행사</t>
+        </is>
+      </c>
+      <c r="B12" s="13">
+        <f>COUNTIF(영업리스트!$D$2:$D$421,A12)</f>
+        <v/>
+      </c>
+      <c r="C12" s="13">
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A12,영업리스트!$B$2:$B$421,"상")</f>
+        <v/>
+      </c>
+      <c r="D12" s="13">
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A12,영업리스트!$B$2:$B$421,"중")</f>
+        <v/>
+      </c>
+      <c r="E12" s="13">
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A12,영업리스트!$B$2:$B$421,"하")</f>
+        <v/>
+      </c>
+      <c r="F12" s="13">
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A12,영업리스트!$Q$2:$Q$421,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="G12" s="13">
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A12,영업리스트!$Q$2:$Q$421,"관심")+COUNTIFS(영업리스트!$D$2:$D$421,A12,영업리스트!$Q$2:$Q$421,"견적요청")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>판촉물·굿즈 제작대행사</t>
+        </is>
+      </c>
+      <c r="B13" s="13">
+        <f>COUNTIF(영업리스트!$D$2:$D$421,A13)</f>
+        <v/>
+      </c>
+      <c r="C13" s="13">
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A13,영업리스트!$B$2:$B$421,"상")</f>
+        <v/>
+      </c>
+      <c r="D13" s="13">
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A13,영업리스트!$B$2:$B$421,"중")</f>
+        <v/>
+      </c>
+      <c r="E13" s="13">
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A13,영업리스트!$B$2:$B$421,"하")</f>
+        <v/>
+      </c>
+      <c r="F13" s="13">
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A13,영업리스트!$Q$2:$Q$421,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="G13" s="13">
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A13,영업리스트!$Q$2:$Q$421,"관심")+COUNTIFS(영업리스트!$D$2:$D$421,A13,영업리스트!$Q$2:$Q$421,"견적요청")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>판촉물·굿즈 제작대행사 · 관공서·학교·금융·프랜차이즈 판촉 납품업체</t>
+        </is>
+      </c>
+      <c r="B14" s="13">
+        <f>COUNTIF(영업리스트!$D$2:$D$421,A14)</f>
+        <v/>
+      </c>
+      <c r="C14" s="13">
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A14,영업리스트!$B$2:$B$421,"상")</f>
+        <v/>
+      </c>
+      <c r="D14" s="13">
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A14,영업리스트!$B$2:$B$421,"중")</f>
+        <v/>
+      </c>
+      <c r="E14" s="13">
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A14,영업리스트!$B$2:$B$421,"하")</f>
+        <v/>
+      </c>
+      <c r="F14" s="13">
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A14,영업리스트!$Q$2:$Q$421,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="G14" s="13">
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A14,영업리스트!$Q$2:$Q$421,"관심")+COUNTIFS(영업리스트!$D$2:$D$421,A14,영업리스트!$Q$2:$Q$421,"견적요청")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
           <t>회수 대상(前 파트너 거래처)</t>
         </is>
       </c>
-      <c r="B12" s="13">
-        <f>COUNTIF(영업리스트!$D$2:$D$403,A12)</f>
+      <c r="B15" s="13">
+        <f>COUNTIF(영업리스트!$D$2:$D$421,A15)</f>
         <v/>
       </c>
-      <c r="C12" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A12,영업리스트!$B$2:$B$403,"상")</f>
+      <c r="C15" s="13">
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A15,영업리스트!$B$2:$B$421,"상")</f>
         <v/>
       </c>
-      <c r="D12" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A12,영업리스트!$B$2:$B$403,"중")</f>
+      <c r="D15" s="13">
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A15,영업리스트!$B$2:$B$421,"중")</f>
         <v/>
       </c>
-      <c r="E12" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A12,영업리스트!$B$2:$B$403,"하")</f>
+      <c r="E15" s="13">
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A15,영업리스트!$B$2:$B$421,"하")</f>
         <v/>
       </c>
-      <c r="F12" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A12,영업리스트!$Q$2:$Q$403,"&lt;&gt;")</f>
+      <c r="F15" s="13">
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A15,영업리스트!$Q$2:$Q$421,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="G12" s="13">
-        <f>COUNTIFS(영업리스트!$D$2:$D$403,A12,영업리스트!$Q$2:$Q$403,"관심")+COUNTIFS(영업리스트!$D$2:$D$403,A12,영업리스트!$Q$2:$Q$403,"견적요청")</f>
+      <c r="G15" s="13">
+        <f>COUNTIFS(영업리스트!$D$2:$D$421,A15,영업리스트!$Q$2:$Q$421,"관심")+COUNTIFS(영업리스트!$D$2:$D$421,A15,영업리스트!$Q$2:$Q$421,"견적요청")</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B13" s="14">
-        <f>SUM(B3:B12)</f>
+      <c r="B16" s="14">
+        <f>SUM(B3:B15)</f>
         <v/>
       </c>
-      <c r="C13" s="14">
-        <f>SUM(C3:C12)</f>
+      <c r="C16" s="14">
+        <f>SUM(C3:C15)</f>
         <v/>
       </c>
-      <c r="D13" s="14">
-        <f>SUM(D3:D12)</f>
+      <c r="D16" s="14">
+        <f>SUM(D3:D15)</f>
         <v/>
       </c>
-      <c r="E13" s="14">
-        <f>SUM(E3:E12)</f>
+      <c r="E16" s="14">
+        <f>SUM(E3:E15)</f>
         <v/>
       </c>
-      <c r="F13" s="14">
-        <f>SUM(F3:F12)</f>
+      <c r="F16" s="14">
+        <f>SUM(F3:F15)</f>
         <v/>
       </c>
-      <c r="G13" s="14">
-        <f>SUM(G3:G12)</f>
+      <c r="G16" s="14">
+        <f>SUM(G3:G15)</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>연락결과 현황</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>결과</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>건수</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>통화</t>
-        </is>
-      </c>
-      <c r="B17" s="2">
-        <f>COUNTIF(영업리스트!$Q$2:$Q$403,A17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>메일발송</t>
-        </is>
-      </c>
-      <c r="B18" s="2">
-        <f>COUNTIF(영업리스트!$Q$2:$Q$403,A18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>관심</t>
-        </is>
-      </c>
-      <c r="B19" s="2">
-        <f>COUNTIF(영업리스트!$Q$2:$Q$403,A19)</f>
-        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>견적요청</t>
+          <t>통화</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <f>COUNTIF(영업리스트!$Q$2:$Q$403,A20)</f>
+        <f>COUNTIF(영업리스트!$Q$2:$Q$421,A20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>거절</t>
+          <t>메일발송</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <f>COUNTIF(영업리스트!$Q$2:$Q$403,A21)</f>
+        <f>COUNTIF(영업리스트!$Q$2:$Q$421,A21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>부재</t>
+          <t>관심</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <f>COUNTIF(영업리스트!$Q$2:$Q$403,A22)</f>
+        <f>COUNTIF(영업리스트!$Q$2:$Q$421,A22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>견적요청</t>
+        </is>
+      </c>
+      <c r="B23" s="2">
+        <f>COUNTIF(영업리스트!$Q$2:$Q$421,A23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>거절</t>
+        </is>
+      </c>
+      <c r="B24" s="2">
+        <f>COUNTIF(영업리스트!$Q$2:$Q$421,A24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>부재</t>
+        </is>
+      </c>
+      <c r="B25" s="2">
+        <f>COUNTIF(영업리스트!$Q$2:$Q$421,A25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>재연락</t>
         </is>
       </c>
-      <c r="B23" s="2">
-        <f>COUNTIF(영업리스트!$Q$2:$Q$403,A23)</f>
+      <c r="B26" s="2">
+        <f>COUNTIF(영업리스트!$Q$2:$Q$421,A26)</f>
         <v/>
       </c>
     </row>

--- a/영업/B2B_영업리스트.xlsx
+++ b/영업/B2B_영업리스트.xlsx
@@ -10499,7 +10499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10509,130 +10509,154 @@
     <row r="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>전화 첫 멘트</t>
+          <t>포지션 한 줄</t>
         </is>
       </c>
       <c r="B1" s="17" t="inlineStr">
         <is>
-          <t>안녕하세요, 올투게더나우 대표 ○○○입니다. 저희는 무릎·허리 보호대를 중국과 한국에서 직접 기획·제조해서 네이버·쿠팡에 판매하는 회사이고, 수출입 사업자를 갖고 있습니다. 귀사에서 굿즈나 판촉물 제작하실 때 중국 생산이 들어가는 품목이 있으면, 공장 발굴부터 샘플, 가격협상, 생산, 검수, 국내 입고까지 저희가 한 번에 맡아드릴 수 있어서 연락드렸습니다. 구매 담당 부서로 연결 가능할까요?</t>
+          <t>품목에 상관없이, 한국에서 필요한 제품과 사양만 주시면 중국 현지 제조공장 발굴 → 샘플 → 가격협상 → 생산 → 검수 → 통관·국내 납품까지 한 번에 연결하는 회사. (보호대는 '우리가 실제로 중국에서 만들어 팔고 있다'는 증거로만 언급)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>핵심 차별점</t>
+          <t>전화 첫 멘트</t>
         </is>
       </c>
       <c r="B2" s="17" t="inlineStr">
         <is>
-          <t>1) 단순 구매대행이 아니라 중국 현지 제조 파트너가 직접 공장을 찾고 생산을 관리합니다. 2) 저희가 실제로 자사 제품을 중국에서 만들어 팔고 있어서 품질·납기 사고를 직접 겪어본 경험이 있습니다. 3) 수출입 사업자로 세금계산서 발행, 통관, KC 인증 안내까지 국내에서 처리합니다.</t>
+          <t>안녕하세요, 올투게더나우 대표 ○○○입니다. 저희는 중국 현지 제조 파트너와 함께 굿즈·판촉물·패키지·생활용품·봉제·전자소품 등 품목 가리지 않고 공장 발굴부터 샘플, 생산, 검수, 국내 입고까지 한 번에 진행하는 회사입니다. 저희 자체 제품도 같은 방식으로 중국에서 만들어 네이버·쿠팡에서 팔고 있어서 품질·납기 관리는 직접 겪어본 경험이 있습니다. 귀사에서 중국 생산이 들어가는 건이 있으면 견적 비교부터 도와드리고 싶은데, 구매 담당 부서로 연결 가능할까요?</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>이메일 제목</t>
+          <t>핵심 차별점</t>
         </is>
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>[제안] 굿즈·판촉물 중국 OEM 생산 대행 (공장 발굴~검수~입고 원스톱) - 올투게더나우</t>
+          <t>1) 단순 구매대행이 아니라 중국 현지 제조 파트너가 직접 공장을 찾고 생산을 관리. 2) 품목 제한 없음: 인쇄물·잡화·봉제·사출·금속·패키지·전자소품까지 공장 네트워크로 대응. 3) 저희도 자체 제품을 중국에서 만들어 파는 회사라 사고 유형(불량, 납기, 인증)을 알고 미리 막음. 4) 수출입 사업자로 세금계산서 발행, 통관, KC 인증 안내까지 국내에서 처리.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
+          <t>이메일 제목</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>[제안] 중국 OEM 생산 원스톱 대행 (공장 발굴~검수~국내 납품, 품목 무관) - 올투게더나우</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
           <t>이메일 본문</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>안녕하세요, 올투게더나우 대표 ○○○입니다.
-저희는 신체 보호대(무릎·팔꿈치·손목·허리)를 중국·한국에서 기획·제조하여 네이버 스마트스토어와 쿠팡에서 판매하고 있으며, 수출입 사업자를 보유하고 있습니다.
-귀사에서 고객사 굿즈·판촉물·기념품 제작 시 중국 생산이 필요한 품목이 있으시면, 아래 과정을 저희가 원스톱으로 진행해 드립니다.
-1. 필요한 제품·사양·수량·예산만 알려주시면 중국 현지 파트너가 제조공장을 발굴
+저희는 중국 현지 제조 파트너와 함께, 품목에 상관없이 중국 생산이 필요한 제품을 아래 과정으로 원스톱 진행해 드립니다.
+1. 제품·사양·수량·예산만 알려주시면 중국 현지 파트너가 제조공장을 발굴
 2. 샘플 제작 및 국내 발송
 3. 가격 협상 및 견적서 제출
 4. 생산 진행 및 출하 전 검수 (사진·영상 보고)
 5. 통관 후 국내 지정 장소 납품, 세금계산서 발행
-부담 없이 진행 중인 건 하나로 견적 비교부터 해보셔도 좋습니다.
-연락 주시면 바로 찾아뵙고 설명드리겠습니다.
+대응 품목: 판촉물·굿즈(인쇄, 아크릴, 금속, 봉제, 사출), 패키지(박스·쇼핑백·파우치), 생활용품·주방용품, 스포츠·헬스용품, 전자소품(보조배터리·케이블 등) 외 다수.
+저희 자체 브랜드 제품도 같은 방식으로 중국에서 생산해 네이버·쿠팡에서 판매 중이라, 품질·납기 관리는 직접 겪어본 노하우로 진행합니다.
+진행 중인 건 하나로 견적 비교부터 해보셔도 좋습니다. 연락 주시면 바로 찾아뵙고 설명드리겠습니다.
 올투게더나우 대표 ○○○ / 전화 000-0000-0000 / 이메일 ○○○@○○○</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>예상 질문 1</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>Q. 이미 거래하는 중국 공장이 있는데요? → A. 그러면 견적 비교용으로만 한 건 받아보세요. 같은 사양으로 저희 견적이 더 낮거나 납기가 빠르면 그때 바꾸시면 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>예상 질문 2</t>
+          <t>예상 질문 1</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>Q. 소량도 되나요? → A. 품목별로 다르지만 300~500개부터 가능한 공장을 찾아드립니다. 우선 사양 주시면 MOQ부터 확인해 드릴게요.</t>
+          <t>Q. 이미 거래하는 중국 공장이 있는데요? → A. 그러면 견적 비교용으로만 한 건 받아보세요. 같은 사양으로 저희 견적이 더 낮거나 납기가 빠르면 그때 바꾸시면 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>예상 질문 3</t>
+          <t>예상 질문 2</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Q. 불량 나면 어떻게 하나요? → A. 출하 전 검수 사진·영상을 보내드리고, 검수 통과 후에만 출고합니다. 계약서에 불량 시 재생산 조건을 명시합니다.</t>
+          <t>Q. 소량도 되나요? → A. 품목별로 다르지만 300~500개부터 가능한 공장을 찾아드립니다. 우선 사양 주시면 MOQ부터 확인해 드릴게요.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>회수 대상 멘트</t>
+          <t>예상 질문 3</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>안녕하세요, 올투게더나우 ○○○ 대표입니다. 그동안 함석민 님을 통해 진행하셨던 중국 생산 건(예: 클립펜·온습도계, 캐릭터 굿즈)은 실제로는 저희 중국 파트너 리자위 공장에서 만들어졌습니다. 현재 함석민 님과는 거래가 정리되어, 앞으로는 저희가 한국 창구를 맡아 같은 공장·같은 품질로 직접 진행해 드립니다. 중간 단계가 하나 빠지는 만큼 단가와 소통 속도 모두 유리합니다. 진행 중이거나 예정된 건 있으시면 바로 견적 드리겠습니다.</t>
+          <t>Q. 불량 나면 어떻게 하나요? → A. 출하 전 검수 사진·영상을 보내드리고, 검수 통과 후에만 출고합니다. 계약서에 불량 시 재생산 조건을 명시합니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>회수 대상 주의</t>
+          <t>예상 질문 4</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>1) 前 파트너 험담은 하지 말고 '거래가 정리됐다'까지만. 2) 상대가 함석민과 계속 거래 중일 수 있으니 첫 통화는 탐색 위주로. 3) 과거 생산 사진·샘플을 리자위에게 미리 받아두면 '같은 공장' 증명이 바로 됩니다. 4) 개인 휴대폰보다 회사 번호·메일로 먼저 연락.</t>
+          <t>Q. 무슨 품목까지 되나요? → A. 저희가 하는 건 특정 제품이 아니라 '공장을 찾아 생산을 관리하는 일'이라 품목 제한이 없습니다. 지금 진행 중인 품목 말씀해 주시면 그 공장부터 찾아드립니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
+          <t>회수 대상 멘트</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>안녕하세요, 올투게더나우 ○○○ 대표입니다. 그동안 함석민 님을 통해 진행하셨던 중국 생산 건(예: 클립펜·온습도계, 캐릭터 굿즈, 패키지 박스)은 실제로는 저희 중국 파트너 리자위 공장에서 만들어졌습니다. 현재 함석민 님과는 거래가 정리되어, 앞으로는 저희가 한국 창구를 맡아 같은 공장·같은 품질로 직접 진행해 드립니다. 중간 단계가 하나 빠지는 만큼 단가와 소통 속도 모두 유리합니다. 진행 중이거나 예정된 건 있으시면 바로 견적 드리겠습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>회수 대상 주의</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>1) 前 파트너 험담은 하지 말고 '거래가 정리됐다'까지만. 2) 상대가 함석민과 계속 거래 중일 수 있으니 첫 통화는 탐색 위주로. 3) 과거 생산 사진·샘플을 리자위에게 미리 받아두면 '같은 공장' 증명이 바로 됩니다. 4) 개인 휴대폰보다 회사 번호·메일로 먼저 연락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
           <t>후속 조치</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>통화 후 24시간 안에 이메일로 회사소개(보호대 제조 사례 사진, 공장 사진) + 견적 요청 양식(품목/사양/수량/희망단가/납기) 발송. 1주 뒤 재연락.</t>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>통화 후 24시간 안에 이메일로 회사소개(중국 공장 사진, 생산 사례 사진, 자사 제품 판매 페이지) + 견적 요청 양식(품목/사양/수량/희망단가/납기) 발송. 1주 뒤 재연락.</t>
         </is>
       </c>
     </row>
